--- a/dist/templates/quotation.xlsx
+++ b/dist/templates/quotation.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nakorn/Documents/GitHub/Datacom_Status_Tracking_FE/public/templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nakorn/github/Datacom_Status_Tracking_FE/public/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A23D962-DC09-6741-B946-ADF6CE6C64C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B943986-E136-004C-816C-0228D7F45DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -779,21 +779,162 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="19" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -808,147 +949,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="19" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2058,160 +2058,160 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:49" ht="27.75" customHeight="1">
-      <c r="N1" s="76" t="s">
+      <c r="N1" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="O1" s="76"/>
-      <c r="P1" s="76"/>
-      <c r="Q1" s="76"/>
-      <c r="R1" s="76"/>
-      <c r="S1" s="76"/>
-      <c r="T1" s="76"/>
-      <c r="U1" s="76"/>
-      <c r="V1" s="76"/>
-      <c r="W1" s="76"/>
-      <c r="X1" s="76"/>
-      <c r="Y1" s="76"/>
-      <c r="Z1" s="76"/>
-      <c r="AA1" s="76"/>
-      <c r="AB1" s="76"/>
-      <c r="AC1" s="76"/>
-      <c r="AD1" s="76"/>
-      <c r="AE1" s="76"/>
-      <c r="AF1" s="76"/>
-      <c r="AG1" s="76"/>
-      <c r="AH1" s="76"/>
-      <c r="AI1" s="76"/>
-      <c r="AJ1" s="76"/>
-      <c r="AK1" s="76"/>
-      <c r="AL1" s="76"/>
-      <c r="AM1" s="76"/>
-      <c r="AN1" s="76"/>
-      <c r="AO1" s="76"/>
-      <c r="AP1" s="76"/>
-      <c r="AQ1" s="76"/>
-      <c r="AR1" s="76"/>
-      <c r="AS1" s="76"/>
-      <c r="AT1" s="76"/>
-      <c r="AU1" s="76"/>
-      <c r="AV1" s="76"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="41"/>
+      <c r="V1" s="41"/>
+      <c r="W1" s="41"/>
+      <c r="X1" s="41"/>
+      <c r="Y1" s="41"/>
+      <c r="Z1" s="41"/>
+      <c r="AA1" s="41"/>
+      <c r="AB1" s="41"/>
+      <c r="AC1" s="41"/>
+      <c r="AD1" s="41"/>
+      <c r="AE1" s="41"/>
+      <c r="AF1" s="41"/>
+      <c r="AG1" s="41"/>
+      <c r="AH1" s="41"/>
+      <c r="AI1" s="41"/>
+      <c r="AJ1" s="41"/>
+      <c r="AK1" s="41"/>
+      <c r="AL1" s="41"/>
+      <c r="AM1" s="41"/>
+      <c r="AN1" s="41"/>
+      <c r="AO1" s="41"/>
+      <c r="AP1" s="41"/>
+      <c r="AQ1" s="41"/>
+      <c r="AR1" s="41"/>
+      <c r="AS1" s="41"/>
+      <c r="AT1" s="41"/>
+      <c r="AU1" s="41"/>
+      <c r="AV1" s="41"/>
     </row>
     <row r="2" spans="2:49" ht="24" customHeight="1">
       <c r="N2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="AN2" s="40"/>
-      <c r="AO2" s="40"/>
-      <c r="AP2" s="40"/>
-      <c r="AQ2" s="40"/>
-      <c r="AR2" s="40"/>
-      <c r="AS2" s="40"/>
-      <c r="AT2" s="40"/>
-      <c r="AU2" s="40"/>
-      <c r="AV2" s="40"/>
+      <c r="AN2" s="91"/>
+      <c r="AO2" s="91"/>
+      <c r="AP2" s="91"/>
+      <c r="AQ2" s="91"/>
+      <c r="AR2" s="91"/>
+      <c r="AS2" s="91"/>
+      <c r="AT2" s="91"/>
+      <c r="AU2" s="91"/>
+      <c r="AV2" s="91"/>
     </row>
     <row r="3" spans="2:49" ht="21" customHeight="1">
-      <c r="N3" s="47" t="s">
+      <c r="N3" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="W3" s="47"/>
-      <c r="X3" s="47"/>
-      <c r="Y3" s="47"/>
-      <c r="Z3" s="47"/>
-      <c r="AA3" s="47"/>
-      <c r="AB3" s="47"/>
-      <c r="AC3" s="47"/>
-      <c r="AD3" s="47"/>
-      <c r="AE3" s="47"/>
-      <c r="AF3" s="47"/>
-      <c r="AG3" s="47"/>
-      <c r="AH3" s="47"/>
-      <c r="AI3" s="47"/>
-      <c r="AJ3" s="47"/>
-      <c r="AK3" s="47"/>
-      <c r="AL3" s="47"/>
-      <c r="AM3" s="47"/>
-      <c r="AN3" s="40"/>
-      <c r="AO3" s="40"/>
-      <c r="AP3" s="40"/>
-      <c r="AQ3" s="40"/>
-      <c r="AR3" s="40"/>
-      <c r="AS3" s="40"/>
-      <c r="AT3" s="40"/>
-      <c r="AU3" s="40"/>
-      <c r="AV3" s="40"/>
+      <c r="O3" s="94"/>
+      <c r="P3" s="94"/>
+      <c r="Q3" s="94"/>
+      <c r="R3" s="94"/>
+      <c r="S3" s="94"/>
+      <c r="T3" s="94"/>
+      <c r="U3" s="94"/>
+      <c r="V3" s="94"/>
+      <c r="W3" s="94"/>
+      <c r="X3" s="94"/>
+      <c r="Y3" s="94"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
+      <c r="AB3" s="94"/>
+      <c r="AC3" s="94"/>
+      <c r="AD3" s="94"/>
+      <c r="AE3" s="94"/>
+      <c r="AF3" s="94"/>
+      <c r="AG3" s="94"/>
+      <c r="AH3" s="94"/>
+      <c r="AI3" s="94"/>
+      <c r="AJ3" s="94"/>
+      <c r="AK3" s="94"/>
+      <c r="AL3" s="94"/>
+      <c r="AM3" s="94"/>
+      <c r="AN3" s="91"/>
+      <c r="AO3" s="91"/>
+      <c r="AP3" s="91"/>
+      <c r="AQ3" s="91"/>
+      <c r="AR3" s="91"/>
+      <c r="AS3" s="91"/>
+      <c r="AT3" s="91"/>
+      <c r="AU3" s="91"/>
+      <c r="AV3" s="91"/>
     </row>
     <row r="4" spans="2:49" ht="19.5" customHeight="1">
-      <c r="N4" s="47" t="s">
+      <c r="N4" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="W4" s="47"/>
-      <c r="X4" s="47"/>
-      <c r="Y4" s="47"/>
-      <c r="Z4" s="47"/>
-      <c r="AA4" s="47"/>
-      <c r="AB4" s="47"/>
-      <c r="AC4" s="47"/>
-      <c r="AD4" s="47"/>
-      <c r="AE4" s="47"/>
-      <c r="AF4" s="47"/>
-      <c r="AG4" s="47"/>
-      <c r="AH4" s="47"/>
-      <c r="AI4" s="47"/>
-      <c r="AJ4" s="47"/>
-      <c r="AK4" s="47"/>
-      <c r="AL4" s="48" t="s">
+      <c r="O4" s="94"/>
+      <c r="P4" s="94"/>
+      <c r="Q4" s="94"/>
+      <c r="R4" s="94"/>
+      <c r="S4" s="94"/>
+      <c r="T4" s="94"/>
+      <c r="U4" s="94"/>
+      <c r="V4" s="94"/>
+      <c r="W4" s="94"/>
+      <c r="X4" s="94"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
+      <c r="AB4" s="94"/>
+      <c r="AC4" s="94"/>
+      <c r="AD4" s="94"/>
+      <c r="AE4" s="94"/>
+      <c r="AF4" s="94"/>
+      <c r="AG4" s="94"/>
+      <c r="AH4" s="94"/>
+      <c r="AI4" s="94"/>
+      <c r="AJ4" s="94"/>
+      <c r="AK4" s="94"/>
+      <c r="AL4" s="95" t="s">
         <v>34</v>
       </c>
-      <c r="AM4" s="48"/>
-      <c r="AN4" s="48"/>
-      <c r="AO4" s="48"/>
-      <c r="AP4" s="48"/>
-      <c r="AQ4" s="48"/>
-      <c r="AR4" s="48"/>
-      <c r="AS4" s="48"/>
-      <c r="AT4" s="48"/>
-      <c r="AU4" s="48"/>
-      <c r="AV4" s="48"/>
-      <c r="AW4" s="48"/>
+      <c r="AM4" s="95"/>
+      <c r="AN4" s="95"/>
+      <c r="AO4" s="95"/>
+      <c r="AP4" s="95"/>
+      <c r="AQ4" s="95"/>
+      <c r="AR4" s="95"/>
+      <c r="AS4" s="95"/>
+      <c r="AT4" s="95"/>
+      <c r="AU4" s="95"/>
+      <c r="AV4" s="95"/>
+      <c r="AW4" s="95"/>
     </row>
     <row r="5" spans="2:49" s="4" customFormat="1" ht="23.25" customHeight="1">
-      <c r="B5" s="49" t="s">
+      <c r="B5" s="96" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
-      <c r="L5" s="49"/>
-      <c r="M5" s="49"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
+      <c r="C5" s="96"/>
+      <c r="D5" s="96"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="96"/>
+      <c r="H5" s="96"/>
+      <c r="I5" s="96"/>
+      <c r="J5" s="96"/>
+      <c r="K5" s="96"/>
+      <c r="L5" s="96"/>
+      <c r="M5" s="96"/>
+      <c r="N5" s="96"/>
+      <c r="O5" s="96"/>
+      <c r="P5" s="96"/>
+      <c r="Q5" s="96"/>
+      <c r="R5" s="96"/>
+      <c r="S5" s="96"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
       <c r="V5" s="2"/>
@@ -2230,53 +2230,53 @@
       <c r="AI5" s="2"/>
       <c r="AJ5" s="2"/>
       <c r="AK5" s="2"/>
-      <c r="AL5" s="48"/>
-      <c r="AM5" s="48"/>
-      <c r="AN5" s="48"/>
-      <c r="AO5" s="48"/>
-      <c r="AP5" s="48"/>
-      <c r="AQ5" s="48"/>
-      <c r="AR5" s="48"/>
-      <c r="AS5" s="48"/>
-      <c r="AT5" s="48"/>
-      <c r="AU5" s="48"/>
-      <c r="AV5" s="48"/>
-      <c r="AW5" s="48"/>
+      <c r="AL5" s="95"/>
+      <c r="AM5" s="95"/>
+      <c r="AN5" s="95"/>
+      <c r="AO5" s="95"/>
+      <c r="AP5" s="95"/>
+      <c r="AQ5" s="95"/>
+      <c r="AR5" s="95"/>
+      <c r="AS5" s="95"/>
+      <c r="AT5" s="95"/>
+      <c r="AU5" s="95"/>
+      <c r="AV5" s="95"/>
+      <c r="AW5" s="95"/>
     </row>
     <row r="6" spans="2:49" s="4" customFormat="1" ht="23.5" customHeight="1">
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="89" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
-      <c r="P6" s="42"/>
-      <c r="Q6" s="42"/>
-      <c r="R6" s="42"/>
-      <c r="S6" s="42"/>
-      <c r="T6" s="42"/>
-      <c r="U6" s="42"/>
-      <c r="V6" s="42"/>
-      <c r="W6" s="42"/>
-      <c r="X6" s="42"/>
-      <c r="Y6" s="42"/>
-      <c r="Z6" s="42"/>
-      <c r="AA6" s="42"/>
-      <c r="AB6" s="42"/>
-      <c r="AC6" s="42"/>
-      <c r="AD6" s="42"/>
-      <c r="AE6" s="42"/>
-      <c r="AF6" s="42"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
+      <c r="N6" s="70"/>
+      <c r="O6" s="70"/>
+      <c r="P6" s="70"/>
+      <c r="Q6" s="70"/>
+      <c r="R6" s="70"/>
+      <c r="S6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="70"/>
+      <c r="W6" s="70"/>
+      <c r="X6" s="70"/>
+      <c r="Y6" s="70"/>
+      <c r="Z6" s="70"/>
+      <c r="AA6" s="70"/>
+      <c r="AB6" s="70"/>
+      <c r="AC6" s="70"/>
+      <c r="AD6" s="70"/>
+      <c r="AE6" s="70"/>
+      <c r="AF6" s="70"/>
       <c r="AG6" s="6"/>
       <c r="AH6" s="25" t="s">
         <v>4</v>
@@ -2285,52 +2285,52 @@
       <c r="AJ6" s="23"/>
       <c r="AK6" s="23"/>
       <c r="AL6" s="23"/>
-      <c r="AM6" s="43"/>
-      <c r="AN6" s="43"/>
-      <c r="AO6" s="43"/>
-      <c r="AP6" s="43"/>
-      <c r="AQ6" s="43"/>
-      <c r="AR6" s="43"/>
-      <c r="AS6" s="43"/>
-      <c r="AT6" s="43"/>
-      <c r="AU6" s="43"/>
-      <c r="AV6" s="43"/>
-      <c r="AW6" s="43"/>
+      <c r="AM6" s="48"/>
+      <c r="AN6" s="48"/>
+      <c r="AO6" s="48"/>
+      <c r="AP6" s="48"/>
+      <c r="AQ6" s="48"/>
+      <c r="AR6" s="48"/>
+      <c r="AS6" s="48"/>
+      <c r="AT6" s="48"/>
+      <c r="AU6" s="48"/>
+      <c r="AV6" s="48"/>
+      <c r="AW6" s="48"/>
     </row>
     <row r="7" spans="2:49" s="4" customFormat="1" ht="21" customHeight="1">
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="89" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="56"/>
-      <c r="M7" s="56"/>
-      <c r="N7" s="56"/>
-      <c r="O7" s="56"/>
-      <c r="P7" s="56"/>
-      <c r="Q7" s="56"/>
-      <c r="R7" s="56"/>
-      <c r="S7" s="56"/>
-      <c r="T7" s="56"/>
-      <c r="U7" s="56"/>
-      <c r="V7" s="56"/>
-      <c r="W7" s="56"/>
-      <c r="X7" s="56"/>
-      <c r="Y7" s="56"/>
-      <c r="Z7" s="56"/>
-      <c r="AA7" s="56"/>
-      <c r="AB7" s="56"/>
-      <c r="AC7" s="56"/>
-      <c r="AD7" s="56"/>
-      <c r="AE7" s="56"/>
-      <c r="AF7" s="56"/>
+      <c r="C7" s="89"/>
+      <c r="D7" s="89"/>
+      <c r="E7" s="89"/>
+      <c r="F7" s="89"/>
+      <c r="G7" s="90"/>
+      <c r="H7" s="90"/>
+      <c r="I7" s="90"/>
+      <c r="J7" s="90"/>
+      <c r="K7" s="90"/>
+      <c r="L7" s="90"/>
+      <c r="M7" s="90"/>
+      <c r="N7" s="90"/>
+      <c r="O7" s="90"/>
+      <c r="P7" s="90"/>
+      <c r="Q7" s="90"/>
+      <c r="R7" s="90"/>
+      <c r="S7" s="90"/>
+      <c r="T7" s="90"/>
+      <c r="U7" s="90"/>
+      <c r="V7" s="90"/>
+      <c r="W7" s="90"/>
+      <c r="X7" s="90"/>
+      <c r="Y7" s="90"/>
+      <c r="Z7" s="90"/>
+      <c r="AA7" s="90"/>
+      <c r="AB7" s="90"/>
+      <c r="AC7" s="90"/>
+      <c r="AD7" s="90"/>
+      <c r="AE7" s="90"/>
+      <c r="AF7" s="90"/>
       <c r="AG7" s="6"/>
       <c r="AH7" s="26" t="s">
         <v>5</v>
@@ -2339,50 +2339,50 @@
       <c r="AJ7" s="24"/>
       <c r="AK7" s="24"/>
       <c r="AL7" s="24"/>
-      <c r="AM7" s="44"/>
-      <c r="AN7" s="44"/>
-      <c r="AO7" s="44"/>
-      <c r="AP7" s="44"/>
-      <c r="AQ7" s="44"/>
-      <c r="AR7" s="44"/>
-      <c r="AS7" s="44"/>
-      <c r="AT7" s="44"/>
-      <c r="AU7" s="44"/>
-      <c r="AV7" s="44"/>
-      <c r="AW7" s="44"/>
+      <c r="AM7" s="61"/>
+      <c r="AN7" s="61"/>
+      <c r="AO7" s="61"/>
+      <c r="AP7" s="61"/>
+      <c r="AQ7" s="61"/>
+      <c r="AR7" s="61"/>
+      <c r="AS7" s="61"/>
+      <c r="AT7" s="61"/>
+      <c r="AU7" s="61"/>
+      <c r="AV7" s="61"/>
+      <c r="AW7" s="61"/>
     </row>
     <row r="8" spans="2:49" s="4" customFormat="1" ht="21" customHeight="1">
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="56"/>
-      <c r="K8" s="56"/>
-      <c r="L8" s="56"/>
-      <c r="M8" s="56"/>
-      <c r="N8" s="56"/>
-      <c r="O8" s="56"/>
-      <c r="P8" s="56"/>
-      <c r="Q8" s="56"/>
-      <c r="R8" s="56"/>
-      <c r="S8" s="56"/>
-      <c r="T8" s="56"/>
-      <c r="U8" s="56"/>
-      <c r="V8" s="56"/>
-      <c r="W8" s="56"/>
-      <c r="X8" s="56"/>
-      <c r="Y8" s="56"/>
-      <c r="Z8" s="56"/>
-      <c r="AA8" s="56"/>
-      <c r="AB8" s="56"/>
-      <c r="AC8" s="56"/>
-      <c r="AD8" s="56"/>
-      <c r="AE8" s="56"/>
-      <c r="AF8" s="56"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="90"/>
+      <c r="H8" s="90"/>
+      <c r="I8" s="90"/>
+      <c r="J8" s="90"/>
+      <c r="K8" s="90"/>
+      <c r="L8" s="90"/>
+      <c r="M8" s="90"/>
+      <c r="N8" s="90"/>
+      <c r="O8" s="90"/>
+      <c r="P8" s="90"/>
+      <c r="Q8" s="90"/>
+      <c r="R8" s="90"/>
+      <c r="S8" s="90"/>
+      <c r="T8" s="90"/>
+      <c r="U8" s="90"/>
+      <c r="V8" s="90"/>
+      <c r="W8" s="90"/>
+      <c r="X8" s="90"/>
+      <c r="Y8" s="90"/>
+      <c r="Z8" s="90"/>
+      <c r="AA8" s="90"/>
+      <c r="AB8" s="90"/>
+      <c r="AC8" s="90"/>
+      <c r="AD8" s="90"/>
+      <c r="AE8" s="90"/>
+      <c r="AF8" s="90"/>
       <c r="AG8" s="6"/>
       <c r="AH8" s="28" t="s">
         <v>30</v>
@@ -2392,875 +2392,875 @@
       <c r="AK8" s="27"/>
       <c r="AL8" s="27"/>
       <c r="AM8" s="27"/>
-      <c r="AN8" s="53"/>
-      <c r="AO8" s="53"/>
-      <c r="AP8" s="53"/>
-      <c r="AQ8" s="53"/>
-      <c r="AR8" s="53"/>
-      <c r="AS8" s="53"/>
-      <c r="AT8" s="53"/>
-      <c r="AU8" s="53"/>
-      <c r="AV8" s="53"/>
-      <c r="AW8" s="53"/>
+      <c r="AN8" s="86"/>
+      <c r="AO8" s="86"/>
+      <c r="AP8" s="86"/>
+      <c r="AQ8" s="86"/>
+      <c r="AR8" s="86"/>
+      <c r="AS8" s="86"/>
+      <c r="AT8" s="86"/>
+      <c r="AU8" s="86"/>
+      <c r="AV8" s="86"/>
+      <c r="AW8" s="86"/>
     </row>
     <row r="9" spans="2:49" s="4" customFormat="1" ht="21" customHeight="1">
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="54"/>
-      <c r="K9" s="54"/>
-      <c r="L9" s="54"/>
-      <c r="M9" s="54"/>
-      <c r="N9" s="54"/>
-      <c r="O9" s="54"/>
-      <c r="P9" s="55"/>
-      <c r="Q9" s="55"/>
-      <c r="R9" s="55"/>
-      <c r="S9" s="55"/>
-      <c r="T9" s="55"/>
-      <c r="U9" s="55"/>
-      <c r="V9" s="55"/>
-      <c r="W9" s="55"/>
-      <c r="X9" s="55"/>
-      <c r="Y9" s="55"/>
-      <c r="Z9" s="55"/>
-      <c r="AA9" s="55"/>
-      <c r="AB9" s="55"/>
-      <c r="AC9" s="55"/>
-      <c r="AD9" s="55"/>
-      <c r="AE9" s="55"/>
-      <c r="AF9" s="55"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="87"/>
+      <c r="F9" s="87"/>
+      <c r="G9" s="87"/>
+      <c r="H9" s="87"/>
+      <c r="I9" s="87"/>
+      <c r="J9" s="87"/>
+      <c r="K9" s="87"/>
+      <c r="L9" s="87"/>
+      <c r="M9" s="87"/>
+      <c r="N9" s="87"/>
+      <c r="O9" s="87"/>
+      <c r="P9" s="88"/>
+      <c r="Q9" s="88"/>
+      <c r="R9" s="88"/>
+      <c r="S9" s="88"/>
+      <c r="T9" s="88"/>
+      <c r="U9" s="88"/>
+      <c r="V9" s="88"/>
+      <c r="W9" s="88"/>
+      <c r="X9" s="88"/>
+      <c r="Y9" s="88"/>
+      <c r="Z9" s="88"/>
+      <c r="AA9" s="88"/>
+      <c r="AB9" s="88"/>
+      <c r="AC9" s="88"/>
+      <c r="AD9" s="88"/>
+      <c r="AE9" s="88"/>
+      <c r="AF9" s="88"/>
       <c r="AG9" s="6"/>
-      <c r="AH9" s="41" t="s">
+      <c r="AH9" s="89" t="s">
         <v>31</v>
       </c>
-      <c r="AI9" s="41"/>
-      <c r="AJ9" s="41"/>
-      <c r="AK9" s="41"/>
-      <c r="AL9" s="41"/>
-      <c r="AM9" s="41"/>
-      <c r="AN9" s="41"/>
-      <c r="AO9" s="41"/>
-      <c r="AP9" s="41"/>
-      <c r="AQ9" s="41"/>
-      <c r="AR9" s="41"/>
-      <c r="AS9" s="41"/>
-      <c r="AT9" s="41"/>
-      <c r="AU9" s="41"/>
-      <c r="AV9" s="41"/>
-      <c r="AW9" s="41"/>
+      <c r="AI9" s="89"/>
+      <c r="AJ9" s="89"/>
+      <c r="AK9" s="89"/>
+      <c r="AL9" s="89"/>
+      <c r="AM9" s="89"/>
+      <c r="AN9" s="89"/>
+      <c r="AO9" s="89"/>
+      <c r="AP9" s="89"/>
+      <c r="AQ9" s="89"/>
+      <c r="AR9" s="89"/>
+      <c r="AS9" s="89"/>
+      <c r="AT9" s="89"/>
+      <c r="AU9" s="89"/>
+      <c r="AV9" s="89"/>
+      <c r="AW9" s="89"/>
     </row>
     <row r="10" spans="2:49" s="4" customFormat="1" ht="13.25" customHeight="1">
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="45"/>
-      <c r="L10" s="45"/>
-      <c r="M10" s="45"/>
-      <c r="N10" s="45"/>
-      <c r="O10" s="45"/>
-      <c r="P10" s="45"/>
-      <c r="Q10" s="45"/>
-      <c r="R10" s="45"/>
-      <c r="S10" s="45"/>
-      <c r="T10" s="45"/>
-      <c r="U10" s="45"/>
-      <c r="V10" s="45"/>
-      <c r="W10" s="45"/>
-      <c r="X10" s="45"/>
-      <c r="Y10" s="45"/>
-      <c r="Z10" s="45"/>
-      <c r="AA10" s="45"/>
-      <c r="AB10" s="45"/>
-      <c r="AC10" s="45"/>
-      <c r="AD10" s="45"/>
-      <c r="AE10" s="45"/>
-      <c r="AF10" s="45"/>
-      <c r="AG10" s="45"/>
-      <c r="AH10" s="45"/>
-      <c r="AI10" s="45"/>
-      <c r="AJ10" s="45"/>
-      <c r="AK10" s="45"/>
-      <c r="AL10" s="45"/>
-      <c r="AM10" s="45"/>
-      <c r="AN10" s="45"/>
-      <c r="AO10" s="45"/>
-      <c r="AP10" s="45"/>
-      <c r="AQ10" s="45"/>
-      <c r="AR10" s="45"/>
-      <c r="AS10" s="45"/>
-      <c r="AT10" s="45"/>
-      <c r="AU10" s="45"/>
-      <c r="AV10" s="45"/>
-      <c r="AW10" s="45"/>
+      <c r="C10" s="92"/>
+      <c r="D10" s="92"/>
+      <c r="E10" s="92"/>
+      <c r="F10" s="92"/>
+      <c r="G10" s="92"/>
+      <c r="H10" s="92"/>
+      <c r="I10" s="92"/>
+      <c r="J10" s="92"/>
+      <c r="K10" s="92"/>
+      <c r="L10" s="92"/>
+      <c r="M10" s="92"/>
+      <c r="N10" s="92"/>
+      <c r="O10" s="92"/>
+      <c r="P10" s="92"/>
+      <c r="Q10" s="92"/>
+      <c r="R10" s="92"/>
+      <c r="S10" s="92"/>
+      <c r="T10" s="92"/>
+      <c r="U10" s="92"/>
+      <c r="V10" s="92"/>
+      <c r="W10" s="92"/>
+      <c r="X10" s="92"/>
+      <c r="Y10" s="92"/>
+      <c r="Z10" s="92"/>
+      <c r="AA10" s="92"/>
+      <c r="AB10" s="92"/>
+      <c r="AC10" s="92"/>
+      <c r="AD10" s="92"/>
+      <c r="AE10" s="92"/>
+      <c r="AF10" s="92"/>
+      <c r="AG10" s="92"/>
+      <c r="AH10" s="92"/>
+      <c r="AI10" s="92"/>
+      <c r="AJ10" s="92"/>
+      <c r="AK10" s="92"/>
+      <c r="AL10" s="92"/>
+      <c r="AM10" s="92"/>
+      <c r="AN10" s="92"/>
+      <c r="AO10" s="92"/>
+      <c r="AP10" s="92"/>
+      <c r="AQ10" s="92"/>
+      <c r="AR10" s="92"/>
+      <c r="AS10" s="92"/>
+      <c r="AT10" s="92"/>
+      <c r="AU10" s="92"/>
+      <c r="AV10" s="92"/>
+      <c r="AW10" s="92"/>
     </row>
     <row r="11" spans="2:49" s="4" customFormat="1" ht="13.25" customHeight="1" thickBot="1">
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="46"/>
-      <c r="K11" s="46"/>
-      <c r="L11" s="46"/>
-      <c r="M11" s="46"/>
-      <c r="N11" s="46"/>
-      <c r="O11" s="46"/>
-      <c r="P11" s="46"/>
-      <c r="Q11" s="46"/>
-      <c r="R11" s="46"/>
-      <c r="S11" s="46"/>
-      <c r="T11" s="46"/>
-      <c r="U11" s="46"/>
-      <c r="V11" s="46"/>
-      <c r="W11" s="46"/>
-      <c r="X11" s="46"/>
-      <c r="Y11" s="46"/>
-      <c r="Z11" s="46"/>
-      <c r="AA11" s="46"/>
-      <c r="AB11" s="46"/>
-      <c r="AC11" s="46"/>
-      <c r="AD11" s="46"/>
-      <c r="AE11" s="46"/>
-      <c r="AF11" s="46"/>
-      <c r="AG11" s="46"/>
-      <c r="AH11" s="46"/>
-      <c r="AI11" s="46"/>
-      <c r="AJ11" s="46"/>
-      <c r="AK11" s="46"/>
-      <c r="AL11" s="46"/>
-      <c r="AM11" s="46"/>
-      <c r="AN11" s="46"/>
-      <c r="AO11" s="46"/>
-      <c r="AP11" s="46"/>
-      <c r="AQ11" s="46"/>
-      <c r="AR11" s="46"/>
-      <c r="AS11" s="46"/>
-      <c r="AT11" s="46"/>
-      <c r="AU11" s="46"/>
-      <c r="AV11" s="46"/>
-      <c r="AW11" s="46"/>
+      <c r="B11" s="93"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="93"/>
+      <c r="K11" s="93"/>
+      <c r="L11" s="93"/>
+      <c r="M11" s="93"/>
+      <c r="N11" s="93"/>
+      <c r="O11" s="93"/>
+      <c r="P11" s="93"/>
+      <c r="Q11" s="93"/>
+      <c r="R11" s="93"/>
+      <c r="S11" s="93"/>
+      <c r="T11" s="93"/>
+      <c r="U11" s="93"/>
+      <c r="V11" s="93"/>
+      <c r="W11" s="93"/>
+      <c r="X11" s="93"/>
+      <c r="Y11" s="93"/>
+      <c r="Z11" s="93"/>
+      <c r="AA11" s="93"/>
+      <c r="AB11" s="93"/>
+      <c r="AC11" s="93"/>
+      <c r="AD11" s="93"/>
+      <c r="AE11" s="93"/>
+      <c r="AF11" s="93"/>
+      <c r="AG11" s="93"/>
+      <c r="AH11" s="93"/>
+      <c r="AI11" s="93"/>
+      <c r="AJ11" s="93"/>
+      <c r="AK11" s="93"/>
+      <c r="AL11" s="93"/>
+      <c r="AM11" s="93"/>
+      <c r="AN11" s="93"/>
+      <c r="AO11" s="93"/>
+      <c r="AP11" s="93"/>
+      <c r="AQ11" s="93"/>
+      <c r="AR11" s="93"/>
+      <c r="AS11" s="93"/>
+      <c r="AT11" s="93"/>
+      <c r="AU11" s="93"/>
+      <c r="AV11" s="93"/>
+      <c r="AW11" s="93"/>
     </row>
     <row r="12" spans="2:49" s="5" customFormat="1" ht="21" customHeight="1" thickTop="1">
-      <c r="B12" s="50" t="s">
+      <c r="B12" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="50" t="s">
+      <c r="C12" s="84"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="85"/>
+      <c r="F12" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="51"/>
-      <c r="K12" s="51"/>
-      <c r="L12" s="51"/>
-      <c r="M12" s="51"/>
-      <c r="N12" s="51"/>
-      <c r="O12" s="51"/>
-      <c r="P12" s="51"/>
-      <c r="Q12" s="51"/>
-      <c r="R12" s="51"/>
-      <c r="S12" s="51"/>
-      <c r="T12" s="51"/>
-      <c r="U12" s="51"/>
-      <c r="V12" s="51"/>
-      <c r="W12" s="51"/>
-      <c r="X12" s="51"/>
-      <c r="Y12" s="51"/>
-      <c r="Z12" s="51"/>
-      <c r="AA12" s="51"/>
-      <c r="AB12" s="51"/>
-      <c r="AC12" s="51"/>
-      <c r="AD12" s="51"/>
-      <c r="AE12" s="51"/>
-      <c r="AF12" s="52"/>
-      <c r="AG12" s="50" t="s">
+      <c r="G12" s="84"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="84"/>
+      <c r="J12" s="84"/>
+      <c r="K12" s="84"/>
+      <c r="L12" s="84"/>
+      <c r="M12" s="84"/>
+      <c r="N12" s="84"/>
+      <c r="O12" s="84"/>
+      <c r="P12" s="84"/>
+      <c r="Q12" s="84"/>
+      <c r="R12" s="84"/>
+      <c r="S12" s="84"/>
+      <c r="T12" s="84"/>
+      <c r="U12" s="84"/>
+      <c r="V12" s="84"/>
+      <c r="W12" s="84"/>
+      <c r="X12" s="84"/>
+      <c r="Y12" s="84"/>
+      <c r="Z12" s="84"/>
+      <c r="AA12" s="84"/>
+      <c r="AB12" s="84"/>
+      <c r="AC12" s="84"/>
+      <c r="AD12" s="84"/>
+      <c r="AE12" s="84"/>
+      <c r="AF12" s="85"/>
+      <c r="AG12" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="AH12" s="51"/>
-      <c r="AI12" s="51"/>
-      <c r="AJ12" s="51"/>
-      <c r="AK12" s="52"/>
-      <c r="AL12" s="50" t="s">
+      <c r="AH12" s="84"/>
+      <c r="AI12" s="84"/>
+      <c r="AJ12" s="84"/>
+      <c r="AK12" s="85"/>
+      <c r="AL12" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="AM12" s="51"/>
-      <c r="AN12" s="51"/>
-      <c r="AO12" s="51"/>
-      <c r="AP12" s="51"/>
-      <c r="AQ12" s="52"/>
-      <c r="AR12" s="50" t="s">
+      <c r="AM12" s="84"/>
+      <c r="AN12" s="84"/>
+      <c r="AO12" s="84"/>
+      <c r="AP12" s="84"/>
+      <c r="AQ12" s="85"/>
+      <c r="AR12" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="AS12" s="51"/>
-      <c r="AT12" s="51"/>
-      <c r="AU12" s="51"/>
-      <c r="AV12" s="51"/>
-      <c r="AW12" s="52"/>
+      <c r="AS12" s="84"/>
+      <c r="AT12" s="84"/>
+      <c r="AU12" s="84"/>
+      <c r="AV12" s="84"/>
+      <c r="AW12" s="85"/>
     </row>
     <row r="13" spans="2:49" s="4" customFormat="1" ht="17" customHeight="1" thickBot="1">
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="80" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="57" t="s">
+      <c r="C13" s="81"/>
+      <c r="D13" s="81"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="80" t="s">
         <v>11</v>
       </c>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="58"/>
-      <c r="K13" s="58"/>
-      <c r="L13" s="58"/>
-      <c r="M13" s="58"/>
-      <c r="N13" s="58"/>
-      <c r="O13" s="58"/>
-      <c r="P13" s="58"/>
-      <c r="Q13" s="58"/>
-      <c r="R13" s="58"/>
-      <c r="S13" s="58"/>
-      <c r="T13" s="58"/>
-      <c r="U13" s="58"/>
-      <c r="V13" s="58"/>
-      <c r="W13" s="58"/>
-      <c r="X13" s="58"/>
-      <c r="Y13" s="58"/>
-      <c r="Z13" s="58"/>
-      <c r="AA13" s="58"/>
-      <c r="AB13" s="58"/>
-      <c r="AC13" s="58"/>
-      <c r="AD13" s="58"/>
-      <c r="AE13" s="58"/>
-      <c r="AF13" s="59"/>
-      <c r="AG13" s="57" t="s">
+      <c r="G13" s="81"/>
+      <c r="H13" s="81"/>
+      <c r="I13" s="81"/>
+      <c r="J13" s="81"/>
+      <c r="K13" s="81"/>
+      <c r="L13" s="81"/>
+      <c r="M13" s="81"/>
+      <c r="N13" s="81"/>
+      <c r="O13" s="81"/>
+      <c r="P13" s="81"/>
+      <c r="Q13" s="81"/>
+      <c r="R13" s="81"/>
+      <c r="S13" s="81"/>
+      <c r="T13" s="81"/>
+      <c r="U13" s="81"/>
+      <c r="V13" s="81"/>
+      <c r="W13" s="81"/>
+      <c r="X13" s="81"/>
+      <c r="Y13" s="81"/>
+      <c r="Z13" s="81"/>
+      <c r="AA13" s="81"/>
+      <c r="AB13" s="81"/>
+      <c r="AC13" s="81"/>
+      <c r="AD13" s="81"/>
+      <c r="AE13" s="81"/>
+      <c r="AF13" s="82"/>
+      <c r="AG13" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="AH13" s="58"/>
-      <c r="AI13" s="58"/>
-      <c r="AJ13" s="58"/>
-      <c r="AK13" s="59"/>
-      <c r="AL13" s="57" t="s">
+      <c r="AH13" s="81"/>
+      <c r="AI13" s="81"/>
+      <c r="AJ13" s="81"/>
+      <c r="AK13" s="82"/>
+      <c r="AL13" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="AM13" s="58"/>
-      <c r="AN13" s="58"/>
-      <c r="AO13" s="58"/>
-      <c r="AP13" s="58"/>
-      <c r="AQ13" s="59"/>
-      <c r="AR13" s="57" t="s">
+      <c r="AM13" s="81"/>
+      <c r="AN13" s="81"/>
+      <c r="AO13" s="81"/>
+      <c r="AP13" s="81"/>
+      <c r="AQ13" s="82"/>
+      <c r="AR13" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="AS13" s="58"/>
-      <c r="AT13" s="58"/>
-      <c r="AU13" s="58"/>
-      <c r="AV13" s="58"/>
-      <c r="AW13" s="59"/>
+      <c r="AS13" s="81"/>
+      <c r="AT13" s="81"/>
+      <c r="AU13" s="81"/>
+      <c r="AV13" s="81"/>
+      <c r="AW13" s="82"/>
     </row>
     <row r="14" spans="2:49" s="4" customFormat="1" ht="20.5" customHeight="1" thickTop="1">
-      <c r="B14" s="60"/>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="72"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="42"/>
-      <c r="K14" s="42"/>
-      <c r="L14" s="42"/>
-      <c r="M14" s="42"/>
-      <c r="N14" s="42"/>
-      <c r="O14" s="42"/>
-      <c r="P14" s="42"/>
-      <c r="Q14" s="42"/>
-      <c r="R14" s="42"/>
-      <c r="S14" s="42"/>
-      <c r="T14" s="42"/>
-      <c r="U14" s="42"/>
-      <c r="V14" s="42"/>
-      <c r="W14" s="42"/>
-      <c r="X14" s="42"/>
-      <c r="Y14" s="42"/>
-      <c r="Z14" s="42"/>
-      <c r="AA14" s="42"/>
-      <c r="AB14" s="42"/>
-      <c r="AC14" s="42"/>
-      <c r="AD14" s="42"/>
-      <c r="AE14" s="42"/>
-      <c r="AF14" s="42"/>
-      <c r="AG14" s="63"/>
-      <c r="AH14" s="64"/>
-      <c r="AI14" s="64"/>
-      <c r="AJ14" s="64"/>
-      <c r="AK14" s="94"/>
-      <c r="AL14" s="67"/>
-      <c r="AM14" s="67"/>
-      <c r="AN14" s="67"/>
-      <c r="AO14" s="67"/>
-      <c r="AP14" s="67"/>
-      <c r="AQ14" s="68"/>
-      <c r="AR14" s="69"/>
-      <c r="AS14" s="70"/>
-      <c r="AT14" s="70"/>
-      <c r="AU14" s="70"/>
-      <c r="AV14" s="70"/>
-      <c r="AW14" s="71"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="70"/>
+      <c r="L14" s="70"/>
+      <c r="M14" s="70"/>
+      <c r="N14" s="70"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="70"/>
+      <c r="Q14" s="70"/>
+      <c r="R14" s="70"/>
+      <c r="S14" s="70"/>
+      <c r="T14" s="70"/>
+      <c r="U14" s="70"/>
+      <c r="V14" s="70"/>
+      <c r="W14" s="70"/>
+      <c r="X14" s="70"/>
+      <c r="Y14" s="70"/>
+      <c r="Z14" s="70"/>
+      <c r="AA14" s="70"/>
+      <c r="AB14" s="70"/>
+      <c r="AC14" s="70"/>
+      <c r="AD14" s="70"/>
+      <c r="AE14" s="70"/>
+      <c r="AF14" s="70"/>
+      <c r="AG14" s="74"/>
+      <c r="AH14" s="75"/>
+      <c r="AI14" s="75"/>
+      <c r="AJ14" s="75"/>
+      <c r="AK14" s="76"/>
+      <c r="AL14" s="62"/>
+      <c r="AM14" s="62"/>
+      <c r="AN14" s="62"/>
+      <c r="AO14" s="62"/>
+      <c r="AP14" s="62"/>
+      <c r="AQ14" s="63"/>
+      <c r="AR14" s="64"/>
+      <c r="AS14" s="49"/>
+      <c r="AT14" s="49"/>
+      <c r="AU14" s="49"/>
+      <c r="AV14" s="49"/>
+      <c r="AW14" s="65"/>
     </row>
     <row r="15" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B15" s="60"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="72"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="42"/>
-      <c r="K15" s="42"/>
-      <c r="L15" s="42"/>
-      <c r="M15" s="42"/>
-      <c r="N15" s="42"/>
-      <c r="O15" s="42"/>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="42"/>
-      <c r="R15" s="42"/>
-      <c r="S15" s="42"/>
-      <c r="T15" s="42"/>
-      <c r="U15" s="42"/>
-      <c r="V15" s="42"/>
-      <c r="W15" s="42"/>
-      <c r="X15" s="42"/>
-      <c r="Y15" s="42"/>
-      <c r="Z15" s="42"/>
-      <c r="AA15" s="42"/>
-      <c r="AB15" s="42"/>
-      <c r="AC15" s="42"/>
-      <c r="AD15" s="42"/>
-      <c r="AE15" s="42"/>
-      <c r="AF15" s="42"/>
-      <c r="AG15" s="63"/>
-      <c r="AH15" s="64"/>
-      <c r="AI15" s="64"/>
-      <c r="AJ15" s="64"/>
-      <c r="AK15" s="94"/>
-      <c r="AL15" s="67"/>
-      <c r="AM15" s="67"/>
-      <c r="AN15" s="67"/>
-      <c r="AO15" s="67"/>
-      <c r="AP15" s="67"/>
-      <c r="AQ15" s="68"/>
-      <c r="AR15" s="69"/>
-      <c r="AS15" s="70"/>
-      <c r="AT15" s="70"/>
-      <c r="AU15" s="70"/>
-      <c r="AV15" s="70"/>
-      <c r="AW15" s="71"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="67"/>
+      <c r="D15" s="67"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="70"/>
+      <c r="L15" s="70"/>
+      <c r="M15" s="70"/>
+      <c r="N15" s="70"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="70"/>
+      <c r="Q15" s="70"/>
+      <c r="R15" s="70"/>
+      <c r="S15" s="70"/>
+      <c r="T15" s="70"/>
+      <c r="U15" s="70"/>
+      <c r="V15" s="70"/>
+      <c r="W15" s="70"/>
+      <c r="X15" s="70"/>
+      <c r="Y15" s="70"/>
+      <c r="Z15" s="70"/>
+      <c r="AA15" s="70"/>
+      <c r="AB15" s="70"/>
+      <c r="AC15" s="70"/>
+      <c r="AD15" s="70"/>
+      <c r="AE15" s="70"/>
+      <c r="AF15" s="70"/>
+      <c r="AG15" s="74"/>
+      <c r="AH15" s="75"/>
+      <c r="AI15" s="75"/>
+      <c r="AJ15" s="75"/>
+      <c r="AK15" s="76"/>
+      <c r="AL15" s="62"/>
+      <c r="AM15" s="62"/>
+      <c r="AN15" s="62"/>
+      <c r="AO15" s="62"/>
+      <c r="AP15" s="62"/>
+      <c r="AQ15" s="63"/>
+      <c r="AR15" s="64"/>
+      <c r="AS15" s="49"/>
+      <c r="AT15" s="49"/>
+      <c r="AU15" s="49"/>
+      <c r="AV15" s="49"/>
+      <c r="AW15" s="65"/>
     </row>
     <row r="16" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B16" s="60"/>
-      <c r="C16" s="61"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="62"/>
-      <c r="F16" s="65"/>
-      <c r="G16" s="66"/>
-      <c r="H16" s="66"/>
-      <c r="I16" s="66"/>
-      <c r="J16" s="66"/>
-      <c r="K16" s="66"/>
-      <c r="L16" s="66"/>
-      <c r="M16" s="66"/>
-      <c r="N16" s="66"/>
-      <c r="O16" s="66"/>
-      <c r="P16" s="66"/>
-      <c r="Q16" s="66"/>
-      <c r="R16" s="66"/>
-      <c r="S16" s="66"/>
-      <c r="T16" s="66"/>
-      <c r="U16" s="66"/>
-      <c r="V16" s="66"/>
-      <c r="W16" s="66"/>
-      <c r="X16" s="66"/>
-      <c r="Y16" s="66"/>
-      <c r="Z16" s="66"/>
-      <c r="AA16" s="66"/>
-      <c r="AB16" s="66"/>
-      <c r="AC16" s="66"/>
-      <c r="AD16" s="66"/>
-      <c r="AE16" s="66"/>
-      <c r="AF16" s="66"/>
-      <c r="AG16" s="63"/>
-      <c r="AH16" s="64"/>
-      <c r="AI16" s="64"/>
-      <c r="AJ16" s="64"/>
-      <c r="AK16" s="94"/>
-      <c r="AL16" s="67"/>
-      <c r="AM16" s="67"/>
-      <c r="AN16" s="67"/>
-      <c r="AO16" s="67"/>
-      <c r="AP16" s="67"/>
-      <c r="AQ16" s="68"/>
-      <c r="AR16" s="69">
+      <c r="B16" s="66"/>
+      <c r="C16" s="67"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="78"/>
+      <c r="G16" s="79"/>
+      <c r="H16" s="79"/>
+      <c r="I16" s="79"/>
+      <c r="J16" s="79"/>
+      <c r="K16" s="79"/>
+      <c r="L16" s="79"/>
+      <c r="M16" s="79"/>
+      <c r="N16" s="79"/>
+      <c r="O16" s="79"/>
+      <c r="P16" s="79"/>
+      <c r="Q16" s="79"/>
+      <c r="R16" s="79"/>
+      <c r="S16" s="79"/>
+      <c r="T16" s="79"/>
+      <c r="U16" s="79"/>
+      <c r="V16" s="79"/>
+      <c r="W16" s="79"/>
+      <c r="X16" s="79"/>
+      <c r="Y16" s="79"/>
+      <c r="Z16" s="79"/>
+      <c r="AA16" s="79"/>
+      <c r="AB16" s="79"/>
+      <c r="AC16" s="79"/>
+      <c r="AD16" s="79"/>
+      <c r="AE16" s="79"/>
+      <c r="AF16" s="79"/>
+      <c r="AG16" s="74"/>
+      <c r="AH16" s="75"/>
+      <c r="AI16" s="75"/>
+      <c r="AJ16" s="75"/>
+      <c r="AK16" s="76"/>
+      <c r="AL16" s="62"/>
+      <c r="AM16" s="62"/>
+      <c r="AN16" s="62"/>
+      <c r="AO16" s="62"/>
+      <c r="AP16" s="62"/>
+      <c r="AQ16" s="63"/>
+      <c r="AR16" s="64">
         <f t="shared" ref="AR16:AR18" si="0">AL16*AG16</f>
         <v>0</v>
       </c>
-      <c r="AS16" s="70"/>
-      <c r="AT16" s="70"/>
-      <c r="AU16" s="70"/>
-      <c r="AV16" s="70"/>
-      <c r="AW16" s="71"/>
+      <c r="AS16" s="49"/>
+      <c r="AT16" s="49"/>
+      <c r="AU16" s="49"/>
+      <c r="AV16" s="49"/>
+      <c r="AW16" s="65"/>
     </row>
     <row r="17" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B17" s="60"/>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="72"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="42"/>
-      <c r="K17" s="42"/>
-      <c r="L17" s="42"/>
-      <c r="M17" s="42"/>
-      <c r="N17" s="42"/>
-      <c r="O17" s="42"/>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="42"/>
-      <c r="R17" s="42"/>
-      <c r="S17" s="42"/>
-      <c r="T17" s="42"/>
-      <c r="U17" s="42"/>
-      <c r="V17" s="42"/>
-      <c r="W17" s="42"/>
-      <c r="X17" s="42"/>
-      <c r="Y17" s="42"/>
-      <c r="Z17" s="42"/>
-      <c r="AA17" s="42"/>
-      <c r="AB17" s="42"/>
-      <c r="AC17" s="42"/>
-      <c r="AD17" s="42"/>
-      <c r="AE17" s="42"/>
-      <c r="AF17" s="42"/>
-      <c r="AG17" s="63"/>
-      <c r="AH17" s="64"/>
-      <c r="AI17" s="64"/>
-      <c r="AJ17" s="64"/>
-      <c r="AK17" s="94"/>
-      <c r="AL17" s="67"/>
-      <c r="AM17" s="67"/>
-      <c r="AN17" s="67"/>
-      <c r="AO17" s="67"/>
-      <c r="AP17" s="67"/>
-      <c r="AQ17" s="68"/>
-      <c r="AR17" s="69">
+      <c r="B17" s="66"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70"/>
+      <c r="I17" s="70"/>
+      <c r="J17" s="70"/>
+      <c r="K17" s="70"/>
+      <c r="L17" s="70"/>
+      <c r="M17" s="70"/>
+      <c r="N17" s="70"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="70"/>
+      <c r="Q17" s="70"/>
+      <c r="R17" s="70"/>
+      <c r="S17" s="70"/>
+      <c r="T17" s="70"/>
+      <c r="U17" s="70"/>
+      <c r="V17" s="70"/>
+      <c r="W17" s="70"/>
+      <c r="X17" s="70"/>
+      <c r="Y17" s="70"/>
+      <c r="Z17" s="70"/>
+      <c r="AA17" s="70"/>
+      <c r="AB17" s="70"/>
+      <c r="AC17" s="70"/>
+      <c r="AD17" s="70"/>
+      <c r="AE17" s="70"/>
+      <c r="AF17" s="70"/>
+      <c r="AG17" s="74"/>
+      <c r="AH17" s="75"/>
+      <c r="AI17" s="75"/>
+      <c r="AJ17" s="75"/>
+      <c r="AK17" s="76"/>
+      <c r="AL17" s="62"/>
+      <c r="AM17" s="62"/>
+      <c r="AN17" s="62"/>
+      <c r="AO17" s="62"/>
+      <c r="AP17" s="62"/>
+      <c r="AQ17" s="63"/>
+      <c r="AR17" s="64">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AS17" s="70"/>
-      <c r="AT17" s="70"/>
-      <c r="AU17" s="70"/>
-      <c r="AV17" s="70"/>
-      <c r="AW17" s="71"/>
+      <c r="AS17" s="49"/>
+      <c r="AT17" s="49"/>
+      <c r="AU17" s="49"/>
+      <c r="AV17" s="49"/>
+      <c r="AW17" s="65"/>
     </row>
     <row r="18" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B18" s="60"/>
-      <c r="C18" s="61"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="72"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="42"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="42"/>
-      <c r="M18" s="42"/>
-      <c r="N18" s="42"/>
-      <c r="O18" s="42"/>
-      <c r="P18" s="42"/>
-      <c r="Q18" s="42"/>
-      <c r="R18" s="42"/>
-      <c r="S18" s="42"/>
-      <c r="T18" s="42"/>
-      <c r="U18" s="42"/>
-      <c r="V18" s="42"/>
-      <c r="W18" s="42"/>
-      <c r="X18" s="42"/>
-      <c r="Y18" s="42"/>
-      <c r="Z18" s="42"/>
-      <c r="AA18" s="42"/>
-      <c r="AB18" s="42"/>
-      <c r="AC18" s="42"/>
-      <c r="AD18" s="42"/>
-      <c r="AE18" s="42"/>
-      <c r="AF18" s="42"/>
-      <c r="AG18" s="63"/>
-      <c r="AH18" s="64"/>
-      <c r="AI18" s="64"/>
-      <c r="AJ18" s="64"/>
-      <c r="AK18" s="94"/>
-      <c r="AL18" s="67"/>
-      <c r="AM18" s="67"/>
-      <c r="AN18" s="67"/>
-      <c r="AO18" s="67"/>
-      <c r="AP18" s="67"/>
-      <c r="AQ18" s="68"/>
-      <c r="AR18" s="69">
+      <c r="B18" s="66"/>
+      <c r="C18" s="67"/>
+      <c r="D18" s="67"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="70"/>
+      <c r="K18" s="70"/>
+      <c r="L18" s="70"/>
+      <c r="M18" s="70"/>
+      <c r="N18" s="70"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="70"/>
+      <c r="Q18" s="70"/>
+      <c r="R18" s="70"/>
+      <c r="S18" s="70"/>
+      <c r="T18" s="70"/>
+      <c r="U18" s="70"/>
+      <c r="V18" s="70"/>
+      <c r="W18" s="70"/>
+      <c r="X18" s="70"/>
+      <c r="Y18" s="70"/>
+      <c r="Z18" s="70"/>
+      <c r="AA18" s="70"/>
+      <c r="AB18" s="70"/>
+      <c r="AC18" s="70"/>
+      <c r="AD18" s="70"/>
+      <c r="AE18" s="70"/>
+      <c r="AF18" s="70"/>
+      <c r="AG18" s="74"/>
+      <c r="AH18" s="75"/>
+      <c r="AI18" s="75"/>
+      <c r="AJ18" s="75"/>
+      <c r="AK18" s="76"/>
+      <c r="AL18" s="62"/>
+      <c r="AM18" s="62"/>
+      <c r="AN18" s="62"/>
+      <c r="AO18" s="62"/>
+      <c r="AP18" s="62"/>
+      <c r="AQ18" s="63"/>
+      <c r="AR18" s="64">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AS18" s="70"/>
-      <c r="AT18" s="70"/>
-      <c r="AU18" s="70"/>
-      <c r="AV18" s="70"/>
-      <c r="AW18" s="71"/>
+      <c r="AS18" s="49"/>
+      <c r="AT18" s="49"/>
+      <c r="AU18" s="49"/>
+      <c r="AV18" s="49"/>
+      <c r="AW18" s="65"/>
     </row>
     <row r="19" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B19" s="60"/>
-      <c r="C19" s="61"/>
-      <c r="D19" s="61"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="42"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="42"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="42"/>
-      <c r="O19" s="42"/>
-      <c r="P19" s="42"/>
-      <c r="Q19" s="42"/>
-      <c r="R19" s="42"/>
-      <c r="S19" s="42"/>
-      <c r="T19" s="42"/>
-      <c r="U19" s="42"/>
-      <c r="V19" s="42"/>
-      <c r="W19" s="42"/>
-      <c r="X19" s="42"/>
-      <c r="Y19" s="42"/>
-      <c r="Z19" s="42"/>
-      <c r="AA19" s="42"/>
-      <c r="AB19" s="42"/>
-      <c r="AC19" s="42"/>
-      <c r="AD19" s="42"/>
-      <c r="AE19" s="42"/>
-      <c r="AF19" s="42"/>
-      <c r="AG19" s="63"/>
-      <c r="AH19" s="64"/>
-      <c r="AI19" s="64"/>
-      <c r="AJ19" s="64"/>
-      <c r="AK19" s="94"/>
-      <c r="AL19" s="67"/>
-      <c r="AM19" s="67"/>
-      <c r="AN19" s="67"/>
-      <c r="AO19" s="67"/>
-      <c r="AP19" s="67"/>
-      <c r="AQ19" s="68"/>
-      <c r="AR19" s="69">
+      <c r="B19" s="66"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="70"/>
+      <c r="J19" s="70"/>
+      <c r="K19" s="70"/>
+      <c r="L19" s="70"/>
+      <c r="M19" s="70"/>
+      <c r="N19" s="70"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="70"/>
+      <c r="Q19" s="70"/>
+      <c r="R19" s="70"/>
+      <c r="S19" s="70"/>
+      <c r="T19" s="70"/>
+      <c r="U19" s="70"/>
+      <c r="V19" s="70"/>
+      <c r="W19" s="70"/>
+      <c r="X19" s="70"/>
+      <c r="Y19" s="70"/>
+      <c r="Z19" s="70"/>
+      <c r="AA19" s="70"/>
+      <c r="AB19" s="70"/>
+      <c r="AC19" s="70"/>
+      <c r="AD19" s="70"/>
+      <c r="AE19" s="70"/>
+      <c r="AF19" s="70"/>
+      <c r="AG19" s="74"/>
+      <c r="AH19" s="75"/>
+      <c r="AI19" s="75"/>
+      <c r="AJ19" s="75"/>
+      <c r="AK19" s="76"/>
+      <c r="AL19" s="62"/>
+      <c r="AM19" s="62"/>
+      <c r="AN19" s="62"/>
+      <c r="AO19" s="62"/>
+      <c r="AP19" s="62"/>
+      <c r="AQ19" s="63"/>
+      <c r="AR19" s="64">
         <f>AL19*AG19</f>
         <v>0</v>
       </c>
-      <c r="AS19" s="70"/>
-      <c r="AT19" s="70"/>
-      <c r="AU19" s="70"/>
-      <c r="AV19" s="70"/>
-      <c r="AW19" s="71"/>
+      <c r="AS19" s="49"/>
+      <c r="AT19" s="49"/>
+      <c r="AU19" s="49"/>
+      <c r="AV19" s="49"/>
+      <c r="AW19" s="65"/>
     </row>
     <row r="20" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B20" s="60"/>
-      <c r="C20" s="61"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="72"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="42"/>
-      <c r="K20" s="42"/>
-      <c r="L20" s="42"/>
-      <c r="M20" s="42"/>
-      <c r="N20" s="42"/>
-      <c r="O20" s="42"/>
-      <c r="P20" s="42"/>
-      <c r="Q20" s="42"/>
-      <c r="R20" s="42"/>
-      <c r="S20" s="42"/>
-      <c r="T20" s="42"/>
-      <c r="U20" s="42"/>
-      <c r="V20" s="42"/>
-      <c r="W20" s="42"/>
-      <c r="X20" s="42"/>
-      <c r="Y20" s="42"/>
-      <c r="Z20" s="42"/>
-      <c r="AA20" s="42"/>
-      <c r="AB20" s="42"/>
-      <c r="AC20" s="42"/>
-      <c r="AD20" s="42"/>
-      <c r="AE20" s="42"/>
-      <c r="AF20" s="42"/>
-      <c r="AG20" s="63"/>
-      <c r="AH20" s="64"/>
-      <c r="AI20" s="64"/>
-      <c r="AJ20" s="64"/>
-      <c r="AK20" s="94"/>
-      <c r="AL20" s="73"/>
-      <c r="AM20" s="67"/>
-      <c r="AN20" s="67"/>
-      <c r="AO20" s="67"/>
-      <c r="AP20" s="67"/>
-      <c r="AQ20" s="68"/>
-      <c r="AR20" s="69">
+      <c r="B20" s="66"/>
+      <c r="C20" s="67"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="70"/>
+      <c r="K20" s="70"/>
+      <c r="L20" s="70"/>
+      <c r="M20" s="70"/>
+      <c r="N20" s="70"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="70"/>
+      <c r="Q20" s="70"/>
+      <c r="R20" s="70"/>
+      <c r="S20" s="70"/>
+      <c r="T20" s="70"/>
+      <c r="U20" s="70"/>
+      <c r="V20" s="70"/>
+      <c r="W20" s="70"/>
+      <c r="X20" s="70"/>
+      <c r="Y20" s="70"/>
+      <c r="Z20" s="70"/>
+      <c r="AA20" s="70"/>
+      <c r="AB20" s="70"/>
+      <c r="AC20" s="70"/>
+      <c r="AD20" s="70"/>
+      <c r="AE20" s="70"/>
+      <c r="AF20" s="70"/>
+      <c r="AG20" s="74"/>
+      <c r="AH20" s="75"/>
+      <c r="AI20" s="75"/>
+      <c r="AJ20" s="75"/>
+      <c r="AK20" s="76"/>
+      <c r="AL20" s="77"/>
+      <c r="AM20" s="62"/>
+      <c r="AN20" s="62"/>
+      <c r="AO20" s="62"/>
+      <c r="AP20" s="62"/>
+      <c r="AQ20" s="63"/>
+      <c r="AR20" s="64">
         <f>AL20*AG20</f>
         <v>0</v>
       </c>
-      <c r="AS20" s="70"/>
-      <c r="AT20" s="70"/>
-      <c r="AU20" s="70"/>
-      <c r="AV20" s="70"/>
-      <c r="AW20" s="71"/>
+      <c r="AS20" s="49"/>
+      <c r="AT20" s="49"/>
+      <c r="AU20" s="49"/>
+      <c r="AV20" s="49"/>
+      <c r="AW20" s="65"/>
     </row>
     <row r="21" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B21" s="60"/>
-      <c r="C21" s="61"/>
-      <c r="D21" s="61"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="72"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="42"/>
-      <c r="K21" s="42"/>
-      <c r="L21" s="42"/>
-      <c r="M21" s="42"/>
-      <c r="N21" s="42"/>
-      <c r="O21" s="42"/>
-      <c r="P21" s="42"/>
-      <c r="Q21" s="42"/>
-      <c r="R21" s="42"/>
-      <c r="S21" s="42"/>
-      <c r="T21" s="42"/>
-      <c r="U21" s="42"/>
-      <c r="V21" s="42"/>
-      <c r="W21" s="42"/>
-      <c r="X21" s="42"/>
-      <c r="Y21" s="42"/>
-      <c r="Z21" s="42"/>
-      <c r="AA21" s="42"/>
-      <c r="AB21" s="42"/>
-      <c r="AC21" s="42"/>
-      <c r="AD21" s="42"/>
-      <c r="AE21" s="42"/>
-      <c r="AF21" s="42"/>
-      <c r="AG21" s="63"/>
-      <c r="AH21" s="64"/>
-      <c r="AI21" s="64"/>
-      <c r="AJ21" s="64"/>
-      <c r="AK21" s="94"/>
-      <c r="AL21" s="67"/>
-      <c r="AM21" s="67"/>
-      <c r="AN21" s="67"/>
-      <c r="AO21" s="67"/>
-      <c r="AP21" s="67"/>
-      <c r="AQ21" s="68"/>
-      <c r="AR21" s="69">
+      <c r="B21" s="66"/>
+      <c r="C21" s="67"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="69"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="70"/>
+      <c r="J21" s="70"/>
+      <c r="K21" s="70"/>
+      <c r="L21" s="70"/>
+      <c r="M21" s="70"/>
+      <c r="N21" s="70"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="70"/>
+      <c r="Q21" s="70"/>
+      <c r="R21" s="70"/>
+      <c r="S21" s="70"/>
+      <c r="T21" s="70"/>
+      <c r="U21" s="70"/>
+      <c r="V21" s="70"/>
+      <c r="W21" s="70"/>
+      <c r="X21" s="70"/>
+      <c r="Y21" s="70"/>
+      <c r="Z21" s="70"/>
+      <c r="AA21" s="70"/>
+      <c r="AB21" s="70"/>
+      <c r="AC21" s="70"/>
+      <c r="AD21" s="70"/>
+      <c r="AE21" s="70"/>
+      <c r="AF21" s="70"/>
+      <c r="AG21" s="74"/>
+      <c r="AH21" s="75"/>
+      <c r="AI21" s="75"/>
+      <c r="AJ21" s="75"/>
+      <c r="AK21" s="76"/>
+      <c r="AL21" s="62"/>
+      <c r="AM21" s="62"/>
+      <c r="AN21" s="62"/>
+      <c r="AO21" s="62"/>
+      <c r="AP21" s="62"/>
+      <c r="AQ21" s="63"/>
+      <c r="AR21" s="64">
         <f t="shared" ref="AR21:AR35" si="1">AL21*AG21</f>
         <v>0</v>
       </c>
-      <c r="AS21" s="70"/>
-      <c r="AT21" s="70"/>
-      <c r="AU21" s="70"/>
-      <c r="AV21" s="70"/>
-      <c r="AW21" s="71"/>
+      <c r="AS21" s="49"/>
+      <c r="AT21" s="49"/>
+      <c r="AU21" s="49"/>
+      <c r="AV21" s="49"/>
+      <c r="AW21" s="65"/>
     </row>
     <row r="22" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B22" s="60"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="42"/>
-      <c r="J22" s="42"/>
-      <c r="K22" s="42"/>
-      <c r="L22" s="42"/>
-      <c r="M22" s="42"/>
-      <c r="N22" s="42"/>
-      <c r="O22" s="42"/>
-      <c r="P22" s="42"/>
-      <c r="Q22" s="42"/>
-      <c r="R22" s="42"/>
-      <c r="S22" s="42"/>
-      <c r="T22" s="42"/>
-      <c r="U22" s="42"/>
-      <c r="V22" s="42"/>
-      <c r="W22" s="42"/>
-      <c r="X22" s="42"/>
-      <c r="Y22" s="42"/>
-      <c r="Z22" s="42"/>
-      <c r="AA22" s="42"/>
-      <c r="AB22" s="42"/>
-      <c r="AC22" s="42"/>
-      <c r="AD22" s="42"/>
-      <c r="AE22" s="42"/>
-      <c r="AF22" s="42"/>
-      <c r="AG22" s="63"/>
-      <c r="AH22" s="64"/>
-      <c r="AI22" s="64"/>
-      <c r="AJ22" s="64"/>
-      <c r="AK22" s="94"/>
-      <c r="AL22" s="67"/>
-      <c r="AM22" s="67"/>
-      <c r="AN22" s="67"/>
-      <c r="AO22" s="67"/>
-      <c r="AP22" s="67"/>
-      <c r="AQ22" s="68"/>
-      <c r="AR22" s="69">
+      <c r="B22" s="66"/>
+      <c r="C22" s="67"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70"/>
+      <c r="J22" s="70"/>
+      <c r="K22" s="70"/>
+      <c r="L22" s="70"/>
+      <c r="M22" s="70"/>
+      <c r="N22" s="70"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="70"/>
+      <c r="Q22" s="70"/>
+      <c r="R22" s="70"/>
+      <c r="S22" s="70"/>
+      <c r="T22" s="70"/>
+      <c r="U22" s="70"/>
+      <c r="V22" s="70"/>
+      <c r="W22" s="70"/>
+      <c r="X22" s="70"/>
+      <c r="Y22" s="70"/>
+      <c r="Z22" s="70"/>
+      <c r="AA22" s="70"/>
+      <c r="AB22" s="70"/>
+      <c r="AC22" s="70"/>
+      <c r="AD22" s="70"/>
+      <c r="AE22" s="70"/>
+      <c r="AF22" s="70"/>
+      <c r="AG22" s="74"/>
+      <c r="AH22" s="75"/>
+      <c r="AI22" s="75"/>
+      <c r="AJ22" s="75"/>
+      <c r="AK22" s="76"/>
+      <c r="AL22" s="62"/>
+      <c r="AM22" s="62"/>
+      <c r="AN22" s="62"/>
+      <c r="AO22" s="62"/>
+      <c r="AP22" s="62"/>
+      <c r="AQ22" s="63"/>
+      <c r="AR22" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AS22" s="70"/>
-      <c r="AT22" s="70"/>
-      <c r="AU22" s="70"/>
-      <c r="AV22" s="70"/>
-      <c r="AW22" s="71"/>
+      <c r="AS22" s="49"/>
+      <c r="AT22" s="49"/>
+      <c r="AU22" s="49"/>
+      <c r="AV22" s="49"/>
+      <c r="AW22" s="65"/>
     </row>
     <row r="23" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B23" s="60"/>
-      <c r="C23" s="61"/>
-      <c r="D23" s="61"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="72"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="42"/>
-      <c r="K23" s="42"/>
-      <c r="L23" s="42"/>
-      <c r="M23" s="42"/>
-      <c r="N23" s="42"/>
-      <c r="O23" s="42"/>
-      <c r="P23" s="42"/>
-      <c r="Q23" s="42"/>
-      <c r="R23" s="42"/>
-      <c r="S23" s="42"/>
-      <c r="T23" s="42"/>
-      <c r="U23" s="42"/>
-      <c r="V23" s="42"/>
-      <c r="W23" s="42"/>
-      <c r="X23" s="42"/>
-      <c r="Y23" s="42"/>
-      <c r="Z23" s="42"/>
-      <c r="AA23" s="42"/>
-      <c r="AB23" s="42"/>
-      <c r="AC23" s="42"/>
-      <c r="AD23" s="42"/>
-      <c r="AE23" s="42"/>
-      <c r="AF23" s="42"/>
-      <c r="AG23" s="63"/>
-      <c r="AH23" s="64"/>
-      <c r="AI23" s="64"/>
-      <c r="AJ23" s="64"/>
-      <c r="AK23" s="94"/>
-      <c r="AL23" s="67"/>
-      <c r="AM23" s="67"/>
-      <c r="AN23" s="67"/>
-      <c r="AO23" s="67"/>
-      <c r="AP23" s="67"/>
-      <c r="AQ23" s="68"/>
-      <c r="AR23" s="69">
+      <c r="B23" s="66"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="69"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="70"/>
+      <c r="J23" s="70"/>
+      <c r="K23" s="70"/>
+      <c r="L23" s="70"/>
+      <c r="M23" s="70"/>
+      <c r="N23" s="70"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="70"/>
+      <c r="Q23" s="70"/>
+      <c r="R23" s="70"/>
+      <c r="S23" s="70"/>
+      <c r="T23" s="70"/>
+      <c r="U23" s="70"/>
+      <c r="V23" s="70"/>
+      <c r="W23" s="70"/>
+      <c r="X23" s="70"/>
+      <c r="Y23" s="70"/>
+      <c r="Z23" s="70"/>
+      <c r="AA23" s="70"/>
+      <c r="AB23" s="70"/>
+      <c r="AC23" s="70"/>
+      <c r="AD23" s="70"/>
+      <c r="AE23" s="70"/>
+      <c r="AF23" s="70"/>
+      <c r="AG23" s="74"/>
+      <c r="AH23" s="75"/>
+      <c r="AI23" s="75"/>
+      <c r="AJ23" s="75"/>
+      <c r="AK23" s="76"/>
+      <c r="AL23" s="62"/>
+      <c r="AM23" s="62"/>
+      <c r="AN23" s="62"/>
+      <c r="AO23" s="62"/>
+      <c r="AP23" s="62"/>
+      <c r="AQ23" s="63"/>
+      <c r="AR23" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AS23" s="70"/>
-      <c r="AT23" s="70"/>
-      <c r="AU23" s="70"/>
-      <c r="AV23" s="70"/>
-      <c r="AW23" s="71"/>
+      <c r="AS23" s="49"/>
+      <c r="AT23" s="49"/>
+      <c r="AU23" s="49"/>
+      <c r="AV23" s="49"/>
+      <c r="AW23" s="65"/>
     </row>
     <row r="24" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B24" s="60"/>
-      <c r="C24" s="61"/>
-      <c r="D24" s="61"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="72"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="42"/>
-      <c r="I24" s="42"/>
-      <c r="J24" s="42"/>
-      <c r="K24" s="42"/>
-      <c r="L24" s="42"/>
-      <c r="M24" s="42"/>
-      <c r="N24" s="42"/>
-      <c r="O24" s="42"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="42"/>
-      <c r="R24" s="42"/>
-      <c r="S24" s="42"/>
-      <c r="T24" s="42"/>
-      <c r="U24" s="42"/>
-      <c r="V24" s="42"/>
-      <c r="W24" s="42"/>
-      <c r="X24" s="42"/>
-      <c r="Y24" s="42"/>
-      <c r="Z24" s="42"/>
-      <c r="AA24" s="42"/>
-      <c r="AB24" s="42"/>
-      <c r="AC24" s="42"/>
-      <c r="AD24" s="42"/>
-      <c r="AE24" s="42"/>
-      <c r="AF24" s="42"/>
-      <c r="AG24" s="63"/>
-      <c r="AH24" s="64"/>
-      <c r="AI24" s="64"/>
-      <c r="AJ24" s="64"/>
-      <c r="AK24" s="94"/>
-      <c r="AL24" s="67"/>
-      <c r="AM24" s="67"/>
-      <c r="AN24" s="67"/>
-      <c r="AO24" s="67"/>
-      <c r="AP24" s="67"/>
-      <c r="AQ24" s="68"/>
-      <c r="AR24" s="69">
+      <c r="B24" s="66"/>
+      <c r="C24" s="67"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="70"/>
+      <c r="J24" s="70"/>
+      <c r="K24" s="70"/>
+      <c r="L24" s="70"/>
+      <c r="M24" s="70"/>
+      <c r="N24" s="70"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="70"/>
+      <c r="Q24" s="70"/>
+      <c r="R24" s="70"/>
+      <c r="S24" s="70"/>
+      <c r="T24" s="70"/>
+      <c r="U24" s="70"/>
+      <c r="V24" s="70"/>
+      <c r="W24" s="70"/>
+      <c r="X24" s="70"/>
+      <c r="Y24" s="70"/>
+      <c r="Z24" s="70"/>
+      <c r="AA24" s="70"/>
+      <c r="AB24" s="70"/>
+      <c r="AC24" s="70"/>
+      <c r="AD24" s="70"/>
+      <c r="AE24" s="70"/>
+      <c r="AF24" s="70"/>
+      <c r="AG24" s="74"/>
+      <c r="AH24" s="75"/>
+      <c r="AI24" s="75"/>
+      <c r="AJ24" s="75"/>
+      <c r="AK24" s="76"/>
+      <c r="AL24" s="62"/>
+      <c r="AM24" s="62"/>
+      <c r="AN24" s="62"/>
+      <c r="AO24" s="62"/>
+      <c r="AP24" s="62"/>
+      <c r="AQ24" s="63"/>
+      <c r="AR24" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AS24" s="70"/>
-      <c r="AT24" s="70"/>
-      <c r="AU24" s="70"/>
-      <c r="AV24" s="70"/>
-      <c r="AW24" s="71"/>
+      <c r="AS24" s="49"/>
+      <c r="AT24" s="49"/>
+      <c r="AU24" s="49"/>
+      <c r="AV24" s="49"/>
+      <c r="AW24" s="65"/>
     </row>
     <row r="25" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B25" s="60"/>
-      <c r="C25" s="61"/>
-      <c r="D25" s="61"/>
-      <c r="E25" s="62"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="68"/>
       <c r="F25" s="37"/>
       <c r="G25" s="36"/>
       <c r="H25" s="36"/>
@@ -3292,7 +3292,7 @@
       <c r="AH25" s="16"/>
       <c r="AI25" s="16"/>
       <c r="AJ25" s="16"/>
-      <c r="AK25" s="95"/>
+      <c r="AK25" s="40"/>
       <c r="AL25" s="38"/>
       <c r="AM25" s="38"/>
       <c r="AN25" s="38"/>
@@ -3307,328 +3307,328 @@
       <c r="AW25" s="35"/>
     </row>
     <row r="26" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B26" s="60"/>
-      <c r="C26" s="61"/>
-      <c r="D26" s="61"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="72"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="42"/>
-      <c r="K26" s="42"/>
-      <c r="L26" s="42"/>
-      <c r="M26" s="42"/>
-      <c r="N26" s="42"/>
-      <c r="O26" s="42"/>
-      <c r="P26" s="42"/>
-      <c r="Q26" s="42"/>
-      <c r="R26" s="42"/>
-      <c r="S26" s="42"/>
-      <c r="T26" s="42"/>
-      <c r="U26" s="42"/>
-      <c r="V26" s="42"/>
-      <c r="W26" s="42"/>
-      <c r="X26" s="42"/>
-      <c r="Y26" s="42"/>
-      <c r="Z26" s="42"/>
-      <c r="AA26" s="42"/>
-      <c r="AB26" s="42"/>
-      <c r="AC26" s="42"/>
-      <c r="AD26" s="42"/>
-      <c r="AE26" s="42"/>
-      <c r="AF26" s="42"/>
-      <c r="AG26" s="63"/>
-      <c r="AH26" s="64"/>
-      <c r="AI26" s="64"/>
-      <c r="AJ26" s="64"/>
-      <c r="AK26" s="94"/>
-      <c r="AL26" s="67"/>
-      <c r="AM26" s="67"/>
-      <c r="AN26" s="67"/>
-      <c r="AO26" s="67"/>
-      <c r="AP26" s="67"/>
-      <c r="AQ26" s="68"/>
-      <c r="AR26" s="69">
+      <c r="B26" s="66"/>
+      <c r="C26" s="67"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="69"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="70"/>
+      <c r="K26" s="70"/>
+      <c r="L26" s="70"/>
+      <c r="M26" s="70"/>
+      <c r="N26" s="70"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="70"/>
+      <c r="Q26" s="70"/>
+      <c r="R26" s="70"/>
+      <c r="S26" s="70"/>
+      <c r="T26" s="70"/>
+      <c r="U26" s="70"/>
+      <c r="V26" s="70"/>
+      <c r="W26" s="70"/>
+      <c r="X26" s="70"/>
+      <c r="Y26" s="70"/>
+      <c r="Z26" s="70"/>
+      <c r="AA26" s="70"/>
+      <c r="AB26" s="70"/>
+      <c r="AC26" s="70"/>
+      <c r="AD26" s="70"/>
+      <c r="AE26" s="70"/>
+      <c r="AF26" s="70"/>
+      <c r="AG26" s="74"/>
+      <c r="AH26" s="75"/>
+      <c r="AI26" s="75"/>
+      <c r="AJ26" s="75"/>
+      <c r="AK26" s="76"/>
+      <c r="AL26" s="62"/>
+      <c r="AM26" s="62"/>
+      <c r="AN26" s="62"/>
+      <c r="AO26" s="62"/>
+      <c r="AP26" s="62"/>
+      <c r="AQ26" s="63"/>
+      <c r="AR26" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AS26" s="70"/>
-      <c r="AT26" s="70"/>
-      <c r="AU26" s="70"/>
-      <c r="AV26" s="70"/>
-      <c r="AW26" s="71"/>
+      <c r="AS26" s="49"/>
+      <c r="AT26" s="49"/>
+      <c r="AU26" s="49"/>
+      <c r="AV26" s="49"/>
+      <c r="AW26" s="65"/>
     </row>
     <row r="27" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B27" s="60"/>
-      <c r="C27" s="61"/>
-      <c r="D27" s="61"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="72"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="42"/>
-      <c r="K27" s="42"/>
-      <c r="L27" s="42"/>
-      <c r="M27" s="42"/>
-      <c r="N27" s="42"/>
-      <c r="O27" s="42"/>
-      <c r="P27" s="42"/>
-      <c r="Q27" s="42"/>
-      <c r="R27" s="42"/>
-      <c r="S27" s="42"/>
-      <c r="T27" s="42"/>
-      <c r="U27" s="42"/>
-      <c r="V27" s="42"/>
-      <c r="W27" s="42"/>
-      <c r="X27" s="42"/>
-      <c r="Y27" s="42"/>
-      <c r="Z27" s="42"/>
-      <c r="AA27" s="42"/>
-      <c r="AB27" s="42"/>
-      <c r="AC27" s="42"/>
-      <c r="AD27" s="42"/>
-      <c r="AE27" s="42"/>
-      <c r="AF27" s="42"/>
-      <c r="AG27" s="63"/>
-      <c r="AH27" s="64"/>
-      <c r="AI27" s="64"/>
-      <c r="AJ27" s="64"/>
-      <c r="AK27" s="94"/>
-      <c r="AL27" s="67"/>
-      <c r="AM27" s="67"/>
-      <c r="AN27" s="67"/>
-      <c r="AO27" s="67"/>
-      <c r="AP27" s="67"/>
-      <c r="AQ27" s="68"/>
-      <c r="AR27" s="69">
+      <c r="B27" s="66"/>
+      <c r="C27" s="67"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="69"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="70"/>
+      <c r="K27" s="70"/>
+      <c r="L27" s="70"/>
+      <c r="M27" s="70"/>
+      <c r="N27" s="70"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="70"/>
+      <c r="Q27" s="70"/>
+      <c r="R27" s="70"/>
+      <c r="S27" s="70"/>
+      <c r="T27" s="70"/>
+      <c r="U27" s="70"/>
+      <c r="V27" s="70"/>
+      <c r="W27" s="70"/>
+      <c r="X27" s="70"/>
+      <c r="Y27" s="70"/>
+      <c r="Z27" s="70"/>
+      <c r="AA27" s="70"/>
+      <c r="AB27" s="70"/>
+      <c r="AC27" s="70"/>
+      <c r="AD27" s="70"/>
+      <c r="AE27" s="70"/>
+      <c r="AF27" s="70"/>
+      <c r="AG27" s="74"/>
+      <c r="AH27" s="75"/>
+      <c r="AI27" s="75"/>
+      <c r="AJ27" s="75"/>
+      <c r="AK27" s="76"/>
+      <c r="AL27" s="62"/>
+      <c r="AM27" s="62"/>
+      <c r="AN27" s="62"/>
+      <c r="AO27" s="62"/>
+      <c r="AP27" s="62"/>
+      <c r="AQ27" s="63"/>
+      <c r="AR27" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AS27" s="70"/>
-      <c r="AT27" s="70"/>
-      <c r="AU27" s="70"/>
-      <c r="AV27" s="70"/>
-      <c r="AW27" s="71"/>
+      <c r="AS27" s="49"/>
+      <c r="AT27" s="49"/>
+      <c r="AU27" s="49"/>
+      <c r="AV27" s="49"/>
+      <c r="AW27" s="65"/>
     </row>
     <row r="28" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B28" s="60"/>
-      <c r="C28" s="61"/>
-      <c r="D28" s="61"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="72"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="42"/>
-      <c r="J28" s="42"/>
-      <c r="K28" s="42"/>
-      <c r="L28" s="42"/>
-      <c r="M28" s="42"/>
-      <c r="N28" s="42"/>
-      <c r="O28" s="42"/>
-      <c r="P28" s="42"/>
-      <c r="Q28" s="42"/>
-      <c r="R28" s="42"/>
-      <c r="S28" s="42"/>
-      <c r="T28" s="42"/>
-      <c r="U28" s="42"/>
-      <c r="V28" s="42"/>
-      <c r="W28" s="42"/>
-      <c r="X28" s="42"/>
-      <c r="Y28" s="42"/>
-      <c r="Z28" s="42"/>
-      <c r="AA28" s="42"/>
-      <c r="AB28" s="42"/>
-      <c r="AC28" s="42"/>
-      <c r="AD28" s="42"/>
-      <c r="AE28" s="42"/>
-      <c r="AF28" s="42"/>
-      <c r="AG28" s="63"/>
-      <c r="AH28" s="64"/>
-      <c r="AI28" s="64"/>
-      <c r="AJ28" s="64"/>
-      <c r="AK28" s="94"/>
-      <c r="AL28" s="67"/>
-      <c r="AM28" s="67"/>
-      <c r="AN28" s="67"/>
-      <c r="AO28" s="67"/>
-      <c r="AP28" s="67"/>
-      <c r="AQ28" s="68"/>
-      <c r="AR28" s="69">
+      <c r="B28" s="66"/>
+      <c r="C28" s="67"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="69"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="70"/>
+      <c r="K28" s="70"/>
+      <c r="L28" s="70"/>
+      <c r="M28" s="70"/>
+      <c r="N28" s="70"/>
+      <c r="O28" s="70"/>
+      <c r="P28" s="70"/>
+      <c r="Q28" s="70"/>
+      <c r="R28" s="70"/>
+      <c r="S28" s="70"/>
+      <c r="T28" s="70"/>
+      <c r="U28" s="70"/>
+      <c r="V28" s="70"/>
+      <c r="W28" s="70"/>
+      <c r="X28" s="70"/>
+      <c r="Y28" s="70"/>
+      <c r="Z28" s="70"/>
+      <c r="AA28" s="70"/>
+      <c r="AB28" s="70"/>
+      <c r="AC28" s="70"/>
+      <c r="AD28" s="70"/>
+      <c r="AE28" s="70"/>
+      <c r="AF28" s="70"/>
+      <c r="AG28" s="74"/>
+      <c r="AH28" s="75"/>
+      <c r="AI28" s="75"/>
+      <c r="AJ28" s="75"/>
+      <c r="AK28" s="76"/>
+      <c r="AL28" s="62"/>
+      <c r="AM28" s="62"/>
+      <c r="AN28" s="62"/>
+      <c r="AO28" s="62"/>
+      <c r="AP28" s="62"/>
+      <c r="AQ28" s="63"/>
+      <c r="AR28" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AS28" s="70"/>
-      <c r="AT28" s="70"/>
-      <c r="AU28" s="70"/>
-      <c r="AV28" s="70"/>
-      <c r="AW28" s="71"/>
+      <c r="AS28" s="49"/>
+      <c r="AT28" s="49"/>
+      <c r="AU28" s="49"/>
+      <c r="AV28" s="49"/>
+      <c r="AW28" s="65"/>
     </row>
     <row r="29" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B29" s="60"/>
-      <c r="C29" s="61"/>
-      <c r="D29" s="61"/>
-      <c r="E29" s="62"/>
-      <c r="F29" s="72"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="42"/>
-      <c r="J29" s="42"/>
-      <c r="K29" s="42"/>
-      <c r="L29" s="42"/>
-      <c r="M29" s="42"/>
-      <c r="N29" s="42"/>
-      <c r="O29" s="42"/>
-      <c r="P29" s="42"/>
-      <c r="Q29" s="42"/>
-      <c r="R29" s="42"/>
-      <c r="S29" s="42"/>
-      <c r="T29" s="42"/>
-      <c r="U29" s="42"/>
-      <c r="V29" s="42"/>
-      <c r="W29" s="42"/>
-      <c r="X29" s="42"/>
-      <c r="Y29" s="42"/>
-      <c r="Z29" s="42"/>
-      <c r="AA29" s="42"/>
-      <c r="AB29" s="42"/>
-      <c r="AC29" s="42"/>
-      <c r="AD29" s="42"/>
-      <c r="AE29" s="42"/>
-      <c r="AF29" s="42"/>
-      <c r="AG29" s="63"/>
-      <c r="AH29" s="64"/>
-      <c r="AI29" s="64"/>
-      <c r="AJ29" s="64"/>
-      <c r="AK29" s="94"/>
-      <c r="AL29" s="67"/>
-      <c r="AM29" s="67"/>
-      <c r="AN29" s="67"/>
-      <c r="AO29" s="67"/>
-      <c r="AP29" s="67"/>
-      <c r="AQ29" s="68"/>
-      <c r="AR29" s="69">
+      <c r="B29" s="66"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="69"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="70"/>
+      <c r="K29" s="70"/>
+      <c r="L29" s="70"/>
+      <c r="M29" s="70"/>
+      <c r="N29" s="70"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="70"/>
+      <c r="Q29" s="70"/>
+      <c r="R29" s="70"/>
+      <c r="S29" s="70"/>
+      <c r="T29" s="70"/>
+      <c r="U29" s="70"/>
+      <c r="V29" s="70"/>
+      <c r="W29" s="70"/>
+      <c r="X29" s="70"/>
+      <c r="Y29" s="70"/>
+      <c r="Z29" s="70"/>
+      <c r="AA29" s="70"/>
+      <c r="AB29" s="70"/>
+      <c r="AC29" s="70"/>
+      <c r="AD29" s="70"/>
+      <c r="AE29" s="70"/>
+      <c r="AF29" s="70"/>
+      <c r="AG29" s="74"/>
+      <c r="AH29" s="75"/>
+      <c r="AI29" s="75"/>
+      <c r="AJ29" s="75"/>
+      <c r="AK29" s="76"/>
+      <c r="AL29" s="62"/>
+      <c r="AM29" s="62"/>
+      <c r="AN29" s="62"/>
+      <c r="AO29" s="62"/>
+      <c r="AP29" s="62"/>
+      <c r="AQ29" s="63"/>
+      <c r="AR29" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AS29" s="70"/>
-      <c r="AT29" s="70"/>
-      <c r="AU29" s="70"/>
-      <c r="AV29" s="70"/>
-      <c r="AW29" s="71"/>
+      <c r="AS29" s="49"/>
+      <c r="AT29" s="49"/>
+      <c r="AU29" s="49"/>
+      <c r="AV29" s="49"/>
+      <c r="AW29" s="65"/>
     </row>
     <row r="30" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B30" s="60"/>
-      <c r="C30" s="61"/>
-      <c r="D30" s="61"/>
-      <c r="E30" s="62"/>
-      <c r="F30" s="72"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="42"/>
-      <c r="I30" s="42"/>
-      <c r="J30" s="42"/>
-      <c r="K30" s="42"/>
-      <c r="L30" s="42"/>
-      <c r="M30" s="42"/>
-      <c r="N30" s="42"/>
-      <c r="O30" s="42"/>
-      <c r="P30" s="42"/>
-      <c r="Q30" s="42"/>
-      <c r="R30" s="42"/>
-      <c r="S30" s="42"/>
-      <c r="T30" s="42"/>
-      <c r="U30" s="42"/>
-      <c r="V30" s="42"/>
-      <c r="W30" s="42"/>
-      <c r="X30" s="42"/>
-      <c r="Y30" s="42"/>
-      <c r="Z30" s="42"/>
-      <c r="AA30" s="42"/>
-      <c r="AB30" s="42"/>
-      <c r="AC30" s="42"/>
-      <c r="AD30" s="42"/>
-      <c r="AE30" s="42"/>
-      <c r="AF30" s="42"/>
-      <c r="AG30" s="63"/>
-      <c r="AH30" s="64"/>
-      <c r="AI30" s="64"/>
-      <c r="AJ30" s="64"/>
-      <c r="AK30" s="94"/>
-      <c r="AL30" s="67"/>
-      <c r="AM30" s="67"/>
-      <c r="AN30" s="67"/>
-      <c r="AO30" s="67"/>
-      <c r="AP30" s="67"/>
-      <c r="AQ30" s="68"/>
-      <c r="AR30" s="69">
+      <c r="B30" s="66"/>
+      <c r="C30" s="67"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="68"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="70"/>
+      <c r="K30" s="70"/>
+      <c r="L30" s="70"/>
+      <c r="M30" s="70"/>
+      <c r="N30" s="70"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="70"/>
+      <c r="Q30" s="70"/>
+      <c r="R30" s="70"/>
+      <c r="S30" s="70"/>
+      <c r="T30" s="70"/>
+      <c r="U30" s="70"/>
+      <c r="V30" s="70"/>
+      <c r="W30" s="70"/>
+      <c r="X30" s="70"/>
+      <c r="Y30" s="70"/>
+      <c r="Z30" s="70"/>
+      <c r="AA30" s="70"/>
+      <c r="AB30" s="70"/>
+      <c r="AC30" s="70"/>
+      <c r="AD30" s="70"/>
+      <c r="AE30" s="70"/>
+      <c r="AF30" s="70"/>
+      <c r="AG30" s="74"/>
+      <c r="AH30" s="75"/>
+      <c r="AI30" s="75"/>
+      <c r="AJ30" s="75"/>
+      <c r="AK30" s="76"/>
+      <c r="AL30" s="62"/>
+      <c r="AM30" s="62"/>
+      <c r="AN30" s="62"/>
+      <c r="AO30" s="62"/>
+      <c r="AP30" s="62"/>
+      <c r="AQ30" s="63"/>
+      <c r="AR30" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AS30" s="70"/>
-      <c r="AT30" s="70"/>
-      <c r="AU30" s="70"/>
-      <c r="AV30" s="70"/>
-      <c r="AW30" s="71"/>
+      <c r="AS30" s="49"/>
+      <c r="AT30" s="49"/>
+      <c r="AU30" s="49"/>
+      <c r="AV30" s="49"/>
+      <c r="AW30" s="65"/>
     </row>
     <row r="31" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B31" s="60"/>
-      <c r="C31" s="61"/>
-      <c r="D31" s="61"/>
-      <c r="E31" s="62"/>
-      <c r="F31" s="72"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="42"/>
-      <c r="J31" s="42"/>
-      <c r="K31" s="42"/>
-      <c r="L31" s="42"/>
-      <c r="M31" s="42"/>
-      <c r="N31" s="42"/>
-      <c r="O31" s="42"/>
-      <c r="P31" s="42"/>
-      <c r="Q31" s="42"/>
-      <c r="R31" s="42"/>
-      <c r="S31" s="42"/>
-      <c r="T31" s="42"/>
-      <c r="U31" s="42"/>
-      <c r="V31" s="42"/>
-      <c r="W31" s="42"/>
-      <c r="X31" s="42"/>
-      <c r="Y31" s="42"/>
-      <c r="Z31" s="42"/>
-      <c r="AA31" s="42"/>
-      <c r="AB31" s="42"/>
-      <c r="AC31" s="42"/>
-      <c r="AD31" s="42"/>
-      <c r="AE31" s="42"/>
-      <c r="AF31" s="42"/>
-      <c r="AG31" s="63"/>
-      <c r="AH31" s="64"/>
-      <c r="AI31" s="64"/>
-      <c r="AJ31" s="64"/>
-      <c r="AK31" s="94"/>
-      <c r="AL31" s="67"/>
-      <c r="AM31" s="67"/>
-      <c r="AN31" s="67"/>
-      <c r="AO31" s="67"/>
-      <c r="AP31" s="67"/>
-      <c r="AQ31" s="68"/>
-      <c r="AR31" s="69">
+      <c r="B31" s="66"/>
+      <c r="C31" s="67"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="68"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="70"/>
+      <c r="K31" s="70"/>
+      <c r="L31" s="70"/>
+      <c r="M31" s="70"/>
+      <c r="N31" s="70"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="70"/>
+      <c r="Q31" s="70"/>
+      <c r="R31" s="70"/>
+      <c r="S31" s="70"/>
+      <c r="T31" s="70"/>
+      <c r="U31" s="70"/>
+      <c r="V31" s="70"/>
+      <c r="W31" s="70"/>
+      <c r="X31" s="70"/>
+      <c r="Y31" s="70"/>
+      <c r="Z31" s="70"/>
+      <c r="AA31" s="70"/>
+      <c r="AB31" s="70"/>
+      <c r="AC31" s="70"/>
+      <c r="AD31" s="70"/>
+      <c r="AE31" s="70"/>
+      <c r="AF31" s="70"/>
+      <c r="AG31" s="74"/>
+      <c r="AH31" s="75"/>
+      <c r="AI31" s="75"/>
+      <c r="AJ31" s="75"/>
+      <c r="AK31" s="76"/>
+      <c r="AL31" s="62"/>
+      <c r="AM31" s="62"/>
+      <c r="AN31" s="62"/>
+      <c r="AO31" s="62"/>
+      <c r="AP31" s="62"/>
+      <c r="AQ31" s="63"/>
+      <c r="AR31" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AS31" s="70"/>
-      <c r="AT31" s="70"/>
-      <c r="AU31" s="70"/>
-      <c r="AV31" s="70"/>
-      <c r="AW31" s="71"/>
+      <c r="AS31" s="49"/>
+      <c r="AT31" s="49"/>
+      <c r="AU31" s="49"/>
+      <c r="AV31" s="49"/>
+      <c r="AW31" s="65"/>
     </row>
     <row r="32" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B32" s="60"/>
-      <c r="C32" s="61"/>
-      <c r="D32" s="61"/>
-      <c r="E32" s="62"/>
+      <c r="B32" s="66"/>
+      <c r="C32" s="67"/>
+      <c r="D32" s="67"/>
+      <c r="E32" s="68"/>
       <c r="F32" s="37"/>
       <c r="G32" s="36"/>
       <c r="H32" s="36"/>
@@ -3660,7 +3660,7 @@
       <c r="AH32" s="16"/>
       <c r="AI32" s="16"/>
       <c r="AJ32" s="16"/>
-      <c r="AK32" s="95"/>
+      <c r="AK32" s="40"/>
       <c r="AL32" s="38"/>
       <c r="AM32" s="38"/>
       <c r="AN32" s="38"/>
@@ -3675,10 +3675,10 @@
       <c r="AW32" s="35"/>
     </row>
     <row r="33" spans="2:54" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B33" s="60"/>
-      <c r="C33" s="61"/>
-      <c r="D33" s="61"/>
-      <c r="E33" s="62"/>
+      <c r="B33" s="66"/>
+      <c r="C33" s="67"/>
+      <c r="D33" s="67"/>
+      <c r="E33" s="68"/>
       <c r="F33" s="37"/>
       <c r="G33" s="36"/>
       <c r="H33" s="36"/>
@@ -3710,7 +3710,7 @@
       <c r="AH33" s="16"/>
       <c r="AI33" s="16"/>
       <c r="AJ33" s="16"/>
-      <c r="AK33" s="95"/>
+      <c r="AK33" s="40"/>
       <c r="AL33" s="38"/>
       <c r="AM33" s="38"/>
       <c r="AN33" s="38"/>
@@ -3725,168 +3725,168 @@
       <c r="AW33" s="35"/>
     </row>
     <row r="34" spans="2:54" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B34" s="60"/>
-      <c r="C34" s="61"/>
-      <c r="D34" s="61"/>
-      <c r="E34" s="62"/>
-      <c r="F34" s="72"/>
-      <c r="G34" s="42"/>
-      <c r="H34" s="42"/>
-      <c r="I34" s="42"/>
-      <c r="J34" s="42"/>
-      <c r="K34" s="42"/>
-      <c r="L34" s="42"/>
-      <c r="M34" s="42"/>
-      <c r="N34" s="42"/>
-      <c r="O34" s="42"/>
-      <c r="P34" s="42"/>
-      <c r="Q34" s="42"/>
-      <c r="R34" s="42"/>
-      <c r="S34" s="42"/>
-      <c r="T34" s="42"/>
-      <c r="U34" s="42"/>
-      <c r="V34" s="42"/>
-      <c r="W34" s="42"/>
-      <c r="X34" s="42"/>
-      <c r="Y34" s="42"/>
-      <c r="Z34" s="42"/>
-      <c r="AA34" s="42"/>
-      <c r="AB34" s="42"/>
-      <c r="AC34" s="42"/>
-      <c r="AD34" s="42"/>
-      <c r="AE34" s="42"/>
-      <c r="AF34" s="42"/>
-      <c r="AG34" s="63"/>
-      <c r="AH34" s="64"/>
-      <c r="AI34" s="64"/>
-      <c r="AJ34" s="64"/>
-      <c r="AK34" s="94"/>
-      <c r="AL34" s="67"/>
-      <c r="AM34" s="67"/>
-      <c r="AN34" s="67"/>
-      <c r="AO34" s="67"/>
-      <c r="AP34" s="67"/>
-      <c r="AQ34" s="68"/>
-      <c r="AR34" s="69">
+      <c r="B34" s="66"/>
+      <c r="C34" s="67"/>
+      <c r="D34" s="67"/>
+      <c r="E34" s="68"/>
+      <c r="F34" s="69"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70"/>
+      <c r="J34" s="70"/>
+      <c r="K34" s="70"/>
+      <c r="L34" s="70"/>
+      <c r="M34" s="70"/>
+      <c r="N34" s="70"/>
+      <c r="O34" s="70"/>
+      <c r="P34" s="70"/>
+      <c r="Q34" s="70"/>
+      <c r="R34" s="70"/>
+      <c r="S34" s="70"/>
+      <c r="T34" s="70"/>
+      <c r="U34" s="70"/>
+      <c r="V34" s="70"/>
+      <c r="W34" s="70"/>
+      <c r="X34" s="70"/>
+      <c r="Y34" s="70"/>
+      <c r="Z34" s="70"/>
+      <c r="AA34" s="70"/>
+      <c r="AB34" s="70"/>
+      <c r="AC34" s="70"/>
+      <c r="AD34" s="70"/>
+      <c r="AE34" s="70"/>
+      <c r="AF34" s="70"/>
+      <c r="AG34" s="74"/>
+      <c r="AH34" s="75"/>
+      <c r="AI34" s="75"/>
+      <c r="AJ34" s="75"/>
+      <c r="AK34" s="76"/>
+      <c r="AL34" s="62"/>
+      <c r="AM34" s="62"/>
+      <c r="AN34" s="62"/>
+      <c r="AO34" s="62"/>
+      <c r="AP34" s="62"/>
+      <c r="AQ34" s="63"/>
+      <c r="AR34" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AS34" s="70"/>
-      <c r="AT34" s="70"/>
-      <c r="AU34" s="70"/>
-      <c r="AV34" s="70"/>
-      <c r="AW34" s="71"/>
+      <c r="AS34" s="49"/>
+      <c r="AT34" s="49"/>
+      <c r="AU34" s="49"/>
+      <c r="AV34" s="49"/>
+      <c r="AW34" s="65"/>
     </row>
     <row r="35" spans="2:54" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B35" s="60"/>
-      <c r="C35" s="61"/>
-      <c r="D35" s="61"/>
-      <c r="E35" s="62"/>
-      <c r="F35" s="72"/>
-      <c r="G35" s="42"/>
-      <c r="H35" s="42"/>
-      <c r="I35" s="42"/>
-      <c r="J35" s="42"/>
-      <c r="K35" s="42"/>
-      <c r="L35" s="42"/>
-      <c r="M35" s="42"/>
-      <c r="N35" s="42"/>
-      <c r="O35" s="42"/>
-      <c r="P35" s="42"/>
-      <c r="Q35" s="42"/>
-      <c r="R35" s="42"/>
-      <c r="S35" s="42"/>
-      <c r="T35" s="42"/>
-      <c r="U35" s="42"/>
-      <c r="V35" s="42"/>
-      <c r="W35" s="42"/>
-      <c r="X35" s="42"/>
-      <c r="Y35" s="42"/>
-      <c r="Z35" s="42"/>
-      <c r="AA35" s="42"/>
-      <c r="AB35" s="42"/>
-      <c r="AC35" s="42"/>
-      <c r="AD35" s="42"/>
-      <c r="AE35" s="42"/>
-      <c r="AF35" s="42"/>
-      <c r="AG35" s="74"/>
-      <c r="AH35" s="75"/>
-      <c r="AI35" s="75"/>
-      <c r="AJ35" s="75"/>
-      <c r="AK35" s="96"/>
-      <c r="AL35" s="67"/>
-      <c r="AM35" s="67"/>
-      <c r="AN35" s="67"/>
-      <c r="AO35" s="67"/>
-      <c r="AP35" s="67"/>
-      <c r="AQ35" s="68"/>
-      <c r="AR35" s="69">
+      <c r="B35" s="66"/>
+      <c r="C35" s="67"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="69"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="70"/>
+      <c r="K35" s="70"/>
+      <c r="L35" s="70"/>
+      <c r="M35" s="70"/>
+      <c r="N35" s="70"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="70"/>
+      <c r="Q35" s="70"/>
+      <c r="R35" s="70"/>
+      <c r="S35" s="70"/>
+      <c r="T35" s="70"/>
+      <c r="U35" s="70"/>
+      <c r="V35" s="70"/>
+      <c r="W35" s="70"/>
+      <c r="X35" s="70"/>
+      <c r="Y35" s="70"/>
+      <c r="Z35" s="70"/>
+      <c r="AA35" s="70"/>
+      <c r="AB35" s="70"/>
+      <c r="AC35" s="70"/>
+      <c r="AD35" s="70"/>
+      <c r="AE35" s="70"/>
+      <c r="AF35" s="70"/>
+      <c r="AG35" s="71"/>
+      <c r="AH35" s="72"/>
+      <c r="AI35" s="72"/>
+      <c r="AJ35" s="72"/>
+      <c r="AK35" s="73"/>
+      <c r="AL35" s="62"/>
+      <c r="AM35" s="62"/>
+      <c r="AN35" s="62"/>
+      <c r="AO35" s="62"/>
+      <c r="AP35" s="62"/>
+      <c r="AQ35" s="63"/>
+      <c r="AR35" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AS35" s="70"/>
-      <c r="AT35" s="70"/>
-      <c r="AU35" s="70"/>
-      <c r="AV35" s="70"/>
-      <c r="AW35" s="71"/>
+      <c r="AS35" s="49"/>
+      <c r="AT35" s="49"/>
+      <c r="AU35" s="49"/>
+      <c r="AV35" s="49"/>
+      <c r="AW35" s="65"/>
     </row>
     <row r="36" spans="2:54" s="4" customFormat="1" ht="20.5" customHeight="1">
-      <c r="B36" s="87" t="str">
+      <c r="B36" s="54" t="str">
         <f>"(  -"&amp;BAHTTEXT(AR38)&amp;"-  )"</f>
         <v>(  -ศูนย์บาทถ้วน-  )</v>
       </c>
-      <c r="C36" s="88"/>
-      <c r="D36" s="88"/>
-      <c r="E36" s="88"/>
-      <c r="F36" s="88"/>
-      <c r="G36" s="88"/>
-      <c r="H36" s="88"/>
-      <c r="I36" s="88"/>
-      <c r="J36" s="88"/>
-      <c r="K36" s="88"/>
-      <c r="L36" s="88"/>
-      <c r="M36" s="88"/>
-      <c r="N36" s="88"/>
-      <c r="O36" s="88"/>
-      <c r="P36" s="88"/>
-      <c r="Q36" s="88"/>
-      <c r="R36" s="88"/>
-      <c r="S36" s="88"/>
-      <c r="T36" s="88"/>
-      <c r="U36" s="88"/>
-      <c r="V36" s="88"/>
-      <c r="W36" s="88"/>
-      <c r="X36" s="88"/>
-      <c r="Y36" s="88"/>
-      <c r="Z36" s="88"/>
-      <c r="AA36" s="88"/>
-      <c r="AB36" s="88"/>
-      <c r="AC36" s="88"/>
-      <c r="AD36" s="88"/>
-      <c r="AE36" s="88"/>
-      <c r="AF36" s="89"/>
-      <c r="AG36" s="90" t="s">
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
+      <c r="J36" s="55"/>
+      <c r="K36" s="55"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="55"/>
+      <c r="N36" s="55"/>
+      <c r="O36" s="55"/>
+      <c r="P36" s="55"/>
+      <c r="Q36" s="55"/>
+      <c r="R36" s="55"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="55"/>
+      <c r="U36" s="55"/>
+      <c r="V36" s="55"/>
+      <c r="W36" s="55"/>
+      <c r="X36" s="55"/>
+      <c r="Y36" s="55"/>
+      <c r="Z36" s="55"/>
+      <c r="AA36" s="55"/>
+      <c r="AB36" s="55"/>
+      <c r="AC36" s="55"/>
+      <c r="AD36" s="55"/>
+      <c r="AE36" s="55"/>
+      <c r="AF36" s="56"/>
+      <c r="AG36" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="AH36" s="43"/>
-      <c r="AI36" s="43"/>
-      <c r="AJ36" s="43"/>
-      <c r="AK36" s="43"/>
-      <c r="AL36" s="91"/>
-      <c r="AM36" s="91"/>
-      <c r="AN36" s="91"/>
-      <c r="AO36" s="91"/>
-      <c r="AP36" s="91"/>
-      <c r="AQ36" s="91"/>
-      <c r="AR36" s="92">
+      <c r="AH36" s="48"/>
+      <c r="AI36" s="48"/>
+      <c r="AJ36" s="48"/>
+      <c r="AK36" s="48"/>
+      <c r="AL36" s="58"/>
+      <c r="AM36" s="58"/>
+      <c r="AN36" s="58"/>
+      <c r="AO36" s="58"/>
+      <c r="AP36" s="58"/>
+      <c r="AQ36" s="58"/>
+      <c r="AR36" s="59">
         <f>AR38*100/107</f>
         <v>0</v>
       </c>
-      <c r="AS36" s="92"/>
-      <c r="AT36" s="92"/>
-      <c r="AU36" s="92"/>
-      <c r="AV36" s="92"/>
-      <c r="AW36" s="92"/>
+      <c r="AS36" s="59"/>
+      <c r="AT36" s="59"/>
+      <c r="AU36" s="59"/>
+      <c r="AV36" s="59"/>
+      <c r="AW36" s="59"/>
     </row>
     <row r="37" spans="2:54" s="4" customFormat="1" ht="20.5" customHeight="1">
       <c r="B37" s="16"/>
@@ -3920,28 +3920,28 @@
       <c r="AD37" s="16"/>
       <c r="AE37" s="16"/>
       <c r="AF37" s="16"/>
-      <c r="AG37" s="90" t="s">
+      <c r="AG37" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="AH37" s="43"/>
-      <c r="AI37" s="43"/>
-      <c r="AJ37" s="43"/>
-      <c r="AK37" s="43"/>
-      <c r="AL37" s="43"/>
-      <c r="AM37" s="43"/>
-      <c r="AN37" s="43"/>
-      <c r="AO37" s="43"/>
-      <c r="AP37" s="43"/>
-      <c r="AQ37" s="43"/>
-      <c r="AR37" s="92">
+      <c r="AH37" s="48"/>
+      <c r="AI37" s="48"/>
+      <c r="AJ37" s="48"/>
+      <c r="AK37" s="48"/>
+      <c r="AL37" s="48"/>
+      <c r="AM37" s="48"/>
+      <c r="AN37" s="48"/>
+      <c r="AO37" s="48"/>
+      <c r="AP37" s="48"/>
+      <c r="AQ37" s="48"/>
+      <c r="AR37" s="59">
         <f>AR38-AR36</f>
         <v>0</v>
       </c>
-      <c r="AS37" s="92"/>
-      <c r="AT37" s="92"/>
-      <c r="AU37" s="92"/>
-      <c r="AV37" s="92"/>
-      <c r="AW37" s="92"/>
+      <c r="AS37" s="59"/>
+      <c r="AT37" s="59"/>
+      <c r="AU37" s="59"/>
+      <c r="AV37" s="59"/>
+      <c r="AW37" s="59"/>
     </row>
     <row r="38" spans="2:54" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="B38" s="6"/>
@@ -3975,28 +3975,28 @@
       <c r="AD38" s="6"/>
       <c r="AE38" s="6"/>
       <c r="AF38" s="6"/>
-      <c r="AG38" s="93" t="s">
+      <c r="AG38" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="AH38" s="44"/>
-      <c r="AI38" s="44"/>
-      <c r="AJ38" s="44"/>
-      <c r="AK38" s="44"/>
-      <c r="AL38" s="44"/>
-      <c r="AM38" s="44"/>
-      <c r="AN38" s="44"/>
-      <c r="AO38" s="44"/>
-      <c r="AP38" s="44"/>
-      <c r="AQ38" s="44"/>
-      <c r="AR38" s="92">
+      <c r="AH38" s="61"/>
+      <c r="AI38" s="61"/>
+      <c r="AJ38" s="61"/>
+      <c r="AK38" s="61"/>
+      <c r="AL38" s="61"/>
+      <c r="AM38" s="61"/>
+      <c r="AN38" s="61"/>
+      <c r="AO38" s="61"/>
+      <c r="AP38" s="61"/>
+      <c r="AQ38" s="61"/>
+      <c r="AR38" s="59">
         <f>SUM(AR14:AW34)</f>
         <v>0</v>
       </c>
-      <c r="AS38" s="92"/>
-      <c r="AT38" s="92"/>
-      <c r="AU38" s="92"/>
-      <c r="AV38" s="92"/>
-      <c r="AW38" s="92"/>
+      <c r="AS38" s="59"/>
+      <c r="AT38" s="59"/>
+      <c r="AU38" s="59"/>
+      <c r="AV38" s="59"/>
+      <c r="AW38" s="59"/>
     </row>
     <row r="39" spans="2:54" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="B39" s="17"/>
@@ -4036,23 +4036,23 @@
       <c r="AD39" s="17"/>
       <c r="AE39" s="17"/>
       <c r="AF39" s="17"/>
-      <c r="AG39" s="43"/>
-      <c r="AH39" s="43"/>
-      <c r="AI39" s="43"/>
-      <c r="AJ39" s="43"/>
-      <c r="AK39" s="43"/>
-      <c r="AL39" s="43"/>
-      <c r="AM39" s="43"/>
-      <c r="AN39" s="43"/>
-      <c r="AO39" s="43"/>
-      <c r="AP39" s="43"/>
-      <c r="AQ39" s="43"/>
-      <c r="AR39" s="70"/>
-      <c r="AS39" s="70"/>
-      <c r="AT39" s="70"/>
-      <c r="AU39" s="70"/>
-      <c r="AV39" s="70"/>
-      <c r="AW39" s="70"/>
+      <c r="AG39" s="48"/>
+      <c r="AH39" s="48"/>
+      <c r="AI39" s="48"/>
+      <c r="AJ39" s="48"/>
+      <c r="AK39" s="48"/>
+      <c r="AL39" s="48"/>
+      <c r="AM39" s="48"/>
+      <c r="AN39" s="48"/>
+      <c r="AO39" s="48"/>
+      <c r="AP39" s="48"/>
+      <c r="AQ39" s="48"/>
+      <c r="AR39" s="49"/>
+      <c r="AS39" s="49"/>
+      <c r="AT39" s="49"/>
+      <c r="AU39" s="49"/>
+      <c r="AV39" s="49"/>
+      <c r="AW39" s="49"/>
     </row>
     <row r="40" spans="2:54" ht="12.5" customHeight="1">
       <c r="D40" s="29" t="s">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="Q41" s="7"/>
       <c r="R41" s="7"/>
-      <c r="S41" s="83"/>
-      <c r="T41" s="83"/>
-      <c r="U41" s="79" t="s">
+      <c r="S41" s="50"/>
+      <c r="T41" s="50"/>
+      <c r="U41" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="V41" s="79"/>
+      <c r="V41" s="44"/>
       <c r="W41" s="20"/>
       <c r="X41" s="20"/>
       <c r="Y41" s="30"/>
@@ -4247,66 +4247,66 @@
       <c r="AD43" s="13"/>
       <c r="AE43" s="13"/>
       <c r="AF43" s="13"/>
-      <c r="AG43" s="84"/>
-      <c r="AH43" s="84"/>
-      <c r="AI43" s="84"/>
-      <c r="AJ43" s="84"/>
+      <c r="AG43" s="51"/>
+      <c r="AH43" s="51"/>
+      <c r="AI43" s="51"/>
+      <c r="AJ43" s="51"/>
       <c r="AK43" s="13"/>
       <c r="AL43" s="13"/>
       <c r="AM43" s="13"/>
       <c r="AN43" s="13"/>
     </row>
     <row r="44" spans="2:54" ht="12.5" customHeight="1">
-      <c r="B44" s="85" t="s">
+      <c r="B44" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="86"/>
-      <c r="D44" s="86"/>
-      <c r="E44" s="86"/>
-      <c r="F44" s="86"/>
-      <c r="G44" s="86"/>
-      <c r="H44" s="86"/>
-      <c r="I44" s="86"/>
-      <c r="J44" s="86"/>
-      <c r="K44" s="86"/>
-      <c r="L44" s="86"/>
-      <c r="M44" s="86"/>
-      <c r="N44" s="86"/>
-      <c r="O44" s="86"/>
-      <c r="P44" s="86"/>
-      <c r="Q44" s="86"/>
-      <c r="R44" s="86"/>
-      <c r="S44" s="86"/>
-      <c r="T44" s="86"/>
-      <c r="U44" s="86"/>
-      <c r="V44" s="86"/>
-      <c r="W44" s="86"/>
-      <c r="X44" s="86"/>
-      <c r="Y44" s="86"/>
-      <c r="Z44" s="86"/>
-      <c r="AA44" s="86"/>
-      <c r="AB44" s="86"/>
-      <c r="AC44" s="86"/>
-      <c r="AD44" s="86"/>
-      <c r="AE44" s="86"/>
-      <c r="AF44" s="86"/>
-      <c r="AG44" s="86"/>
-      <c r="AH44" s="86"/>
-      <c r="AI44" s="86"/>
-      <c r="AJ44" s="86"/>
-      <c r="AK44" s="86"/>
-      <c r="AL44" s="86"/>
-      <c r="AM44" s="86"/>
-      <c r="AN44" s="86"/>
-      <c r="AO44" s="86"/>
-      <c r="AP44" s="86"/>
-      <c r="AQ44" s="86"/>
-      <c r="AR44" s="86"/>
-      <c r="AS44" s="86"/>
-      <c r="AT44" s="86"/>
-      <c r="AU44" s="86"/>
-      <c r="AV44" s="86"/>
-      <c r="AW44" s="86"/>
+      <c r="C44" s="53"/>
+      <c r="D44" s="53"/>
+      <c r="E44" s="53"/>
+      <c r="F44" s="53"/>
+      <c r="G44" s="53"/>
+      <c r="H44" s="53"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="53"/>
+      <c r="K44" s="53"/>
+      <c r="L44" s="53"/>
+      <c r="M44" s="53"/>
+      <c r="N44" s="53"/>
+      <c r="O44" s="53"/>
+      <c r="P44" s="53"/>
+      <c r="Q44" s="53"/>
+      <c r="R44" s="53"/>
+      <c r="S44" s="53"/>
+      <c r="T44" s="53"/>
+      <c r="U44" s="53"/>
+      <c r="V44" s="53"/>
+      <c r="W44" s="53"/>
+      <c r="X44" s="53"/>
+      <c r="Y44" s="53"/>
+      <c r="Z44" s="53"/>
+      <c r="AA44" s="53"/>
+      <c r="AB44" s="53"/>
+      <c r="AC44" s="53"/>
+      <c r="AD44" s="53"/>
+      <c r="AE44" s="53"/>
+      <c r="AF44" s="53"/>
+      <c r="AG44" s="53"/>
+      <c r="AH44" s="53"/>
+      <c r="AI44" s="53"/>
+      <c r="AJ44" s="53"/>
+      <c r="AK44" s="53"/>
+      <c r="AL44" s="53"/>
+      <c r="AM44" s="53"/>
+      <c r="AN44" s="53"/>
+      <c r="AO44" s="53"/>
+      <c r="AP44" s="53"/>
+      <c r="AQ44" s="53"/>
+      <c r="AR44" s="53"/>
+      <c r="AS44" s="53"/>
+      <c r="AT44" s="53"/>
+      <c r="AU44" s="53"/>
+      <c r="AV44" s="53"/>
+      <c r="AW44" s="53"/>
     </row>
     <row r="45" spans="2:54" ht="12.5" customHeight="1">
       <c r="B45" s="7"/>
@@ -4323,27 +4323,27 @@
       <c r="M45" s="7"/>
       <c r="N45" s="7"/>
       <c r="O45" s="7"/>
-      <c r="P45" s="78"/>
-      <c r="Q45" s="78"/>
-      <c r="R45" s="79"/>
-      <c r="S45" s="79"/>
+      <c r="P45" s="43"/>
+      <c r="Q45" s="43"/>
+      <c r="R45" s="44"/>
+      <c r="S45" s="44"/>
       <c r="T45" s="7"/>
-      <c r="U45" s="80"/>
-      <c r="V45" s="80"/>
-      <c r="W45" s="80"/>
-      <c r="X45" s="80"/>
-      <c r="Y45" s="80"/>
-      <c r="Z45" s="80"/>
-      <c r="AA45" s="80"/>
-      <c r="AB45" s="80"/>
-      <c r="AC45" s="80"/>
-      <c r="AD45" s="80"/>
-      <c r="AE45" s="80"/>
-      <c r="AF45" s="80"/>
-      <c r="AG45" s="80"/>
-      <c r="AH45" s="80"/>
-      <c r="AI45" s="80"/>
-      <c r="AJ45" s="80"/>
+      <c r="U45" s="45"/>
+      <c r="V45" s="45"/>
+      <c r="W45" s="45"/>
+      <c r="X45" s="45"/>
+      <c r="Y45" s="45"/>
+      <c r="Z45" s="45"/>
+      <c r="AA45" s="45"/>
+      <c r="AB45" s="45"/>
+      <c r="AC45" s="45"/>
+      <c r="AD45" s="45"/>
+      <c r="AE45" s="45"/>
+      <c r="AF45" s="45"/>
+      <c r="AG45" s="45"/>
+      <c r="AH45" s="45"/>
+      <c r="AI45" s="45"/>
+      <c r="AJ45" s="45"/>
       <c r="AK45" s="7"/>
       <c r="AL45" s="7"/>
       <c r="AM45" s="7"/>
@@ -4351,161 +4351,161 @@
     </row>
     <row r="46" spans="2:54" ht="20" customHeight="1" thickBot="1">
       <c r="B46" s="7"/>
-      <c r="C46" s="81"/>
-      <c r="D46" s="81"/>
-      <c r="E46" s="81"/>
-      <c r="F46" s="81"/>
-      <c r="G46" s="81"/>
-      <c r="H46" s="81"/>
-      <c r="I46" s="81"/>
-      <c r="J46" s="81"/>
-      <c r="K46" s="81"/>
-      <c r="L46" s="81"/>
-      <c r="M46" s="81"/>
-      <c r="N46" s="81"/>
-      <c r="O46" s="81"/>
-      <c r="P46" s="81"/>
-      <c r="Q46" s="81"/>
-      <c r="R46" s="81"/>
-      <c r="S46" s="81"/>
-      <c r="T46" s="81"/>
-      <c r="U46" s="81"/>
-      <c r="V46" s="81"/>
-      <c r="W46" s="81"/>
-      <c r="X46" s="81"/>
+      <c r="C46" s="46"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="46"/>
+      <c r="G46" s="46"/>
+      <c r="H46" s="46"/>
+      <c r="I46" s="46"/>
+      <c r="J46" s="46"/>
+      <c r="K46" s="46"/>
+      <c r="L46" s="46"/>
+      <c r="M46" s="46"/>
+      <c r="N46" s="46"/>
+      <c r="O46" s="46"/>
+      <c r="P46" s="46"/>
+      <c r="Q46" s="46"/>
+      <c r="R46" s="46"/>
+      <c r="S46" s="46"/>
+      <c r="T46" s="46"/>
+      <c r="U46" s="46"/>
+      <c r="V46" s="46"/>
+      <c r="W46" s="46"/>
+      <c r="X46" s="46"/>
       <c r="Y46" s="22"/>
-      <c r="Z46" s="81"/>
-      <c r="AA46" s="81"/>
-      <c r="AB46" s="81"/>
-      <c r="AC46" s="81"/>
-      <c r="AD46" s="81"/>
-      <c r="AE46" s="81"/>
-      <c r="AF46" s="81"/>
-      <c r="AG46" s="81"/>
-      <c r="AH46" s="81"/>
-      <c r="AI46" s="81"/>
-      <c r="AJ46" s="81"/>
-      <c r="AK46" s="81"/>
-      <c r="AL46" s="81"/>
-      <c r="AM46" s="81"/>
-      <c r="AN46" s="81"/>
-      <c r="AO46" s="81"/>
-      <c r="AP46" s="81"/>
-      <c r="AQ46" s="81"/>
-      <c r="AR46" s="81"/>
-      <c r="AS46" s="81"/>
-      <c r="AT46" s="81"/>
-      <c r="AU46" s="81"/>
-      <c r="AV46" s="81"/>
-      <c r="AW46" s="81"/>
+      <c r="Z46" s="46"/>
+      <c r="AA46" s="46"/>
+      <c r="AB46" s="46"/>
+      <c r="AC46" s="46"/>
+      <c r="AD46" s="46"/>
+      <c r="AE46" s="46"/>
+      <c r="AF46" s="46"/>
+      <c r="AG46" s="46"/>
+      <c r="AH46" s="46"/>
+      <c r="AI46" s="46"/>
+      <c r="AJ46" s="46"/>
+      <c r="AK46" s="46"/>
+      <c r="AL46" s="46"/>
+      <c r="AM46" s="46"/>
+      <c r="AN46" s="46"/>
+      <c r="AO46" s="46"/>
+      <c r="AP46" s="46"/>
+      <c r="AQ46" s="46"/>
+      <c r="AR46" s="46"/>
+      <c r="AS46" s="46"/>
+      <c r="AT46" s="46"/>
+      <c r="AU46" s="46"/>
+      <c r="AV46" s="46"/>
+      <c r="AW46" s="46"/>
     </row>
     <row r="47" spans="2:54" ht="22.25" customHeight="1" thickTop="1">
       <c r="B47" s="7"/>
-      <c r="C47" s="82" t="s">
+      <c r="C47" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="D47" s="82"/>
-      <c r="E47" s="82"/>
-      <c r="F47" s="82"/>
-      <c r="G47" s="82"/>
-      <c r="H47" s="82"/>
-      <c r="I47" s="82"/>
-      <c r="J47" s="82"/>
-      <c r="K47" s="82"/>
-      <c r="L47" s="82"/>
-      <c r="M47" s="82"/>
-      <c r="N47" s="82"/>
-      <c r="O47" s="82"/>
-      <c r="P47" s="82"/>
-      <c r="Q47" s="82"/>
-      <c r="R47" s="82"/>
-      <c r="S47" s="82"/>
-      <c r="T47" s="82"/>
-      <c r="U47" s="82"/>
-      <c r="V47" s="82"/>
-      <c r="W47" s="82"/>
-      <c r="X47" s="82"/>
+      <c r="D47" s="47"/>
+      <c r="E47" s="47"/>
+      <c r="F47" s="47"/>
+      <c r="G47" s="47"/>
+      <c r="H47" s="47"/>
+      <c r="I47" s="47"/>
+      <c r="J47" s="47"/>
+      <c r="K47" s="47"/>
+      <c r="L47" s="47"/>
+      <c r="M47" s="47"/>
+      <c r="N47" s="47"/>
+      <c r="O47" s="47"/>
+      <c r="P47" s="47"/>
+      <c r="Q47" s="47"/>
+      <c r="R47" s="47"/>
+      <c r="S47" s="47"/>
+      <c r="T47" s="47"/>
+      <c r="U47" s="47"/>
+      <c r="V47" s="47"/>
+      <c r="W47" s="47"/>
+      <c r="X47" s="47"/>
       <c r="Y47" s="7"/>
-      <c r="Z47" s="82" t="s">
+      <c r="Z47" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="AA47" s="82"/>
-      <c r="AB47" s="82"/>
-      <c r="AC47" s="82"/>
-      <c r="AD47" s="82"/>
-      <c r="AE47" s="82"/>
-      <c r="AF47" s="82"/>
-      <c r="AG47" s="82"/>
-      <c r="AH47" s="82"/>
-      <c r="AI47" s="82"/>
-      <c r="AJ47" s="82"/>
-      <c r="AK47" s="82"/>
-      <c r="AL47" s="82"/>
-      <c r="AM47" s="82"/>
-      <c r="AN47" s="82"/>
-      <c r="AO47" s="82"/>
-      <c r="AP47" s="82"/>
-      <c r="AQ47" s="82"/>
-      <c r="AR47" s="82"/>
-      <c r="AS47" s="82"/>
-      <c r="AT47" s="82"/>
-      <c r="AU47" s="82"/>
-      <c r="AV47" s="82"/>
-      <c r="AW47" s="82"/>
+      <c r="AA47" s="47"/>
+      <c r="AB47" s="47"/>
+      <c r="AC47" s="47"/>
+      <c r="AD47" s="47"/>
+      <c r="AE47" s="47"/>
+      <c r="AF47" s="47"/>
+      <c r="AG47" s="47"/>
+      <c r="AH47" s="47"/>
+      <c r="AI47" s="47"/>
+      <c r="AJ47" s="47"/>
+      <c r="AK47" s="47"/>
+      <c r="AL47" s="47"/>
+      <c r="AM47" s="47"/>
+      <c r="AN47" s="47"/>
+      <c r="AO47" s="47"/>
+      <c r="AP47" s="47"/>
+      <c r="AQ47" s="47"/>
+      <c r="AR47" s="47"/>
+      <c r="AS47" s="47"/>
+      <c r="AT47" s="47"/>
+      <c r="AU47" s="47"/>
+      <c r="AV47" s="47"/>
+      <c r="AW47" s="47"/>
     </row>
     <row r="48" spans="2:54">
       <c r="B48" s="7"/>
-      <c r="C48" s="77" t="s">
+      <c r="C48" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="D48" s="77"/>
-      <c r="E48" s="77"/>
-      <c r="F48" s="77"/>
-      <c r="G48" s="77"/>
-      <c r="H48" s="77"/>
-      <c r="I48" s="77"/>
-      <c r="J48" s="77"/>
-      <c r="K48" s="77"/>
-      <c r="L48" s="77"/>
-      <c r="M48" s="77"/>
-      <c r="N48" s="77"/>
-      <c r="O48" s="77"/>
-      <c r="P48" s="77"/>
-      <c r="Q48" s="77"/>
-      <c r="R48" s="77"/>
-      <c r="S48" s="77"/>
-      <c r="T48" s="77"/>
-      <c r="U48" s="77"/>
-      <c r="V48" s="77"/>
-      <c r="W48" s="77"/>
-      <c r="X48" s="77"/>
+      <c r="D48" s="42"/>
+      <c r="E48" s="42"/>
+      <c r="F48" s="42"/>
+      <c r="G48" s="42"/>
+      <c r="H48" s="42"/>
+      <c r="I48" s="42"/>
+      <c r="J48" s="42"/>
+      <c r="K48" s="42"/>
+      <c r="L48" s="42"/>
+      <c r="M48" s="42"/>
+      <c r="N48" s="42"/>
+      <c r="O48" s="42"/>
+      <c r="P48" s="42"/>
+      <c r="Q48" s="42"/>
+      <c r="R48" s="42"/>
+      <c r="S48" s="42"/>
+      <c r="T48" s="42"/>
+      <c r="U48" s="42"/>
+      <c r="V48" s="42"/>
+      <c r="W48" s="42"/>
+      <c r="X48" s="42"/>
       <c r="Y48" s="7"/>
-      <c r="Z48" s="77" t="s">
+      <c r="Z48" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="AA48" s="77"/>
-      <c r="AB48" s="77"/>
-      <c r="AC48" s="77"/>
-      <c r="AD48" s="77"/>
-      <c r="AE48" s="77"/>
-      <c r="AF48" s="77"/>
-      <c r="AG48" s="77"/>
-      <c r="AH48" s="77"/>
-      <c r="AI48" s="77"/>
-      <c r="AJ48" s="77"/>
-      <c r="AK48" s="77"/>
-      <c r="AL48" s="77"/>
-      <c r="AM48" s="77"/>
-      <c r="AN48" s="77"/>
-      <c r="AO48" s="77"/>
-      <c r="AP48" s="77"/>
-      <c r="AQ48" s="77"/>
-      <c r="AR48" s="77"/>
-      <c r="AS48" s="77"/>
-      <c r="AT48" s="77"/>
-      <c r="AU48" s="77"/>
-      <c r="AV48" s="77"/>
-      <c r="AW48" s="77"/>
+      <c r="AA48" s="42"/>
+      <c r="AB48" s="42"/>
+      <c r="AC48" s="42"/>
+      <c r="AD48" s="42"/>
+      <c r="AE48" s="42"/>
+      <c r="AF48" s="42"/>
+      <c r="AG48" s="42"/>
+      <c r="AH48" s="42"/>
+      <c r="AI48" s="42"/>
+      <c r="AJ48" s="42"/>
+      <c r="AK48" s="42"/>
+      <c r="AL48" s="42"/>
+      <c r="AM48" s="42"/>
+      <c r="AN48" s="42"/>
+      <c r="AO48" s="42"/>
+      <c r="AP48" s="42"/>
+      <c r="AQ48" s="42"/>
+      <c r="AR48" s="42"/>
+      <c r="AS48" s="42"/>
+      <c r="AT48" s="42"/>
+      <c r="AU48" s="42"/>
+      <c r="AV48" s="42"/>
+      <c r="AW48" s="42"/>
       <c r="AX48" s="21"/>
       <c r="AY48" s="21"/>
       <c r="AZ48" s="21"/>
@@ -4514,6 +4514,149 @@
     </row>
   </sheetData>
   <mergeCells count="167">
+    <mergeCell ref="AN2:AV3"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="G6:AF6"/>
+    <mergeCell ref="AM6:AW6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="AM7:AW7"/>
+    <mergeCell ref="B10:AW11"/>
+    <mergeCell ref="N3:AM3"/>
+    <mergeCell ref="N4:AK4"/>
+    <mergeCell ref="AL4:AW5"/>
+    <mergeCell ref="B5:S5"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="F12:AF12"/>
+    <mergeCell ref="AG12:AK12"/>
+    <mergeCell ref="AL12:AQ12"/>
+    <mergeCell ref="AR12:AW12"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="AN8:AW8"/>
+    <mergeCell ref="B9:O9"/>
+    <mergeCell ref="P9:AF9"/>
+    <mergeCell ref="AH9:AW9"/>
+    <mergeCell ref="G7:AF8"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="F13:AF13"/>
+    <mergeCell ref="AG13:AK13"/>
+    <mergeCell ref="AL13:AQ13"/>
+    <mergeCell ref="AR13:AW13"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="F14:AF14"/>
+    <mergeCell ref="AG14:AI14"/>
+    <mergeCell ref="AJ14:AK14"/>
+    <mergeCell ref="AL14:AQ14"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="F16:AF16"/>
+    <mergeCell ref="AG16:AI16"/>
+    <mergeCell ref="AJ16:AK16"/>
+    <mergeCell ref="AL16:AQ16"/>
+    <mergeCell ref="AR16:AW16"/>
+    <mergeCell ref="AR14:AW14"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="F15:AF15"/>
+    <mergeCell ref="AG15:AI15"/>
+    <mergeCell ref="AJ15:AK15"/>
+    <mergeCell ref="AL15:AQ15"/>
+    <mergeCell ref="AR15:AW15"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="F18:AF18"/>
+    <mergeCell ref="AG18:AI18"/>
+    <mergeCell ref="AJ18:AK18"/>
+    <mergeCell ref="AL18:AQ18"/>
+    <mergeCell ref="AR18:AW18"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="F17:AF17"/>
+    <mergeCell ref="AG17:AI17"/>
+    <mergeCell ref="AJ17:AK17"/>
+    <mergeCell ref="AL17:AQ17"/>
+    <mergeCell ref="AR17:AW17"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="F20:AF20"/>
+    <mergeCell ref="AG20:AI20"/>
+    <mergeCell ref="AJ20:AK20"/>
+    <mergeCell ref="AL20:AQ20"/>
+    <mergeCell ref="AR20:AW20"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="F19:AF19"/>
+    <mergeCell ref="AG19:AI19"/>
+    <mergeCell ref="AJ19:AK19"/>
+    <mergeCell ref="AL19:AQ19"/>
+    <mergeCell ref="AR19:AW19"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="F22:AF22"/>
+    <mergeCell ref="AG22:AI22"/>
+    <mergeCell ref="AJ22:AK22"/>
+    <mergeCell ref="AL22:AQ22"/>
+    <mergeCell ref="AR22:AW22"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="F21:AF21"/>
+    <mergeCell ref="AG21:AI21"/>
+    <mergeCell ref="AJ21:AK21"/>
+    <mergeCell ref="AL21:AQ21"/>
+    <mergeCell ref="AR21:AW21"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="F24:AF24"/>
+    <mergeCell ref="AG24:AI24"/>
+    <mergeCell ref="AJ24:AK24"/>
+    <mergeCell ref="AL24:AQ24"/>
+    <mergeCell ref="AR24:AW24"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="F23:AF23"/>
+    <mergeCell ref="AG23:AI23"/>
+    <mergeCell ref="AJ23:AK23"/>
+    <mergeCell ref="AL23:AQ23"/>
+    <mergeCell ref="AR23:AW23"/>
+    <mergeCell ref="AR26:AW26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="F27:AF27"/>
+    <mergeCell ref="AG27:AI27"/>
+    <mergeCell ref="AJ27:AK27"/>
+    <mergeCell ref="AL27:AQ27"/>
+    <mergeCell ref="AR27:AW27"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="F26:AF26"/>
+    <mergeCell ref="AG26:AI26"/>
+    <mergeCell ref="AJ26:AK26"/>
+    <mergeCell ref="AL26:AQ26"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:AF29"/>
+    <mergeCell ref="AG29:AI29"/>
+    <mergeCell ref="AJ29:AK29"/>
+    <mergeCell ref="AL29:AQ29"/>
+    <mergeCell ref="AR29:AW29"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="F28:AF28"/>
+    <mergeCell ref="AG28:AI28"/>
+    <mergeCell ref="AJ28:AK28"/>
+    <mergeCell ref="AL28:AQ28"/>
+    <mergeCell ref="AR28:AW28"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="F31:AF31"/>
+    <mergeCell ref="AG31:AI31"/>
+    <mergeCell ref="AJ31:AK31"/>
+    <mergeCell ref="AL31:AQ31"/>
+    <mergeCell ref="AR31:AW31"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="F30:AF30"/>
+    <mergeCell ref="AG30:AI30"/>
+    <mergeCell ref="AJ30:AK30"/>
+    <mergeCell ref="AL30:AQ30"/>
+    <mergeCell ref="AR30:AW30"/>
+    <mergeCell ref="AR34:AW34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="F35:AF35"/>
+    <mergeCell ref="AG35:AI35"/>
+    <mergeCell ref="AJ35:AK35"/>
+    <mergeCell ref="AL35:AQ35"/>
+    <mergeCell ref="AR35:AW35"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="F34:AF34"/>
+    <mergeCell ref="AG34:AI34"/>
+    <mergeCell ref="AJ34:AK34"/>
     <mergeCell ref="N1:AV1"/>
     <mergeCell ref="C48:X48"/>
     <mergeCell ref="Z48:AW48"/>
@@ -4538,149 +4681,6 @@
     <mergeCell ref="AG38:AQ38"/>
     <mergeCell ref="AR38:AW38"/>
     <mergeCell ref="AL34:AQ34"/>
-    <mergeCell ref="AR34:AW34"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="F35:AF35"/>
-    <mergeCell ref="AG35:AI35"/>
-    <mergeCell ref="AJ35:AK35"/>
-    <mergeCell ref="AL35:AQ35"/>
-    <mergeCell ref="AR35:AW35"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="F34:AF34"/>
-    <mergeCell ref="AG34:AI34"/>
-    <mergeCell ref="AJ34:AK34"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="F31:AF31"/>
-    <mergeCell ref="AG31:AI31"/>
-    <mergeCell ref="AJ31:AK31"/>
-    <mergeCell ref="AL31:AQ31"/>
-    <mergeCell ref="AR31:AW31"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="F30:AF30"/>
-    <mergeCell ref="AG30:AI30"/>
-    <mergeCell ref="AJ30:AK30"/>
-    <mergeCell ref="AL30:AQ30"/>
-    <mergeCell ref="AR30:AW30"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:AF29"/>
-    <mergeCell ref="AG29:AI29"/>
-    <mergeCell ref="AJ29:AK29"/>
-    <mergeCell ref="AL29:AQ29"/>
-    <mergeCell ref="AR29:AW29"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="F28:AF28"/>
-    <mergeCell ref="AG28:AI28"/>
-    <mergeCell ref="AJ28:AK28"/>
-    <mergeCell ref="AL28:AQ28"/>
-    <mergeCell ref="AR28:AW28"/>
-    <mergeCell ref="AR26:AW26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="F27:AF27"/>
-    <mergeCell ref="AG27:AI27"/>
-    <mergeCell ref="AJ27:AK27"/>
-    <mergeCell ref="AL27:AQ27"/>
-    <mergeCell ref="AR27:AW27"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="F26:AF26"/>
-    <mergeCell ref="AG26:AI26"/>
-    <mergeCell ref="AJ26:AK26"/>
-    <mergeCell ref="AL26:AQ26"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="F24:AF24"/>
-    <mergeCell ref="AG24:AI24"/>
-    <mergeCell ref="AJ24:AK24"/>
-    <mergeCell ref="AL24:AQ24"/>
-    <mergeCell ref="AR24:AW24"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="F23:AF23"/>
-    <mergeCell ref="AG23:AI23"/>
-    <mergeCell ref="AJ23:AK23"/>
-    <mergeCell ref="AL23:AQ23"/>
-    <mergeCell ref="AR23:AW23"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="F22:AF22"/>
-    <mergeCell ref="AG22:AI22"/>
-    <mergeCell ref="AJ22:AK22"/>
-    <mergeCell ref="AL22:AQ22"/>
-    <mergeCell ref="AR22:AW22"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="F21:AF21"/>
-    <mergeCell ref="AG21:AI21"/>
-    <mergeCell ref="AJ21:AK21"/>
-    <mergeCell ref="AL21:AQ21"/>
-    <mergeCell ref="AR21:AW21"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="F20:AF20"/>
-    <mergeCell ref="AG20:AI20"/>
-    <mergeCell ref="AJ20:AK20"/>
-    <mergeCell ref="AL20:AQ20"/>
-    <mergeCell ref="AR20:AW20"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="F19:AF19"/>
-    <mergeCell ref="AG19:AI19"/>
-    <mergeCell ref="AJ19:AK19"/>
-    <mergeCell ref="AL19:AQ19"/>
-    <mergeCell ref="AR19:AW19"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="F18:AF18"/>
-    <mergeCell ref="AG18:AI18"/>
-    <mergeCell ref="AJ18:AK18"/>
-    <mergeCell ref="AL18:AQ18"/>
-    <mergeCell ref="AR18:AW18"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="F17:AF17"/>
-    <mergeCell ref="AG17:AI17"/>
-    <mergeCell ref="AJ17:AK17"/>
-    <mergeCell ref="AL17:AQ17"/>
-    <mergeCell ref="AR17:AW17"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="F16:AF16"/>
-    <mergeCell ref="AG16:AI16"/>
-    <mergeCell ref="AJ16:AK16"/>
-    <mergeCell ref="AL16:AQ16"/>
-    <mergeCell ref="AR16:AW16"/>
-    <mergeCell ref="AR14:AW14"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="F15:AF15"/>
-    <mergeCell ref="AG15:AI15"/>
-    <mergeCell ref="AJ15:AK15"/>
-    <mergeCell ref="AL15:AQ15"/>
-    <mergeCell ref="AR15:AW15"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="F13:AF13"/>
-    <mergeCell ref="AG13:AK13"/>
-    <mergeCell ref="AL13:AQ13"/>
-    <mergeCell ref="AR13:AW13"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="F14:AF14"/>
-    <mergeCell ref="AG14:AI14"/>
-    <mergeCell ref="AJ14:AK14"/>
-    <mergeCell ref="AL14:AQ14"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="F12:AF12"/>
-    <mergeCell ref="AG12:AK12"/>
-    <mergeCell ref="AL12:AQ12"/>
-    <mergeCell ref="AR12:AW12"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="AN8:AW8"/>
-    <mergeCell ref="B9:O9"/>
-    <mergeCell ref="P9:AF9"/>
-    <mergeCell ref="AH9:AW9"/>
-    <mergeCell ref="G7:AF8"/>
-    <mergeCell ref="AN2:AV3"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="G6:AF6"/>
-    <mergeCell ref="AM6:AW6"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="AM7:AW7"/>
-    <mergeCell ref="B10:AW11"/>
-    <mergeCell ref="N3:AM3"/>
-    <mergeCell ref="N4:AK4"/>
-    <mergeCell ref="AL4:AW5"/>
-    <mergeCell ref="B5:S5"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.27559055118110237" top="0.39370078740157483" bottom="0" header="0.19685039370078741" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" scale="95" orientation="portrait" r:id="rId1"/>

--- a/dist/templates/quotation.xlsx
+++ b/dist/templates/quotation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nakorn/github/Datacom_Status_Tracking_FE/public/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B943986-E136-004C-816C-0228D7F45DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0245C876-8B3F-E44D-A382-506C8F90F65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -668,7 +668,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -767,129 +767,123 @@
     <xf numFmtId="166" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="19" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="19" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -949,6 +943,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2058,160 +2055,160 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:49" ht="27.75" customHeight="1">
-      <c r="N1" s="41" t="s">
+      <c r="N1" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
-      <c r="W1" s="41"/>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="41"/>
-      <c r="AA1" s="41"/>
-      <c r="AB1" s="41"/>
-      <c r="AC1" s="41"/>
-      <c r="AD1" s="41"/>
-      <c r="AE1" s="41"/>
-      <c r="AF1" s="41"/>
-      <c r="AG1" s="41"/>
-      <c r="AH1" s="41"/>
-      <c r="AI1" s="41"/>
-      <c r="AJ1" s="41"/>
-      <c r="AK1" s="41"/>
-      <c r="AL1" s="41"/>
-      <c r="AM1" s="41"/>
-      <c r="AN1" s="41"/>
-      <c r="AO1" s="41"/>
-      <c r="AP1" s="41"/>
-      <c r="AQ1" s="41"/>
-      <c r="AR1" s="41"/>
-      <c r="AS1" s="41"/>
-      <c r="AT1" s="41"/>
-      <c r="AU1" s="41"/>
-      <c r="AV1" s="41"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="39"/>
+      <c r="Y1" s="39"/>
+      <c r="Z1" s="39"/>
+      <c r="AA1" s="39"/>
+      <c r="AB1" s="39"/>
+      <c r="AC1" s="39"/>
+      <c r="AD1" s="39"/>
+      <c r="AE1" s="39"/>
+      <c r="AF1" s="39"/>
+      <c r="AG1" s="39"/>
+      <c r="AH1" s="39"/>
+      <c r="AI1" s="39"/>
+      <c r="AJ1" s="39"/>
+      <c r="AK1" s="39"/>
+      <c r="AL1" s="39"/>
+      <c r="AM1" s="39"/>
+      <c r="AN1" s="39"/>
+      <c r="AO1" s="39"/>
+      <c r="AP1" s="39"/>
+      <c r="AQ1" s="39"/>
+      <c r="AR1" s="39"/>
+      <c r="AS1" s="39"/>
+      <c r="AT1" s="39"/>
+      <c r="AU1" s="39"/>
+      <c r="AV1" s="39"/>
     </row>
     <row r="2" spans="2:49" ht="24" customHeight="1">
       <c r="N2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="AN2" s="91"/>
-      <c r="AO2" s="91"/>
-      <c r="AP2" s="91"/>
-      <c r="AQ2" s="91"/>
-      <c r="AR2" s="91"/>
-      <c r="AS2" s="91"/>
-      <c r="AT2" s="91"/>
-      <c r="AU2" s="91"/>
-      <c r="AV2" s="91"/>
+      <c r="AN2" s="89"/>
+      <c r="AO2" s="89"/>
+      <c r="AP2" s="89"/>
+      <c r="AQ2" s="89"/>
+      <c r="AR2" s="89"/>
+      <c r="AS2" s="89"/>
+      <c r="AT2" s="89"/>
+      <c r="AU2" s="89"/>
+      <c r="AV2" s="89"/>
     </row>
     <row r="3" spans="2:49" ht="21" customHeight="1">
-      <c r="N3" s="94" t="s">
+      <c r="N3" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="O3" s="94"/>
-      <c r="P3" s="94"/>
-      <c r="Q3" s="94"/>
-      <c r="R3" s="94"/>
-      <c r="S3" s="94"/>
-      <c r="T3" s="94"/>
-      <c r="U3" s="94"/>
-      <c r="V3" s="94"/>
-      <c r="W3" s="94"/>
-      <c r="X3" s="94"/>
-      <c r="Y3" s="94"/>
-      <c r="Z3" s="94"/>
-      <c r="AA3" s="94"/>
-      <c r="AB3" s="94"/>
-      <c r="AC3" s="94"/>
-      <c r="AD3" s="94"/>
-      <c r="AE3" s="94"/>
-      <c r="AF3" s="94"/>
-      <c r="AG3" s="94"/>
-      <c r="AH3" s="94"/>
-      <c r="AI3" s="94"/>
-      <c r="AJ3" s="94"/>
-      <c r="AK3" s="94"/>
-      <c r="AL3" s="94"/>
-      <c r="AM3" s="94"/>
-      <c r="AN3" s="91"/>
-      <c r="AO3" s="91"/>
-      <c r="AP3" s="91"/>
-      <c r="AQ3" s="91"/>
-      <c r="AR3" s="91"/>
-      <c r="AS3" s="91"/>
-      <c r="AT3" s="91"/>
-      <c r="AU3" s="91"/>
-      <c r="AV3" s="91"/>
+      <c r="O3" s="92"/>
+      <c r="P3" s="92"/>
+      <c r="Q3" s="92"/>
+      <c r="R3" s="92"/>
+      <c r="S3" s="92"/>
+      <c r="T3" s="92"/>
+      <c r="U3" s="92"/>
+      <c r="V3" s="92"/>
+      <c r="W3" s="92"/>
+      <c r="X3" s="92"/>
+      <c r="Y3" s="92"/>
+      <c r="Z3" s="92"/>
+      <c r="AA3" s="92"/>
+      <c r="AB3" s="92"/>
+      <c r="AC3" s="92"/>
+      <c r="AD3" s="92"/>
+      <c r="AE3" s="92"/>
+      <c r="AF3" s="92"/>
+      <c r="AG3" s="92"/>
+      <c r="AH3" s="92"/>
+      <c r="AI3" s="92"/>
+      <c r="AJ3" s="92"/>
+      <c r="AK3" s="92"/>
+      <c r="AL3" s="92"/>
+      <c r="AM3" s="92"/>
+      <c r="AN3" s="89"/>
+      <c r="AO3" s="89"/>
+      <c r="AP3" s="89"/>
+      <c r="AQ3" s="89"/>
+      <c r="AR3" s="89"/>
+      <c r="AS3" s="89"/>
+      <c r="AT3" s="89"/>
+      <c r="AU3" s="89"/>
+      <c r="AV3" s="89"/>
     </row>
     <row r="4" spans="2:49" ht="19.5" customHeight="1">
-      <c r="N4" s="94" t="s">
+      <c r="N4" s="92" t="s">
         <v>1</v>
       </c>
-      <c r="O4" s="94"/>
-      <c r="P4" s="94"/>
-      <c r="Q4" s="94"/>
-      <c r="R4" s="94"/>
-      <c r="S4" s="94"/>
-      <c r="T4" s="94"/>
-      <c r="U4" s="94"/>
-      <c r="V4" s="94"/>
-      <c r="W4" s="94"/>
-      <c r="X4" s="94"/>
-      <c r="Y4" s="94"/>
-      <c r="Z4" s="94"/>
-      <c r="AA4" s="94"/>
-      <c r="AB4" s="94"/>
-      <c r="AC4" s="94"/>
-      <c r="AD4" s="94"/>
-      <c r="AE4" s="94"/>
-      <c r="AF4" s="94"/>
-      <c r="AG4" s="94"/>
-      <c r="AH4" s="94"/>
-      <c r="AI4" s="94"/>
-      <c r="AJ4" s="94"/>
-      <c r="AK4" s="94"/>
-      <c r="AL4" s="95" t="s">
+      <c r="O4" s="92"/>
+      <c r="P4" s="92"/>
+      <c r="Q4" s="92"/>
+      <c r="R4" s="92"/>
+      <c r="S4" s="92"/>
+      <c r="T4" s="92"/>
+      <c r="U4" s="92"/>
+      <c r="V4" s="92"/>
+      <c r="W4" s="92"/>
+      <c r="X4" s="92"/>
+      <c r="Y4" s="92"/>
+      <c r="Z4" s="92"/>
+      <c r="AA4" s="92"/>
+      <c r="AB4" s="92"/>
+      <c r="AC4" s="92"/>
+      <c r="AD4" s="92"/>
+      <c r="AE4" s="92"/>
+      <c r="AF4" s="92"/>
+      <c r="AG4" s="92"/>
+      <c r="AH4" s="92"/>
+      <c r="AI4" s="92"/>
+      <c r="AJ4" s="92"/>
+      <c r="AK4" s="92"/>
+      <c r="AL4" s="93" t="s">
         <v>34</v>
       </c>
-      <c r="AM4" s="95"/>
-      <c r="AN4" s="95"/>
-      <c r="AO4" s="95"/>
-      <c r="AP4" s="95"/>
-      <c r="AQ4" s="95"/>
-      <c r="AR4" s="95"/>
-      <c r="AS4" s="95"/>
-      <c r="AT4" s="95"/>
-      <c r="AU4" s="95"/>
-      <c r="AV4" s="95"/>
-      <c r="AW4" s="95"/>
+      <c r="AM4" s="93"/>
+      <c r="AN4" s="93"/>
+      <c r="AO4" s="93"/>
+      <c r="AP4" s="93"/>
+      <c r="AQ4" s="93"/>
+      <c r="AR4" s="93"/>
+      <c r="AS4" s="93"/>
+      <c r="AT4" s="93"/>
+      <c r="AU4" s="93"/>
+      <c r="AV4" s="93"/>
+      <c r="AW4" s="93"/>
     </row>
     <row r="5" spans="2:49" s="4" customFormat="1" ht="23.25" customHeight="1">
-      <c r="B5" s="96" t="s">
+      <c r="B5" s="94" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="96"/>
-      <c r="D5" s="96"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="96"/>
-      <c r="G5" s="96"/>
-      <c r="H5" s="96"/>
-      <c r="I5" s="96"/>
-      <c r="J5" s="96"/>
-      <c r="K5" s="96"/>
-      <c r="L5" s="96"/>
-      <c r="M5" s="96"/>
-      <c r="N5" s="96"/>
-      <c r="O5" s="96"/>
-      <c r="P5" s="96"/>
-      <c r="Q5" s="96"/>
-      <c r="R5" s="96"/>
-      <c r="S5" s="96"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="94"/>
+      <c r="F5" s="94"/>
+      <c r="G5" s="94"/>
+      <c r="H5" s="94"/>
+      <c r="I5" s="94"/>
+      <c r="J5" s="94"/>
+      <c r="K5" s="94"/>
+      <c r="L5" s="94"/>
+      <c r="M5" s="94"/>
+      <c r="N5" s="94"/>
+      <c r="O5" s="94"/>
+      <c r="P5" s="94"/>
+      <c r="Q5" s="94"/>
+      <c r="R5" s="94"/>
+      <c r="S5" s="94"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
       <c r="V5" s="2"/>
@@ -2230,53 +2227,53 @@
       <c r="AI5" s="2"/>
       <c r="AJ5" s="2"/>
       <c r="AK5" s="2"/>
-      <c r="AL5" s="95"/>
-      <c r="AM5" s="95"/>
-      <c r="AN5" s="95"/>
-      <c r="AO5" s="95"/>
-      <c r="AP5" s="95"/>
-      <c r="AQ5" s="95"/>
-      <c r="AR5" s="95"/>
-      <c r="AS5" s="95"/>
-      <c r="AT5" s="95"/>
-      <c r="AU5" s="95"/>
-      <c r="AV5" s="95"/>
-      <c r="AW5" s="95"/>
+      <c r="AL5" s="93"/>
+      <c r="AM5" s="93"/>
+      <c r="AN5" s="93"/>
+      <c r="AO5" s="93"/>
+      <c r="AP5" s="93"/>
+      <c r="AQ5" s="93"/>
+      <c r="AR5" s="93"/>
+      <c r="AS5" s="93"/>
+      <c r="AT5" s="93"/>
+      <c r="AU5" s="93"/>
+      <c r="AV5" s="93"/>
+      <c r="AW5" s="93"/>
     </row>
     <row r="6" spans="2:49" s="4" customFormat="1" ht="23.5" customHeight="1">
-      <c r="B6" s="89" t="s">
+      <c r="B6" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="70"/>
-      <c r="P6" s="70"/>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="70"/>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="70"/>
-      <c r="W6" s="70"/>
-      <c r="X6" s="70"/>
-      <c r="Y6" s="70"/>
-      <c r="Z6" s="70"/>
-      <c r="AA6" s="70"/>
-      <c r="AB6" s="70"/>
-      <c r="AC6" s="70"/>
-      <c r="AD6" s="70"/>
-      <c r="AE6" s="70"/>
-      <c r="AF6" s="70"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="87"/>
+      <c r="E6" s="87"/>
+      <c r="F6" s="87"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
+      <c r="N6" s="68"/>
+      <c r="O6" s="68"/>
+      <c r="P6" s="68"/>
+      <c r="Q6" s="68"/>
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="68"/>
+      <c r="U6" s="68"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="68"/>
+      <c r="Y6" s="68"/>
+      <c r="Z6" s="68"/>
+      <c r="AA6" s="68"/>
+      <c r="AB6" s="68"/>
+      <c r="AC6" s="68"/>
+      <c r="AD6" s="68"/>
+      <c r="AE6" s="68"/>
+      <c r="AF6" s="68"/>
       <c r="AG6" s="6"/>
       <c r="AH6" s="25" t="s">
         <v>4</v>
@@ -2285,52 +2282,52 @@
       <c r="AJ6" s="23"/>
       <c r="AK6" s="23"/>
       <c r="AL6" s="23"/>
-      <c r="AM6" s="48"/>
-      <c r="AN6" s="48"/>
-      <c r="AO6" s="48"/>
-      <c r="AP6" s="48"/>
-      <c r="AQ6" s="48"/>
-      <c r="AR6" s="48"/>
-      <c r="AS6" s="48"/>
-      <c r="AT6" s="48"/>
-      <c r="AU6" s="48"/>
-      <c r="AV6" s="48"/>
-      <c r="AW6" s="48"/>
+      <c r="AM6" s="46"/>
+      <c r="AN6" s="46"/>
+      <c r="AO6" s="46"/>
+      <c r="AP6" s="46"/>
+      <c r="AQ6" s="46"/>
+      <c r="AR6" s="46"/>
+      <c r="AS6" s="46"/>
+      <c r="AT6" s="46"/>
+      <c r="AU6" s="46"/>
+      <c r="AV6" s="46"/>
+      <c r="AW6" s="46"/>
     </row>
     <row r="7" spans="2:49" s="4" customFormat="1" ht="21" customHeight="1">
-      <c r="B7" s="89" t="s">
+      <c r="B7" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="89"/>
-      <c r="D7" s="89"/>
-      <c r="E7" s="89"/>
-      <c r="F7" s="89"/>
-      <c r="G7" s="90"/>
-      <c r="H7" s="90"/>
-      <c r="I7" s="90"/>
-      <c r="J7" s="90"/>
-      <c r="K7" s="90"/>
-      <c r="L7" s="90"/>
-      <c r="M7" s="90"/>
-      <c r="N7" s="90"/>
-      <c r="O7" s="90"/>
-      <c r="P7" s="90"/>
-      <c r="Q7" s="90"/>
-      <c r="R7" s="90"/>
-      <c r="S7" s="90"/>
-      <c r="T7" s="90"/>
-      <c r="U7" s="90"/>
-      <c r="V7" s="90"/>
-      <c r="W7" s="90"/>
-      <c r="X7" s="90"/>
-      <c r="Y7" s="90"/>
-      <c r="Z7" s="90"/>
-      <c r="AA7" s="90"/>
-      <c r="AB7" s="90"/>
-      <c r="AC7" s="90"/>
-      <c r="AD7" s="90"/>
-      <c r="AE7" s="90"/>
-      <c r="AF7" s="90"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="87"/>
+      <c r="G7" s="88"/>
+      <c r="H7" s="88"/>
+      <c r="I7" s="88"/>
+      <c r="J7" s="88"/>
+      <c r="K7" s="88"/>
+      <c r="L7" s="88"/>
+      <c r="M7" s="88"/>
+      <c r="N7" s="88"/>
+      <c r="O7" s="88"/>
+      <c r="P7" s="88"/>
+      <c r="Q7" s="88"/>
+      <c r="R7" s="88"/>
+      <c r="S7" s="88"/>
+      <c r="T7" s="88"/>
+      <c r="U7" s="88"/>
+      <c r="V7" s="88"/>
+      <c r="W7" s="88"/>
+      <c r="X7" s="88"/>
+      <c r="Y7" s="88"/>
+      <c r="Z7" s="88"/>
+      <c r="AA7" s="88"/>
+      <c r="AB7" s="88"/>
+      <c r="AC7" s="88"/>
+      <c r="AD7" s="88"/>
+      <c r="AE7" s="88"/>
+      <c r="AF7" s="88"/>
       <c r="AG7" s="6"/>
       <c r="AH7" s="26" t="s">
         <v>5</v>
@@ -2339,50 +2336,50 @@
       <c r="AJ7" s="24"/>
       <c r="AK7" s="24"/>
       <c r="AL7" s="24"/>
-      <c r="AM7" s="61"/>
-      <c r="AN7" s="61"/>
-      <c r="AO7" s="61"/>
-      <c r="AP7" s="61"/>
-      <c r="AQ7" s="61"/>
-      <c r="AR7" s="61"/>
-      <c r="AS7" s="61"/>
-      <c r="AT7" s="61"/>
-      <c r="AU7" s="61"/>
-      <c r="AV7" s="61"/>
-      <c r="AW7" s="61"/>
+      <c r="AM7" s="59"/>
+      <c r="AN7" s="59"/>
+      <c r="AO7" s="59"/>
+      <c r="AP7" s="59"/>
+      <c r="AQ7" s="59"/>
+      <c r="AR7" s="59"/>
+      <c r="AS7" s="59"/>
+      <c r="AT7" s="59"/>
+      <c r="AU7" s="59"/>
+      <c r="AV7" s="59"/>
+      <c r="AW7" s="59"/>
     </row>
     <row r="8" spans="2:49" s="4" customFormat="1" ht="21" customHeight="1">
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="90"/>
-      <c r="H8" s="90"/>
-      <c r="I8" s="90"/>
-      <c r="J8" s="90"/>
-      <c r="K8" s="90"/>
-      <c r="L8" s="90"/>
-      <c r="M8" s="90"/>
-      <c r="N8" s="90"/>
-      <c r="O8" s="90"/>
-      <c r="P8" s="90"/>
-      <c r="Q8" s="90"/>
-      <c r="R8" s="90"/>
-      <c r="S8" s="90"/>
-      <c r="T8" s="90"/>
-      <c r="U8" s="90"/>
-      <c r="V8" s="90"/>
-      <c r="W8" s="90"/>
-      <c r="X8" s="90"/>
-      <c r="Y8" s="90"/>
-      <c r="Z8" s="90"/>
-      <c r="AA8" s="90"/>
-      <c r="AB8" s="90"/>
-      <c r="AC8" s="90"/>
-      <c r="AD8" s="90"/>
-      <c r="AE8" s="90"/>
-      <c r="AF8" s="90"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="88"/>
+      <c r="I8" s="88"/>
+      <c r="J8" s="88"/>
+      <c r="K8" s="88"/>
+      <c r="L8" s="88"/>
+      <c r="M8" s="88"/>
+      <c r="N8" s="88"/>
+      <c r="O8" s="88"/>
+      <c r="P8" s="88"/>
+      <c r="Q8" s="88"/>
+      <c r="R8" s="88"/>
+      <c r="S8" s="88"/>
+      <c r="T8" s="88"/>
+      <c r="U8" s="88"/>
+      <c r="V8" s="88"/>
+      <c r="W8" s="88"/>
+      <c r="X8" s="88"/>
+      <c r="Y8" s="88"/>
+      <c r="Z8" s="88"/>
+      <c r="AA8" s="88"/>
+      <c r="AB8" s="88"/>
+      <c r="AC8" s="88"/>
+      <c r="AD8" s="88"/>
+      <c r="AE8" s="88"/>
+      <c r="AF8" s="88"/>
       <c r="AG8" s="6"/>
       <c r="AH8" s="28" t="s">
         <v>30</v>
@@ -2392,913 +2389,913 @@
       <c r="AK8" s="27"/>
       <c r="AL8" s="27"/>
       <c r="AM8" s="27"/>
-      <c r="AN8" s="86"/>
-      <c r="AO8" s="86"/>
-      <c r="AP8" s="86"/>
-      <c r="AQ8" s="86"/>
-      <c r="AR8" s="86"/>
-      <c r="AS8" s="86"/>
-      <c r="AT8" s="86"/>
-      <c r="AU8" s="86"/>
-      <c r="AV8" s="86"/>
-      <c r="AW8" s="86"/>
+      <c r="AN8" s="84"/>
+      <c r="AO8" s="84"/>
+      <c r="AP8" s="84"/>
+      <c r="AQ8" s="84"/>
+      <c r="AR8" s="84"/>
+      <c r="AS8" s="84"/>
+      <c r="AT8" s="84"/>
+      <c r="AU8" s="84"/>
+      <c r="AV8" s="84"/>
+      <c r="AW8" s="84"/>
     </row>
     <row r="9" spans="2:49" s="4" customFormat="1" ht="21" customHeight="1">
-      <c r="B9" s="87" t="s">
+      <c r="B9" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="87"/>
-      <c r="D9" s="87"/>
-      <c r="E9" s="87"/>
-      <c r="F9" s="87"/>
-      <c r="G9" s="87"/>
-      <c r="H9" s="87"/>
-      <c r="I9" s="87"/>
-      <c r="J9" s="87"/>
-      <c r="K9" s="87"/>
-      <c r="L9" s="87"/>
-      <c r="M9" s="87"/>
-      <c r="N9" s="87"/>
-      <c r="O9" s="87"/>
-      <c r="P9" s="88"/>
-      <c r="Q9" s="88"/>
-      <c r="R9" s="88"/>
-      <c r="S9" s="88"/>
-      <c r="T9" s="88"/>
-      <c r="U9" s="88"/>
-      <c r="V9" s="88"/>
-      <c r="W9" s="88"/>
-      <c r="X9" s="88"/>
-      <c r="Y9" s="88"/>
-      <c r="Z9" s="88"/>
-      <c r="AA9" s="88"/>
-      <c r="AB9" s="88"/>
-      <c r="AC9" s="88"/>
-      <c r="AD9" s="88"/>
-      <c r="AE9" s="88"/>
-      <c r="AF9" s="88"/>
+      <c r="C9" s="85"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="85"/>
+      <c r="F9" s="85"/>
+      <c r="G9" s="85"/>
+      <c r="H9" s="85"/>
+      <c r="I9" s="85"/>
+      <c r="J9" s="85"/>
+      <c r="K9" s="85"/>
+      <c r="L9" s="85"/>
+      <c r="M9" s="85"/>
+      <c r="N9" s="85"/>
+      <c r="O9" s="85"/>
+      <c r="P9" s="86"/>
+      <c r="Q9" s="86"/>
+      <c r="R9" s="86"/>
+      <c r="S9" s="86"/>
+      <c r="T9" s="86"/>
+      <c r="U9" s="86"/>
+      <c r="V9" s="86"/>
+      <c r="W9" s="86"/>
+      <c r="X9" s="86"/>
+      <c r="Y9" s="86"/>
+      <c r="Z9" s="86"/>
+      <c r="AA9" s="86"/>
+      <c r="AB9" s="86"/>
+      <c r="AC9" s="86"/>
+      <c r="AD9" s="86"/>
+      <c r="AE9" s="86"/>
+      <c r="AF9" s="86"/>
       <c r="AG9" s="6"/>
-      <c r="AH9" s="89" t="s">
+      <c r="AH9" s="87" t="s">
         <v>31</v>
       </c>
-      <c r="AI9" s="89"/>
-      <c r="AJ9" s="89"/>
-      <c r="AK9" s="89"/>
-      <c r="AL9" s="89"/>
-      <c r="AM9" s="89"/>
-      <c r="AN9" s="89"/>
-      <c r="AO9" s="89"/>
-      <c r="AP9" s="89"/>
-      <c r="AQ9" s="89"/>
-      <c r="AR9" s="89"/>
-      <c r="AS9" s="89"/>
-      <c r="AT9" s="89"/>
-      <c r="AU9" s="89"/>
-      <c r="AV9" s="89"/>
-      <c r="AW9" s="89"/>
+      <c r="AI9" s="87"/>
+      <c r="AJ9" s="87"/>
+      <c r="AK9" s="87"/>
+      <c r="AL9" s="87"/>
+      <c r="AM9" s="87"/>
+      <c r="AN9" s="87"/>
+      <c r="AO9" s="87"/>
+      <c r="AP9" s="87"/>
+      <c r="AQ9" s="87"/>
+      <c r="AR9" s="87"/>
+      <c r="AS9" s="87"/>
+      <c r="AT9" s="87"/>
+      <c r="AU9" s="87"/>
+      <c r="AV9" s="87"/>
+      <c r="AW9" s="87"/>
     </row>
     <row r="10" spans="2:49" s="4" customFormat="1" ht="13.25" customHeight="1">
-      <c r="B10" s="92" t="s">
+      <c r="B10" s="90" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="92"/>
-      <c r="D10" s="92"/>
-      <c r="E10" s="92"/>
-      <c r="F10" s="92"/>
-      <c r="G10" s="92"/>
-      <c r="H10" s="92"/>
-      <c r="I10" s="92"/>
-      <c r="J10" s="92"/>
-      <c r="K10" s="92"/>
-      <c r="L10" s="92"/>
-      <c r="M10" s="92"/>
-      <c r="N10" s="92"/>
-      <c r="O10" s="92"/>
-      <c r="P10" s="92"/>
-      <c r="Q10" s="92"/>
-      <c r="R10" s="92"/>
-      <c r="S10" s="92"/>
-      <c r="T10" s="92"/>
-      <c r="U10" s="92"/>
-      <c r="V10" s="92"/>
-      <c r="W10" s="92"/>
-      <c r="X10" s="92"/>
-      <c r="Y10" s="92"/>
-      <c r="Z10" s="92"/>
-      <c r="AA10" s="92"/>
-      <c r="AB10" s="92"/>
-      <c r="AC10" s="92"/>
-      <c r="AD10" s="92"/>
-      <c r="AE10" s="92"/>
-      <c r="AF10" s="92"/>
-      <c r="AG10" s="92"/>
-      <c r="AH10" s="92"/>
-      <c r="AI10" s="92"/>
-      <c r="AJ10" s="92"/>
-      <c r="AK10" s="92"/>
-      <c r="AL10" s="92"/>
-      <c r="AM10" s="92"/>
-      <c r="AN10" s="92"/>
-      <c r="AO10" s="92"/>
-      <c r="AP10" s="92"/>
-      <c r="AQ10" s="92"/>
-      <c r="AR10" s="92"/>
-      <c r="AS10" s="92"/>
-      <c r="AT10" s="92"/>
-      <c r="AU10" s="92"/>
-      <c r="AV10" s="92"/>
-      <c r="AW10" s="92"/>
+      <c r="C10" s="90"/>
+      <c r="D10" s="90"/>
+      <c r="E10" s="90"/>
+      <c r="F10" s="90"/>
+      <c r="G10" s="90"/>
+      <c r="H10" s="90"/>
+      <c r="I10" s="90"/>
+      <c r="J10" s="90"/>
+      <c r="K10" s="90"/>
+      <c r="L10" s="90"/>
+      <c r="M10" s="90"/>
+      <c r="N10" s="90"/>
+      <c r="O10" s="90"/>
+      <c r="P10" s="90"/>
+      <c r="Q10" s="90"/>
+      <c r="R10" s="90"/>
+      <c r="S10" s="90"/>
+      <c r="T10" s="90"/>
+      <c r="U10" s="90"/>
+      <c r="V10" s="90"/>
+      <c r="W10" s="90"/>
+      <c r="X10" s="90"/>
+      <c r="Y10" s="90"/>
+      <c r="Z10" s="90"/>
+      <c r="AA10" s="90"/>
+      <c r="AB10" s="90"/>
+      <c r="AC10" s="90"/>
+      <c r="AD10" s="90"/>
+      <c r="AE10" s="90"/>
+      <c r="AF10" s="90"/>
+      <c r="AG10" s="90"/>
+      <c r="AH10" s="90"/>
+      <c r="AI10" s="90"/>
+      <c r="AJ10" s="90"/>
+      <c r="AK10" s="90"/>
+      <c r="AL10" s="90"/>
+      <c r="AM10" s="90"/>
+      <c r="AN10" s="90"/>
+      <c r="AO10" s="90"/>
+      <c r="AP10" s="90"/>
+      <c r="AQ10" s="90"/>
+      <c r="AR10" s="90"/>
+      <c r="AS10" s="90"/>
+      <c r="AT10" s="90"/>
+      <c r="AU10" s="90"/>
+      <c r="AV10" s="90"/>
+      <c r="AW10" s="90"/>
     </row>
     <row r="11" spans="2:49" s="4" customFormat="1" ht="13.25" customHeight="1" thickBot="1">
-      <c r="B11" s="93"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="93"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="93"/>
-      <c r="G11" s="93"/>
-      <c r="H11" s="93"/>
-      <c r="I11" s="93"/>
-      <c r="J11" s="93"/>
-      <c r="K11" s="93"/>
-      <c r="L11" s="93"/>
-      <c r="M11" s="93"/>
-      <c r="N11" s="93"/>
-      <c r="O11" s="93"/>
-      <c r="P11" s="93"/>
-      <c r="Q11" s="93"/>
-      <c r="R11" s="93"/>
-      <c r="S11" s="93"/>
-      <c r="T11" s="93"/>
-      <c r="U11" s="93"/>
-      <c r="V11" s="93"/>
-      <c r="W11" s="93"/>
-      <c r="X11" s="93"/>
-      <c r="Y11" s="93"/>
-      <c r="Z11" s="93"/>
-      <c r="AA11" s="93"/>
-      <c r="AB11" s="93"/>
-      <c r="AC11" s="93"/>
-      <c r="AD11" s="93"/>
-      <c r="AE11" s="93"/>
-      <c r="AF11" s="93"/>
-      <c r="AG11" s="93"/>
-      <c r="AH11" s="93"/>
-      <c r="AI11" s="93"/>
-      <c r="AJ11" s="93"/>
-      <c r="AK11" s="93"/>
-      <c r="AL11" s="93"/>
-      <c r="AM11" s="93"/>
-      <c r="AN11" s="93"/>
-      <c r="AO11" s="93"/>
-      <c r="AP11" s="93"/>
-      <c r="AQ11" s="93"/>
-      <c r="AR11" s="93"/>
-      <c r="AS11" s="93"/>
-      <c r="AT11" s="93"/>
-      <c r="AU11" s="93"/>
-      <c r="AV11" s="93"/>
-      <c r="AW11" s="93"/>
+      <c r="B11" s="91"/>
+      <c r="C11" s="91"/>
+      <c r="D11" s="91"/>
+      <c r="E11" s="91"/>
+      <c r="F11" s="91"/>
+      <c r="G11" s="91"/>
+      <c r="H11" s="91"/>
+      <c r="I11" s="91"/>
+      <c r="J11" s="91"/>
+      <c r="K11" s="91"/>
+      <c r="L11" s="91"/>
+      <c r="M11" s="91"/>
+      <c r="N11" s="91"/>
+      <c r="O11" s="91"/>
+      <c r="P11" s="91"/>
+      <c r="Q11" s="91"/>
+      <c r="R11" s="91"/>
+      <c r="S11" s="91"/>
+      <c r="T11" s="91"/>
+      <c r="U11" s="91"/>
+      <c r="V11" s="91"/>
+      <c r="W11" s="91"/>
+      <c r="X11" s="91"/>
+      <c r="Y11" s="91"/>
+      <c r="Z11" s="91"/>
+      <c r="AA11" s="91"/>
+      <c r="AB11" s="91"/>
+      <c r="AC11" s="91"/>
+      <c r="AD11" s="91"/>
+      <c r="AE11" s="91"/>
+      <c r="AF11" s="91"/>
+      <c r="AG11" s="91"/>
+      <c r="AH11" s="91"/>
+      <c r="AI11" s="91"/>
+      <c r="AJ11" s="91"/>
+      <c r="AK11" s="91"/>
+      <c r="AL11" s="91"/>
+      <c r="AM11" s="91"/>
+      <c r="AN11" s="91"/>
+      <c r="AO11" s="91"/>
+      <c r="AP11" s="91"/>
+      <c r="AQ11" s="91"/>
+      <c r="AR11" s="91"/>
+      <c r="AS11" s="91"/>
+      <c r="AT11" s="91"/>
+      <c r="AU11" s="91"/>
+      <c r="AV11" s="91"/>
+      <c r="AW11" s="91"/>
     </row>
     <row r="12" spans="2:49" s="5" customFormat="1" ht="21" customHeight="1" thickTop="1">
-      <c r="B12" s="83" t="s">
+      <c r="B12" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="84"/>
-      <c r="D12" s="84"/>
-      <c r="E12" s="85"/>
-      <c r="F12" s="83" t="s">
+      <c r="C12" s="82"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="81" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="84"/>
-      <c r="H12" s="84"/>
-      <c r="I12" s="84"/>
-      <c r="J12" s="84"/>
-      <c r="K12" s="84"/>
-      <c r="L12" s="84"/>
-      <c r="M12" s="84"/>
-      <c r="N12" s="84"/>
-      <c r="O12" s="84"/>
-      <c r="P12" s="84"/>
-      <c r="Q12" s="84"/>
-      <c r="R12" s="84"/>
-      <c r="S12" s="84"/>
-      <c r="T12" s="84"/>
-      <c r="U12" s="84"/>
-      <c r="V12" s="84"/>
-      <c r="W12" s="84"/>
-      <c r="X12" s="84"/>
-      <c r="Y12" s="84"/>
-      <c r="Z12" s="84"/>
-      <c r="AA12" s="84"/>
-      <c r="AB12" s="84"/>
-      <c r="AC12" s="84"/>
-      <c r="AD12" s="84"/>
-      <c r="AE12" s="84"/>
-      <c r="AF12" s="85"/>
-      <c r="AG12" s="83" t="s">
+      <c r="G12" s="82"/>
+      <c r="H12" s="82"/>
+      <c r="I12" s="82"/>
+      <c r="J12" s="82"/>
+      <c r="K12" s="82"/>
+      <c r="L12" s="82"/>
+      <c r="M12" s="82"/>
+      <c r="N12" s="82"/>
+      <c r="O12" s="82"/>
+      <c r="P12" s="82"/>
+      <c r="Q12" s="82"/>
+      <c r="R12" s="82"/>
+      <c r="S12" s="82"/>
+      <c r="T12" s="82"/>
+      <c r="U12" s="82"/>
+      <c r="V12" s="82"/>
+      <c r="W12" s="82"/>
+      <c r="X12" s="82"/>
+      <c r="Y12" s="82"/>
+      <c r="Z12" s="82"/>
+      <c r="AA12" s="82"/>
+      <c r="AB12" s="82"/>
+      <c r="AC12" s="82"/>
+      <c r="AD12" s="82"/>
+      <c r="AE12" s="82"/>
+      <c r="AF12" s="83"/>
+      <c r="AG12" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="AH12" s="84"/>
-      <c r="AI12" s="84"/>
-      <c r="AJ12" s="84"/>
-      <c r="AK12" s="85"/>
-      <c r="AL12" s="83" t="s">
+      <c r="AH12" s="82"/>
+      <c r="AI12" s="82"/>
+      <c r="AJ12" s="82"/>
+      <c r="AK12" s="83"/>
+      <c r="AL12" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="AM12" s="84"/>
-      <c r="AN12" s="84"/>
-      <c r="AO12" s="84"/>
-      <c r="AP12" s="84"/>
-      <c r="AQ12" s="85"/>
-      <c r="AR12" s="83" t="s">
+      <c r="AM12" s="82"/>
+      <c r="AN12" s="82"/>
+      <c r="AO12" s="82"/>
+      <c r="AP12" s="82"/>
+      <c r="AQ12" s="83"/>
+      <c r="AR12" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="AS12" s="84"/>
-      <c r="AT12" s="84"/>
-      <c r="AU12" s="84"/>
-      <c r="AV12" s="84"/>
-      <c r="AW12" s="85"/>
+      <c r="AS12" s="82"/>
+      <c r="AT12" s="82"/>
+      <c r="AU12" s="82"/>
+      <c r="AV12" s="82"/>
+      <c r="AW12" s="83"/>
     </row>
     <row r="13" spans="2:49" s="4" customFormat="1" ht="17" customHeight="1" thickBot="1">
-      <c r="B13" s="80" t="s">
+      <c r="B13" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="81"/>
-      <c r="D13" s="81"/>
-      <c r="E13" s="82"/>
-      <c r="F13" s="80" t="s">
+      <c r="C13" s="79"/>
+      <c r="D13" s="79"/>
+      <c r="E13" s="80"/>
+      <c r="F13" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="G13" s="81"/>
-      <c r="H13" s="81"/>
-      <c r="I13" s="81"/>
-      <c r="J13" s="81"/>
-      <c r="K13" s="81"/>
-      <c r="L13" s="81"/>
-      <c r="M13" s="81"/>
-      <c r="N13" s="81"/>
-      <c r="O13" s="81"/>
-      <c r="P13" s="81"/>
-      <c r="Q13" s="81"/>
-      <c r="R13" s="81"/>
-      <c r="S13" s="81"/>
-      <c r="T13" s="81"/>
-      <c r="U13" s="81"/>
-      <c r="V13" s="81"/>
-      <c r="W13" s="81"/>
-      <c r="X13" s="81"/>
-      <c r="Y13" s="81"/>
-      <c r="Z13" s="81"/>
-      <c r="AA13" s="81"/>
-      <c r="AB13" s="81"/>
-      <c r="AC13" s="81"/>
-      <c r="AD13" s="81"/>
-      <c r="AE13" s="81"/>
-      <c r="AF13" s="82"/>
-      <c r="AG13" s="80" t="s">
+      <c r="G13" s="79"/>
+      <c r="H13" s="79"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="79"/>
+      <c r="K13" s="79"/>
+      <c r="L13" s="79"/>
+      <c r="M13" s="79"/>
+      <c r="N13" s="79"/>
+      <c r="O13" s="79"/>
+      <c r="P13" s="79"/>
+      <c r="Q13" s="79"/>
+      <c r="R13" s="79"/>
+      <c r="S13" s="79"/>
+      <c r="T13" s="79"/>
+      <c r="U13" s="79"/>
+      <c r="V13" s="79"/>
+      <c r="W13" s="79"/>
+      <c r="X13" s="79"/>
+      <c r="Y13" s="79"/>
+      <c r="Z13" s="79"/>
+      <c r="AA13" s="79"/>
+      <c r="AB13" s="79"/>
+      <c r="AC13" s="79"/>
+      <c r="AD13" s="79"/>
+      <c r="AE13" s="79"/>
+      <c r="AF13" s="80"/>
+      <c r="AG13" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="AH13" s="81"/>
-      <c r="AI13" s="81"/>
-      <c r="AJ13" s="81"/>
-      <c r="AK13" s="82"/>
-      <c r="AL13" s="80" t="s">
+      <c r="AH13" s="79"/>
+      <c r="AI13" s="79"/>
+      <c r="AJ13" s="79"/>
+      <c r="AK13" s="80"/>
+      <c r="AL13" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="AM13" s="81"/>
-      <c r="AN13" s="81"/>
-      <c r="AO13" s="81"/>
-      <c r="AP13" s="81"/>
-      <c r="AQ13" s="82"/>
-      <c r="AR13" s="80" t="s">
+      <c r="AM13" s="79"/>
+      <c r="AN13" s="79"/>
+      <c r="AO13" s="79"/>
+      <c r="AP13" s="79"/>
+      <c r="AQ13" s="80"/>
+      <c r="AR13" s="78" t="s">
         <v>14</v>
       </c>
-      <c r="AS13" s="81"/>
-      <c r="AT13" s="81"/>
-      <c r="AU13" s="81"/>
-      <c r="AV13" s="81"/>
-      <c r="AW13" s="82"/>
+      <c r="AS13" s="79"/>
+      <c r="AT13" s="79"/>
+      <c r="AU13" s="79"/>
+      <c r="AV13" s="79"/>
+      <c r="AW13" s="80"/>
     </row>
     <row r="14" spans="2:49" s="4" customFormat="1" ht="20.5" customHeight="1" thickTop="1">
-      <c r="B14" s="66"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="68"/>
-      <c r="F14" s="69"/>
-      <c r="G14" s="70"/>
-      <c r="H14" s="70"/>
-      <c r="I14" s="70"/>
-      <c r="J14" s="70"/>
-      <c r="K14" s="70"/>
-      <c r="L14" s="70"/>
-      <c r="M14" s="70"/>
-      <c r="N14" s="70"/>
-      <c r="O14" s="70"/>
-      <c r="P14" s="70"/>
-      <c r="Q14" s="70"/>
-      <c r="R14" s="70"/>
-      <c r="S14" s="70"/>
-      <c r="T14" s="70"/>
-      <c r="U14" s="70"/>
-      <c r="V14" s="70"/>
-      <c r="W14" s="70"/>
-      <c r="X14" s="70"/>
-      <c r="Y14" s="70"/>
-      <c r="Z14" s="70"/>
-      <c r="AA14" s="70"/>
-      <c r="AB14" s="70"/>
-      <c r="AC14" s="70"/>
-      <c r="AD14" s="70"/>
-      <c r="AE14" s="70"/>
-      <c r="AF14" s="70"/>
-      <c r="AG14" s="74"/>
-      <c r="AH14" s="75"/>
-      <c r="AI14" s="75"/>
-      <c r="AJ14" s="75"/>
-      <c r="AK14" s="76"/>
-      <c r="AL14" s="62"/>
-      <c r="AM14" s="62"/>
-      <c r="AN14" s="62"/>
-      <c r="AO14" s="62"/>
-      <c r="AP14" s="62"/>
-      <c r="AQ14" s="63"/>
-      <c r="AR14" s="64"/>
-      <c r="AS14" s="49"/>
-      <c r="AT14" s="49"/>
-      <c r="AU14" s="49"/>
-      <c r="AV14" s="49"/>
-      <c r="AW14" s="65"/>
+      <c r="B14" s="64"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="68"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="68"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="68"/>
+      <c r="M14" s="68"/>
+      <c r="N14" s="68"/>
+      <c r="O14" s="68"/>
+      <c r="P14" s="68"/>
+      <c r="Q14" s="68"/>
+      <c r="R14" s="68"/>
+      <c r="S14" s="68"/>
+      <c r="T14" s="68"/>
+      <c r="U14" s="68"/>
+      <c r="V14" s="68"/>
+      <c r="W14" s="68"/>
+      <c r="X14" s="68"/>
+      <c r="Y14" s="68"/>
+      <c r="Z14" s="68"/>
+      <c r="AA14" s="68"/>
+      <c r="AB14" s="68"/>
+      <c r="AC14" s="68"/>
+      <c r="AD14" s="68"/>
+      <c r="AE14" s="68"/>
+      <c r="AF14" s="68"/>
+      <c r="AG14" s="72"/>
+      <c r="AH14" s="73"/>
+      <c r="AI14" s="73"/>
+      <c r="AJ14" s="73"/>
+      <c r="AK14" s="74"/>
+      <c r="AL14" s="60"/>
+      <c r="AM14" s="60"/>
+      <c r="AN14" s="60"/>
+      <c r="AO14" s="60"/>
+      <c r="AP14" s="60"/>
+      <c r="AQ14" s="61"/>
+      <c r="AR14" s="62"/>
+      <c r="AS14" s="47"/>
+      <c r="AT14" s="47"/>
+      <c r="AU14" s="47"/>
+      <c r="AV14" s="47"/>
+      <c r="AW14" s="63"/>
     </row>
     <row r="15" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B15" s="66"/>
-      <c r="C15" s="67"/>
-      <c r="D15" s="67"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="70"/>
-      <c r="H15" s="70"/>
-      <c r="I15" s="70"/>
-      <c r="J15" s="70"/>
-      <c r="K15" s="70"/>
-      <c r="L15" s="70"/>
-      <c r="M15" s="70"/>
-      <c r="N15" s="70"/>
-      <c r="O15" s="70"/>
-      <c r="P15" s="70"/>
-      <c r="Q15" s="70"/>
-      <c r="R15" s="70"/>
-      <c r="S15" s="70"/>
-      <c r="T15" s="70"/>
-      <c r="U15" s="70"/>
-      <c r="V15" s="70"/>
-      <c r="W15" s="70"/>
-      <c r="X15" s="70"/>
-      <c r="Y15" s="70"/>
-      <c r="Z15" s="70"/>
-      <c r="AA15" s="70"/>
-      <c r="AB15" s="70"/>
-      <c r="AC15" s="70"/>
-      <c r="AD15" s="70"/>
-      <c r="AE15" s="70"/>
-      <c r="AF15" s="70"/>
-      <c r="AG15" s="74"/>
-      <c r="AH15" s="75"/>
-      <c r="AI15" s="75"/>
-      <c r="AJ15" s="75"/>
-      <c r="AK15" s="76"/>
-      <c r="AL15" s="62"/>
-      <c r="AM15" s="62"/>
-      <c r="AN15" s="62"/>
-      <c r="AO15" s="62"/>
-      <c r="AP15" s="62"/>
-      <c r="AQ15" s="63"/>
-      <c r="AR15" s="64"/>
-      <c r="AS15" s="49"/>
-      <c r="AT15" s="49"/>
-      <c r="AU15" s="49"/>
-      <c r="AV15" s="49"/>
-      <c r="AW15" s="65"/>
+      <c r="B15" s="64"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="68"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="68"/>
+      <c r="J15" s="68"/>
+      <c r="K15" s="68"/>
+      <c r="L15" s="68"/>
+      <c r="M15" s="68"/>
+      <c r="N15" s="68"/>
+      <c r="O15" s="68"/>
+      <c r="P15" s="68"/>
+      <c r="Q15" s="68"/>
+      <c r="R15" s="68"/>
+      <c r="S15" s="68"/>
+      <c r="T15" s="68"/>
+      <c r="U15" s="68"/>
+      <c r="V15" s="68"/>
+      <c r="W15" s="68"/>
+      <c r="X15" s="68"/>
+      <c r="Y15" s="68"/>
+      <c r="Z15" s="68"/>
+      <c r="AA15" s="68"/>
+      <c r="AB15" s="68"/>
+      <c r="AC15" s="68"/>
+      <c r="AD15" s="68"/>
+      <c r="AE15" s="68"/>
+      <c r="AF15" s="68"/>
+      <c r="AG15" s="72"/>
+      <c r="AH15" s="73"/>
+      <c r="AI15" s="73"/>
+      <c r="AJ15" s="73"/>
+      <c r="AK15" s="74"/>
+      <c r="AL15" s="60"/>
+      <c r="AM15" s="60"/>
+      <c r="AN15" s="60"/>
+      <c r="AO15" s="60"/>
+      <c r="AP15" s="60"/>
+      <c r="AQ15" s="61"/>
+      <c r="AR15" s="62"/>
+      <c r="AS15" s="47"/>
+      <c r="AT15" s="47"/>
+      <c r="AU15" s="47"/>
+      <c r="AV15" s="47"/>
+      <c r="AW15" s="63"/>
     </row>
     <row r="16" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B16" s="66"/>
-      <c r="C16" s="67"/>
-      <c r="D16" s="67"/>
-      <c r="E16" s="68"/>
-      <c r="F16" s="78"/>
-      <c r="G16" s="79"/>
-      <c r="H16" s="79"/>
-      <c r="I16" s="79"/>
-      <c r="J16" s="79"/>
-      <c r="K16" s="79"/>
-      <c r="L16" s="79"/>
-      <c r="M16" s="79"/>
-      <c r="N16" s="79"/>
-      <c r="O16" s="79"/>
-      <c r="P16" s="79"/>
-      <c r="Q16" s="79"/>
-      <c r="R16" s="79"/>
-      <c r="S16" s="79"/>
-      <c r="T16" s="79"/>
-      <c r="U16" s="79"/>
-      <c r="V16" s="79"/>
-      <c r="W16" s="79"/>
-      <c r="X16" s="79"/>
-      <c r="Y16" s="79"/>
-      <c r="Z16" s="79"/>
-      <c r="AA16" s="79"/>
-      <c r="AB16" s="79"/>
-      <c r="AC16" s="79"/>
-      <c r="AD16" s="79"/>
-      <c r="AE16" s="79"/>
-      <c r="AF16" s="79"/>
-      <c r="AG16" s="74"/>
-      <c r="AH16" s="75"/>
-      <c r="AI16" s="75"/>
-      <c r="AJ16" s="75"/>
-      <c r="AK16" s="76"/>
-      <c r="AL16" s="62"/>
-      <c r="AM16" s="62"/>
-      <c r="AN16" s="62"/>
-      <c r="AO16" s="62"/>
-      <c r="AP16" s="62"/>
-      <c r="AQ16" s="63"/>
-      <c r="AR16" s="64">
+      <c r="B16" s="64"/>
+      <c r="C16" s="65"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="76"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="77"/>
+      <c r="J16" s="77"/>
+      <c r="K16" s="77"/>
+      <c r="L16" s="77"/>
+      <c r="M16" s="77"/>
+      <c r="N16" s="77"/>
+      <c r="O16" s="77"/>
+      <c r="P16" s="77"/>
+      <c r="Q16" s="77"/>
+      <c r="R16" s="77"/>
+      <c r="S16" s="77"/>
+      <c r="T16" s="77"/>
+      <c r="U16" s="77"/>
+      <c r="V16" s="77"/>
+      <c r="W16" s="77"/>
+      <c r="X16" s="77"/>
+      <c r="Y16" s="77"/>
+      <c r="Z16" s="77"/>
+      <c r="AA16" s="77"/>
+      <c r="AB16" s="77"/>
+      <c r="AC16" s="77"/>
+      <c r="AD16" s="77"/>
+      <c r="AE16" s="77"/>
+      <c r="AF16" s="77"/>
+      <c r="AG16" s="72"/>
+      <c r="AH16" s="73"/>
+      <c r="AI16" s="73"/>
+      <c r="AJ16" s="73"/>
+      <c r="AK16" s="74"/>
+      <c r="AL16" s="60"/>
+      <c r="AM16" s="60"/>
+      <c r="AN16" s="60"/>
+      <c r="AO16" s="60"/>
+      <c r="AP16" s="60"/>
+      <c r="AQ16" s="61"/>
+      <c r="AR16" s="62">
         <f t="shared" ref="AR16:AR18" si="0">AL16*AG16</f>
         <v>0</v>
       </c>
-      <c r="AS16" s="49"/>
-      <c r="AT16" s="49"/>
-      <c r="AU16" s="49"/>
-      <c r="AV16" s="49"/>
-      <c r="AW16" s="65"/>
+      <c r="AS16" s="47"/>
+      <c r="AT16" s="47"/>
+      <c r="AU16" s="47"/>
+      <c r="AV16" s="47"/>
+      <c r="AW16" s="63"/>
     </row>
     <row r="17" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B17" s="66"/>
-      <c r="C17" s="67"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
-      <c r="I17" s="70"/>
-      <c r="J17" s="70"/>
-      <c r="K17" s="70"/>
-      <c r="L17" s="70"/>
-      <c r="M17" s="70"/>
-      <c r="N17" s="70"/>
-      <c r="O17" s="70"/>
-      <c r="P17" s="70"/>
-      <c r="Q17" s="70"/>
-      <c r="R17" s="70"/>
-      <c r="S17" s="70"/>
-      <c r="T17" s="70"/>
-      <c r="U17" s="70"/>
-      <c r="V17" s="70"/>
-      <c r="W17" s="70"/>
-      <c r="X17" s="70"/>
-      <c r="Y17" s="70"/>
-      <c r="Z17" s="70"/>
-      <c r="AA17" s="70"/>
-      <c r="AB17" s="70"/>
-      <c r="AC17" s="70"/>
-      <c r="AD17" s="70"/>
-      <c r="AE17" s="70"/>
-      <c r="AF17" s="70"/>
-      <c r="AG17" s="74"/>
-      <c r="AH17" s="75"/>
-      <c r="AI17" s="75"/>
-      <c r="AJ17" s="75"/>
-      <c r="AK17" s="76"/>
-      <c r="AL17" s="62"/>
-      <c r="AM17" s="62"/>
-      <c r="AN17" s="62"/>
-      <c r="AO17" s="62"/>
-      <c r="AP17" s="62"/>
-      <c r="AQ17" s="63"/>
-      <c r="AR17" s="64">
+      <c r="B17" s="64"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
+      <c r="L17" s="68"/>
+      <c r="M17" s="68"/>
+      <c r="N17" s="68"/>
+      <c r="O17" s="68"/>
+      <c r="P17" s="68"/>
+      <c r="Q17" s="68"/>
+      <c r="R17" s="68"/>
+      <c r="S17" s="68"/>
+      <c r="T17" s="68"/>
+      <c r="U17" s="68"/>
+      <c r="V17" s="68"/>
+      <c r="W17" s="68"/>
+      <c r="X17" s="68"/>
+      <c r="Y17" s="68"/>
+      <c r="Z17" s="68"/>
+      <c r="AA17" s="68"/>
+      <c r="AB17" s="68"/>
+      <c r="AC17" s="68"/>
+      <c r="AD17" s="68"/>
+      <c r="AE17" s="68"/>
+      <c r="AF17" s="68"/>
+      <c r="AG17" s="72"/>
+      <c r="AH17" s="73"/>
+      <c r="AI17" s="73"/>
+      <c r="AJ17" s="73"/>
+      <c r="AK17" s="74"/>
+      <c r="AL17" s="60"/>
+      <c r="AM17" s="60"/>
+      <c r="AN17" s="60"/>
+      <c r="AO17" s="60"/>
+      <c r="AP17" s="60"/>
+      <c r="AQ17" s="61"/>
+      <c r="AR17" s="62">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AS17" s="49"/>
-      <c r="AT17" s="49"/>
-      <c r="AU17" s="49"/>
-      <c r="AV17" s="49"/>
-      <c r="AW17" s="65"/>
+      <c r="AS17" s="47"/>
+      <c r="AT17" s="47"/>
+      <c r="AU17" s="47"/>
+      <c r="AV17" s="47"/>
+      <c r="AW17" s="63"/>
     </row>
     <row r="18" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B18" s="66"/>
-      <c r="C18" s="67"/>
-      <c r="D18" s="67"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="70"/>
-      <c r="H18" s="70"/>
-      <c r="I18" s="70"/>
-      <c r="J18" s="70"/>
-      <c r="K18" s="70"/>
-      <c r="L18" s="70"/>
-      <c r="M18" s="70"/>
-      <c r="N18" s="70"/>
-      <c r="O18" s="70"/>
-      <c r="P18" s="70"/>
-      <c r="Q18" s="70"/>
-      <c r="R18" s="70"/>
-      <c r="S18" s="70"/>
-      <c r="T18" s="70"/>
-      <c r="U18" s="70"/>
-      <c r="V18" s="70"/>
-      <c r="W18" s="70"/>
-      <c r="X18" s="70"/>
-      <c r="Y18" s="70"/>
-      <c r="Z18" s="70"/>
-      <c r="AA18" s="70"/>
-      <c r="AB18" s="70"/>
-      <c r="AC18" s="70"/>
-      <c r="AD18" s="70"/>
-      <c r="AE18" s="70"/>
-      <c r="AF18" s="70"/>
-      <c r="AG18" s="74"/>
-      <c r="AH18" s="75"/>
-      <c r="AI18" s="75"/>
-      <c r="AJ18" s="75"/>
-      <c r="AK18" s="76"/>
-      <c r="AL18" s="62"/>
-      <c r="AM18" s="62"/>
-      <c r="AN18" s="62"/>
-      <c r="AO18" s="62"/>
-      <c r="AP18" s="62"/>
-      <c r="AQ18" s="63"/>
-      <c r="AR18" s="64">
+      <c r="B18" s="64"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="66"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="68"/>
+      <c r="K18" s="68"/>
+      <c r="L18" s="68"/>
+      <c r="M18" s="68"/>
+      <c r="N18" s="68"/>
+      <c r="O18" s="68"/>
+      <c r="P18" s="68"/>
+      <c r="Q18" s="68"/>
+      <c r="R18" s="68"/>
+      <c r="S18" s="68"/>
+      <c r="T18" s="68"/>
+      <c r="U18" s="68"/>
+      <c r="V18" s="68"/>
+      <c r="W18" s="68"/>
+      <c r="X18" s="68"/>
+      <c r="Y18" s="68"/>
+      <c r="Z18" s="68"/>
+      <c r="AA18" s="68"/>
+      <c r="AB18" s="68"/>
+      <c r="AC18" s="68"/>
+      <c r="AD18" s="68"/>
+      <c r="AE18" s="68"/>
+      <c r="AF18" s="68"/>
+      <c r="AG18" s="72"/>
+      <c r="AH18" s="73"/>
+      <c r="AI18" s="73"/>
+      <c r="AJ18" s="73"/>
+      <c r="AK18" s="74"/>
+      <c r="AL18" s="60"/>
+      <c r="AM18" s="60"/>
+      <c r="AN18" s="60"/>
+      <c r="AO18" s="60"/>
+      <c r="AP18" s="60"/>
+      <c r="AQ18" s="61"/>
+      <c r="AR18" s="62">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AS18" s="49"/>
-      <c r="AT18" s="49"/>
-      <c r="AU18" s="49"/>
-      <c r="AV18" s="49"/>
-      <c r="AW18" s="65"/>
+      <c r="AS18" s="47"/>
+      <c r="AT18" s="47"/>
+      <c r="AU18" s="47"/>
+      <c r="AV18" s="47"/>
+      <c r="AW18" s="63"/>
     </row>
     <row r="19" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B19" s="66"/>
-      <c r="C19" s="67"/>
-      <c r="D19" s="67"/>
-      <c r="E19" s="68"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
-      <c r="I19" s="70"/>
-      <c r="J19" s="70"/>
-      <c r="K19" s="70"/>
-      <c r="L19" s="70"/>
-      <c r="M19" s="70"/>
-      <c r="N19" s="70"/>
-      <c r="O19" s="70"/>
-      <c r="P19" s="70"/>
-      <c r="Q19" s="70"/>
-      <c r="R19" s="70"/>
-      <c r="S19" s="70"/>
-      <c r="T19" s="70"/>
-      <c r="U19" s="70"/>
-      <c r="V19" s="70"/>
-      <c r="W19" s="70"/>
-      <c r="X19" s="70"/>
-      <c r="Y19" s="70"/>
-      <c r="Z19" s="70"/>
-      <c r="AA19" s="70"/>
-      <c r="AB19" s="70"/>
-      <c r="AC19" s="70"/>
-      <c r="AD19" s="70"/>
-      <c r="AE19" s="70"/>
-      <c r="AF19" s="70"/>
-      <c r="AG19" s="74"/>
-      <c r="AH19" s="75"/>
-      <c r="AI19" s="75"/>
-      <c r="AJ19" s="75"/>
-      <c r="AK19" s="76"/>
-      <c r="AL19" s="62"/>
-      <c r="AM19" s="62"/>
-      <c r="AN19" s="62"/>
-      <c r="AO19" s="62"/>
-      <c r="AP19" s="62"/>
-      <c r="AQ19" s="63"/>
-      <c r="AR19" s="64">
+      <c r="B19" s="64"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="66"/>
+      <c r="F19" s="67"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="68"/>
+      <c r="L19" s="68"/>
+      <c r="M19" s="68"/>
+      <c r="N19" s="68"/>
+      <c r="O19" s="68"/>
+      <c r="P19" s="68"/>
+      <c r="Q19" s="68"/>
+      <c r="R19" s="68"/>
+      <c r="S19" s="68"/>
+      <c r="T19" s="68"/>
+      <c r="U19" s="68"/>
+      <c r="V19" s="68"/>
+      <c r="W19" s="68"/>
+      <c r="X19" s="68"/>
+      <c r="Y19" s="68"/>
+      <c r="Z19" s="68"/>
+      <c r="AA19" s="68"/>
+      <c r="AB19" s="68"/>
+      <c r="AC19" s="68"/>
+      <c r="AD19" s="68"/>
+      <c r="AE19" s="68"/>
+      <c r="AF19" s="68"/>
+      <c r="AG19" s="72"/>
+      <c r="AH19" s="73"/>
+      <c r="AI19" s="73"/>
+      <c r="AJ19" s="73"/>
+      <c r="AK19" s="74"/>
+      <c r="AL19" s="60"/>
+      <c r="AM19" s="60"/>
+      <c r="AN19" s="60"/>
+      <c r="AO19" s="60"/>
+      <c r="AP19" s="60"/>
+      <c r="AQ19" s="61"/>
+      <c r="AR19" s="62">
         <f>AL19*AG19</f>
         <v>0</v>
       </c>
-      <c r="AS19" s="49"/>
-      <c r="AT19" s="49"/>
-      <c r="AU19" s="49"/>
-      <c r="AV19" s="49"/>
-      <c r="AW19" s="65"/>
+      <c r="AS19" s="47"/>
+      <c r="AT19" s="47"/>
+      <c r="AU19" s="47"/>
+      <c r="AV19" s="47"/>
+      <c r="AW19" s="63"/>
     </row>
     <row r="20" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B20" s="66"/>
-      <c r="C20" s="67"/>
-      <c r="D20" s="67"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="69"/>
-      <c r="G20" s="70"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="70"/>
-      <c r="J20" s="70"/>
-      <c r="K20" s="70"/>
-      <c r="L20" s="70"/>
-      <c r="M20" s="70"/>
-      <c r="N20" s="70"/>
-      <c r="O20" s="70"/>
-      <c r="P20" s="70"/>
-      <c r="Q20" s="70"/>
-      <c r="R20" s="70"/>
-      <c r="S20" s="70"/>
-      <c r="T20" s="70"/>
-      <c r="U20" s="70"/>
-      <c r="V20" s="70"/>
-      <c r="W20" s="70"/>
-      <c r="X20" s="70"/>
-      <c r="Y20" s="70"/>
-      <c r="Z20" s="70"/>
-      <c r="AA20" s="70"/>
-      <c r="AB20" s="70"/>
-      <c r="AC20" s="70"/>
-      <c r="AD20" s="70"/>
-      <c r="AE20" s="70"/>
-      <c r="AF20" s="70"/>
-      <c r="AG20" s="74"/>
-      <c r="AH20" s="75"/>
-      <c r="AI20" s="75"/>
-      <c r="AJ20" s="75"/>
-      <c r="AK20" s="76"/>
-      <c r="AL20" s="77"/>
-      <c r="AM20" s="62"/>
-      <c r="AN20" s="62"/>
-      <c r="AO20" s="62"/>
-      <c r="AP20" s="62"/>
-      <c r="AQ20" s="63"/>
-      <c r="AR20" s="64">
+      <c r="B20" s="64"/>
+      <c r="C20" s="65"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="66"/>
+      <c r="F20" s="67"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="68"/>
+      <c r="L20" s="68"/>
+      <c r="M20" s="68"/>
+      <c r="N20" s="68"/>
+      <c r="O20" s="68"/>
+      <c r="P20" s="68"/>
+      <c r="Q20" s="68"/>
+      <c r="R20" s="68"/>
+      <c r="S20" s="68"/>
+      <c r="T20" s="68"/>
+      <c r="U20" s="68"/>
+      <c r="V20" s="68"/>
+      <c r="W20" s="68"/>
+      <c r="X20" s="68"/>
+      <c r="Y20" s="68"/>
+      <c r="Z20" s="68"/>
+      <c r="AA20" s="68"/>
+      <c r="AB20" s="68"/>
+      <c r="AC20" s="68"/>
+      <c r="AD20" s="68"/>
+      <c r="AE20" s="68"/>
+      <c r="AF20" s="68"/>
+      <c r="AG20" s="72"/>
+      <c r="AH20" s="73"/>
+      <c r="AI20" s="73"/>
+      <c r="AJ20" s="73"/>
+      <c r="AK20" s="74"/>
+      <c r="AL20" s="75"/>
+      <c r="AM20" s="60"/>
+      <c r="AN20" s="60"/>
+      <c r="AO20" s="60"/>
+      <c r="AP20" s="60"/>
+      <c r="AQ20" s="61"/>
+      <c r="AR20" s="62">
         <f>AL20*AG20</f>
         <v>0</v>
       </c>
-      <c r="AS20" s="49"/>
-      <c r="AT20" s="49"/>
-      <c r="AU20" s="49"/>
-      <c r="AV20" s="49"/>
-      <c r="AW20" s="65"/>
+      <c r="AS20" s="47"/>
+      <c r="AT20" s="47"/>
+      <c r="AU20" s="47"/>
+      <c r="AV20" s="47"/>
+      <c r="AW20" s="63"/>
     </row>
     <row r="21" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B21" s="66"/>
-      <c r="C21" s="67"/>
-      <c r="D21" s="67"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
-      <c r="I21" s="70"/>
-      <c r="J21" s="70"/>
-      <c r="K21" s="70"/>
-      <c r="L21" s="70"/>
-      <c r="M21" s="70"/>
-      <c r="N21" s="70"/>
-      <c r="O21" s="70"/>
-      <c r="P21" s="70"/>
-      <c r="Q21" s="70"/>
-      <c r="R21" s="70"/>
-      <c r="S21" s="70"/>
-      <c r="T21" s="70"/>
-      <c r="U21" s="70"/>
-      <c r="V21" s="70"/>
-      <c r="W21" s="70"/>
-      <c r="X21" s="70"/>
-      <c r="Y21" s="70"/>
-      <c r="Z21" s="70"/>
-      <c r="AA21" s="70"/>
-      <c r="AB21" s="70"/>
-      <c r="AC21" s="70"/>
-      <c r="AD21" s="70"/>
-      <c r="AE21" s="70"/>
-      <c r="AF21" s="70"/>
-      <c r="AG21" s="74"/>
-      <c r="AH21" s="75"/>
-      <c r="AI21" s="75"/>
-      <c r="AJ21" s="75"/>
-      <c r="AK21" s="76"/>
-      <c r="AL21" s="62"/>
-      <c r="AM21" s="62"/>
-      <c r="AN21" s="62"/>
-      <c r="AO21" s="62"/>
-      <c r="AP21" s="62"/>
-      <c r="AQ21" s="63"/>
-      <c r="AR21" s="64">
+      <c r="B21" s="64"/>
+      <c r="C21" s="65"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="66"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="68"/>
+      <c r="L21" s="68"/>
+      <c r="M21" s="68"/>
+      <c r="N21" s="68"/>
+      <c r="O21" s="68"/>
+      <c r="P21" s="68"/>
+      <c r="Q21" s="68"/>
+      <c r="R21" s="68"/>
+      <c r="S21" s="68"/>
+      <c r="T21" s="68"/>
+      <c r="U21" s="68"/>
+      <c r="V21" s="68"/>
+      <c r="W21" s="68"/>
+      <c r="X21" s="68"/>
+      <c r="Y21" s="68"/>
+      <c r="Z21" s="68"/>
+      <c r="AA21" s="68"/>
+      <c r="AB21" s="68"/>
+      <c r="AC21" s="68"/>
+      <c r="AD21" s="68"/>
+      <c r="AE21" s="68"/>
+      <c r="AF21" s="68"/>
+      <c r="AG21" s="72"/>
+      <c r="AH21" s="73"/>
+      <c r="AI21" s="73"/>
+      <c r="AJ21" s="73"/>
+      <c r="AK21" s="74"/>
+      <c r="AL21" s="60"/>
+      <c r="AM21" s="60"/>
+      <c r="AN21" s="60"/>
+      <c r="AO21" s="60"/>
+      <c r="AP21" s="60"/>
+      <c r="AQ21" s="61"/>
+      <c r="AR21" s="62">
         <f t="shared" ref="AR21:AR35" si="1">AL21*AG21</f>
         <v>0</v>
       </c>
-      <c r="AS21" s="49"/>
-      <c r="AT21" s="49"/>
-      <c r="AU21" s="49"/>
-      <c r="AV21" s="49"/>
-      <c r="AW21" s="65"/>
+      <c r="AS21" s="47"/>
+      <c r="AT21" s="47"/>
+      <c r="AU21" s="47"/>
+      <c r="AV21" s="47"/>
+      <c r="AW21" s="63"/>
     </row>
     <row r="22" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B22" s="66"/>
-      <c r="C22" s="67"/>
-      <c r="D22" s="67"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="70"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
-      <c r="J22" s="70"/>
-      <c r="K22" s="70"/>
-      <c r="L22" s="70"/>
-      <c r="M22" s="70"/>
-      <c r="N22" s="70"/>
-      <c r="O22" s="70"/>
-      <c r="P22" s="70"/>
-      <c r="Q22" s="70"/>
-      <c r="R22" s="70"/>
-      <c r="S22" s="70"/>
-      <c r="T22" s="70"/>
-      <c r="U22" s="70"/>
-      <c r="V22" s="70"/>
-      <c r="W22" s="70"/>
-      <c r="X22" s="70"/>
-      <c r="Y22" s="70"/>
-      <c r="Z22" s="70"/>
-      <c r="AA22" s="70"/>
-      <c r="AB22" s="70"/>
-      <c r="AC22" s="70"/>
-      <c r="AD22" s="70"/>
-      <c r="AE22" s="70"/>
-      <c r="AF22" s="70"/>
-      <c r="AG22" s="74"/>
-      <c r="AH22" s="75"/>
-      <c r="AI22" s="75"/>
-      <c r="AJ22" s="75"/>
-      <c r="AK22" s="76"/>
-      <c r="AL22" s="62"/>
-      <c r="AM22" s="62"/>
-      <c r="AN22" s="62"/>
-      <c r="AO22" s="62"/>
-      <c r="AP22" s="62"/>
-      <c r="AQ22" s="63"/>
-      <c r="AR22" s="64">
+      <c r="B22" s="64"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="66"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="68"/>
+      <c r="L22" s="68"/>
+      <c r="M22" s="68"/>
+      <c r="N22" s="68"/>
+      <c r="O22" s="68"/>
+      <c r="P22" s="68"/>
+      <c r="Q22" s="68"/>
+      <c r="R22" s="68"/>
+      <c r="S22" s="68"/>
+      <c r="T22" s="68"/>
+      <c r="U22" s="68"/>
+      <c r="V22" s="68"/>
+      <c r="W22" s="68"/>
+      <c r="X22" s="68"/>
+      <c r="Y22" s="68"/>
+      <c r="Z22" s="68"/>
+      <c r="AA22" s="68"/>
+      <c r="AB22" s="68"/>
+      <c r="AC22" s="68"/>
+      <c r="AD22" s="68"/>
+      <c r="AE22" s="68"/>
+      <c r="AF22" s="68"/>
+      <c r="AG22" s="72"/>
+      <c r="AH22" s="73"/>
+      <c r="AI22" s="73"/>
+      <c r="AJ22" s="73"/>
+      <c r="AK22" s="74"/>
+      <c r="AL22" s="60"/>
+      <c r="AM22" s="60"/>
+      <c r="AN22" s="60"/>
+      <c r="AO22" s="60"/>
+      <c r="AP22" s="60"/>
+      <c r="AQ22" s="61"/>
+      <c r="AR22" s="62">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AS22" s="49"/>
-      <c r="AT22" s="49"/>
-      <c r="AU22" s="49"/>
-      <c r="AV22" s="49"/>
-      <c r="AW22" s="65"/>
+      <c r="AS22" s="47"/>
+      <c r="AT22" s="47"/>
+      <c r="AU22" s="47"/>
+      <c r="AV22" s="47"/>
+      <c r="AW22" s="63"/>
     </row>
     <row r="23" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B23" s="66"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="69"/>
-      <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="70"/>
-      <c r="J23" s="70"/>
-      <c r="K23" s="70"/>
-      <c r="L23" s="70"/>
-      <c r="M23" s="70"/>
-      <c r="N23" s="70"/>
-      <c r="O23" s="70"/>
-      <c r="P23" s="70"/>
-      <c r="Q23" s="70"/>
-      <c r="R23" s="70"/>
-      <c r="S23" s="70"/>
-      <c r="T23" s="70"/>
-      <c r="U23" s="70"/>
-      <c r="V23" s="70"/>
-      <c r="W23" s="70"/>
-      <c r="X23" s="70"/>
-      <c r="Y23" s="70"/>
-      <c r="Z23" s="70"/>
-      <c r="AA23" s="70"/>
-      <c r="AB23" s="70"/>
-      <c r="AC23" s="70"/>
-      <c r="AD23" s="70"/>
-      <c r="AE23" s="70"/>
-      <c r="AF23" s="70"/>
-      <c r="AG23" s="74"/>
-      <c r="AH23" s="75"/>
-      <c r="AI23" s="75"/>
-      <c r="AJ23" s="75"/>
-      <c r="AK23" s="76"/>
-      <c r="AL23" s="62"/>
-      <c r="AM23" s="62"/>
-      <c r="AN23" s="62"/>
-      <c r="AO23" s="62"/>
-      <c r="AP23" s="62"/>
-      <c r="AQ23" s="63"/>
-      <c r="AR23" s="64">
+      <c r="B23" s="64"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="68"/>
+      <c r="K23" s="68"/>
+      <c r="L23" s="68"/>
+      <c r="M23" s="68"/>
+      <c r="N23" s="68"/>
+      <c r="O23" s="68"/>
+      <c r="P23" s="68"/>
+      <c r="Q23" s="68"/>
+      <c r="R23" s="68"/>
+      <c r="S23" s="68"/>
+      <c r="T23" s="68"/>
+      <c r="U23" s="68"/>
+      <c r="V23" s="68"/>
+      <c r="W23" s="68"/>
+      <c r="X23" s="68"/>
+      <c r="Y23" s="68"/>
+      <c r="Z23" s="68"/>
+      <c r="AA23" s="68"/>
+      <c r="AB23" s="68"/>
+      <c r="AC23" s="68"/>
+      <c r="AD23" s="68"/>
+      <c r="AE23" s="68"/>
+      <c r="AF23" s="68"/>
+      <c r="AG23" s="72"/>
+      <c r="AH23" s="73"/>
+      <c r="AI23" s="73"/>
+      <c r="AJ23" s="73"/>
+      <c r="AK23" s="74"/>
+      <c r="AL23" s="60"/>
+      <c r="AM23" s="60"/>
+      <c r="AN23" s="60"/>
+      <c r="AO23" s="60"/>
+      <c r="AP23" s="60"/>
+      <c r="AQ23" s="61"/>
+      <c r="AR23" s="62">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AS23" s="49"/>
-      <c r="AT23" s="49"/>
-      <c r="AU23" s="49"/>
-      <c r="AV23" s="49"/>
-      <c r="AW23" s="65"/>
+      <c r="AS23" s="47"/>
+      <c r="AT23" s="47"/>
+      <c r="AU23" s="47"/>
+      <c r="AV23" s="47"/>
+      <c r="AW23" s="63"/>
     </row>
     <row r="24" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B24" s="66"/>
-      <c r="C24" s="67"/>
-      <c r="D24" s="67"/>
-      <c r="E24" s="68"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="70"/>
-      <c r="J24" s="70"/>
-      <c r="K24" s="70"/>
-      <c r="L24" s="70"/>
-      <c r="M24" s="70"/>
-      <c r="N24" s="70"/>
-      <c r="O24" s="70"/>
-      <c r="P24" s="70"/>
-      <c r="Q24" s="70"/>
-      <c r="R24" s="70"/>
-      <c r="S24" s="70"/>
-      <c r="T24" s="70"/>
-      <c r="U24" s="70"/>
-      <c r="V24" s="70"/>
-      <c r="W24" s="70"/>
-      <c r="X24" s="70"/>
-      <c r="Y24" s="70"/>
-      <c r="Z24" s="70"/>
-      <c r="AA24" s="70"/>
-      <c r="AB24" s="70"/>
-      <c r="AC24" s="70"/>
-      <c r="AD24" s="70"/>
-      <c r="AE24" s="70"/>
-      <c r="AF24" s="70"/>
-      <c r="AG24" s="74"/>
-      <c r="AH24" s="75"/>
-      <c r="AI24" s="75"/>
-      <c r="AJ24" s="75"/>
-      <c r="AK24" s="76"/>
-      <c r="AL24" s="62"/>
-      <c r="AM24" s="62"/>
-      <c r="AN24" s="62"/>
-      <c r="AO24" s="62"/>
-      <c r="AP24" s="62"/>
-      <c r="AQ24" s="63"/>
-      <c r="AR24" s="64">
+      <c r="B24" s="64"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="66"/>
+      <c r="F24" s="67"/>
+      <c r="G24" s="68"/>
+      <c r="H24" s="68"/>
+      <c r="I24" s="68"/>
+      <c r="J24" s="68"/>
+      <c r="K24" s="68"/>
+      <c r="L24" s="68"/>
+      <c r="M24" s="68"/>
+      <c r="N24" s="68"/>
+      <c r="O24" s="68"/>
+      <c r="P24" s="68"/>
+      <c r="Q24" s="68"/>
+      <c r="R24" s="68"/>
+      <c r="S24" s="68"/>
+      <c r="T24" s="68"/>
+      <c r="U24" s="68"/>
+      <c r="V24" s="68"/>
+      <c r="W24" s="68"/>
+      <c r="X24" s="68"/>
+      <c r="Y24" s="68"/>
+      <c r="Z24" s="68"/>
+      <c r="AA24" s="68"/>
+      <c r="AB24" s="68"/>
+      <c r="AC24" s="68"/>
+      <c r="AD24" s="68"/>
+      <c r="AE24" s="68"/>
+      <c r="AF24" s="68"/>
+      <c r="AG24" s="72"/>
+      <c r="AH24" s="73"/>
+      <c r="AI24" s="73"/>
+      <c r="AJ24" s="73"/>
+      <c r="AK24" s="74"/>
+      <c r="AL24" s="60"/>
+      <c r="AM24" s="60"/>
+      <c r="AN24" s="60"/>
+      <c r="AO24" s="60"/>
+      <c r="AP24" s="60"/>
+      <c r="AQ24" s="61"/>
+      <c r="AR24" s="62">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AS24" s="49"/>
-      <c r="AT24" s="49"/>
-      <c r="AU24" s="49"/>
-      <c r="AV24" s="49"/>
-      <c r="AW24" s="65"/>
+      <c r="AS24" s="47"/>
+      <c r="AT24" s="47"/>
+      <c r="AU24" s="47"/>
+      <c r="AV24" s="47"/>
+      <c r="AW24" s="63"/>
     </row>
     <row r="25" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B25" s="66"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="36"/>
-      <c r="K25" s="36"/>
-      <c r="L25" s="36"/>
-      <c r="M25" s="36"/>
-      <c r="N25" s="36"/>
-      <c r="O25" s="36"/>
-      <c r="P25" s="36"/>
-      <c r="Q25" s="36"/>
-      <c r="R25" s="36"/>
-      <c r="S25" s="36"/>
-      <c r="T25" s="36"/>
-      <c r="U25" s="36"/>
-      <c r="V25" s="36"/>
-      <c r="W25" s="36"/>
-      <c r="X25" s="36"/>
-      <c r="Y25" s="36"/>
-      <c r="Z25" s="36"/>
-      <c r="AA25" s="36"/>
-      <c r="AB25" s="36"/>
-      <c r="AC25" s="36"/>
-      <c r="AD25" s="36"/>
-      <c r="AE25" s="36"/>
-      <c r="AF25" s="36"/>
+      <c r="B25" s="64"/>
+      <c r="C25" s="65"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="66"/>
+      <c r="F25" s="67"/>
+      <c r="G25" s="68"/>
+      <c r="H25" s="68"/>
+      <c r="I25" s="68"/>
+      <c r="J25" s="68"/>
+      <c r="K25" s="68"/>
+      <c r="L25" s="68"/>
+      <c r="M25" s="68"/>
+      <c r="N25" s="68"/>
+      <c r="O25" s="68"/>
+      <c r="P25" s="68"/>
+      <c r="Q25" s="68"/>
+      <c r="R25" s="68"/>
+      <c r="S25" s="68"/>
+      <c r="T25" s="68"/>
+      <c r="U25" s="68"/>
+      <c r="V25" s="68"/>
+      <c r="W25" s="68"/>
+      <c r="X25" s="68"/>
+      <c r="Y25" s="68"/>
+      <c r="Z25" s="68"/>
+      <c r="AA25" s="68"/>
+      <c r="AB25" s="68"/>
+      <c r="AC25" s="68"/>
+      <c r="AD25" s="68"/>
+      <c r="AE25" s="68"/>
+      <c r="AF25" s="95"/>
       <c r="AG25" s="32"/>
       <c r="AH25" s="16"/>
       <c r="AI25" s="16"/>
       <c r="AJ25" s="16"/>
-      <c r="AK25" s="40"/>
-      <c r="AL25" s="38"/>
-      <c r="AM25" s="38"/>
-      <c r="AN25" s="38"/>
-      <c r="AO25" s="38"/>
-      <c r="AP25" s="38"/>
-      <c r="AQ25" s="39"/>
+      <c r="AK25" s="38"/>
+      <c r="AL25" s="36"/>
+      <c r="AM25" s="36"/>
+      <c r="AN25" s="36"/>
+      <c r="AO25" s="36"/>
+      <c r="AP25" s="36"/>
+      <c r="AQ25" s="37"/>
       <c r="AR25" s="33"/>
       <c r="AS25" s="34"/>
       <c r="AT25" s="34"/>
@@ -3307,366 +3304,366 @@
       <c r="AW25" s="35"/>
     </row>
     <row r="26" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B26" s="66"/>
-      <c r="C26" s="67"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="68"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="70"/>
-      <c r="J26" s="70"/>
-      <c r="K26" s="70"/>
-      <c r="L26" s="70"/>
-      <c r="M26" s="70"/>
-      <c r="N26" s="70"/>
-      <c r="O26" s="70"/>
-      <c r="P26" s="70"/>
-      <c r="Q26" s="70"/>
-      <c r="R26" s="70"/>
-      <c r="S26" s="70"/>
-      <c r="T26" s="70"/>
-      <c r="U26" s="70"/>
-      <c r="V26" s="70"/>
-      <c r="W26" s="70"/>
-      <c r="X26" s="70"/>
-      <c r="Y26" s="70"/>
-      <c r="Z26" s="70"/>
-      <c r="AA26" s="70"/>
-      <c r="AB26" s="70"/>
-      <c r="AC26" s="70"/>
-      <c r="AD26" s="70"/>
-      <c r="AE26" s="70"/>
-      <c r="AF26" s="70"/>
-      <c r="AG26" s="74"/>
-      <c r="AH26" s="75"/>
-      <c r="AI26" s="75"/>
-      <c r="AJ26" s="75"/>
-      <c r="AK26" s="76"/>
-      <c r="AL26" s="62"/>
-      <c r="AM26" s="62"/>
-      <c r="AN26" s="62"/>
-      <c r="AO26" s="62"/>
-      <c r="AP26" s="62"/>
-      <c r="AQ26" s="63"/>
-      <c r="AR26" s="64">
+      <c r="B26" s="64"/>
+      <c r="C26" s="65"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="66"/>
+      <c r="F26" s="67"/>
+      <c r="G26" s="68"/>
+      <c r="H26" s="68"/>
+      <c r="I26" s="68"/>
+      <c r="J26" s="68"/>
+      <c r="K26" s="68"/>
+      <c r="L26" s="68"/>
+      <c r="M26" s="68"/>
+      <c r="N26" s="68"/>
+      <c r="O26" s="68"/>
+      <c r="P26" s="68"/>
+      <c r="Q26" s="68"/>
+      <c r="R26" s="68"/>
+      <c r="S26" s="68"/>
+      <c r="T26" s="68"/>
+      <c r="U26" s="68"/>
+      <c r="V26" s="68"/>
+      <c r="W26" s="68"/>
+      <c r="X26" s="68"/>
+      <c r="Y26" s="68"/>
+      <c r="Z26" s="68"/>
+      <c r="AA26" s="68"/>
+      <c r="AB26" s="68"/>
+      <c r="AC26" s="68"/>
+      <c r="AD26" s="68"/>
+      <c r="AE26" s="68"/>
+      <c r="AF26" s="68"/>
+      <c r="AG26" s="72"/>
+      <c r="AH26" s="73"/>
+      <c r="AI26" s="73"/>
+      <c r="AJ26" s="73"/>
+      <c r="AK26" s="74"/>
+      <c r="AL26" s="60"/>
+      <c r="AM26" s="60"/>
+      <c r="AN26" s="60"/>
+      <c r="AO26" s="60"/>
+      <c r="AP26" s="60"/>
+      <c r="AQ26" s="61"/>
+      <c r="AR26" s="62">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AS26" s="49"/>
-      <c r="AT26" s="49"/>
-      <c r="AU26" s="49"/>
-      <c r="AV26" s="49"/>
-      <c r="AW26" s="65"/>
+      <c r="AS26" s="47"/>
+      <c r="AT26" s="47"/>
+      <c r="AU26" s="47"/>
+      <c r="AV26" s="47"/>
+      <c r="AW26" s="63"/>
     </row>
     <row r="27" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B27" s="66"/>
-      <c r="C27" s="67"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="68"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="70"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="70"/>
-      <c r="J27" s="70"/>
-      <c r="K27" s="70"/>
-      <c r="L27" s="70"/>
-      <c r="M27" s="70"/>
-      <c r="N27" s="70"/>
-      <c r="O27" s="70"/>
-      <c r="P27" s="70"/>
-      <c r="Q27" s="70"/>
-      <c r="R27" s="70"/>
-      <c r="S27" s="70"/>
-      <c r="T27" s="70"/>
-      <c r="U27" s="70"/>
-      <c r="V27" s="70"/>
-      <c r="W27" s="70"/>
-      <c r="X27" s="70"/>
-      <c r="Y27" s="70"/>
-      <c r="Z27" s="70"/>
-      <c r="AA27" s="70"/>
-      <c r="AB27" s="70"/>
-      <c r="AC27" s="70"/>
-      <c r="AD27" s="70"/>
-      <c r="AE27" s="70"/>
-      <c r="AF27" s="70"/>
-      <c r="AG27" s="74"/>
-      <c r="AH27" s="75"/>
-      <c r="AI27" s="75"/>
-      <c r="AJ27" s="75"/>
-      <c r="AK27" s="76"/>
-      <c r="AL27" s="62"/>
-      <c r="AM27" s="62"/>
-      <c r="AN27" s="62"/>
-      <c r="AO27" s="62"/>
-      <c r="AP27" s="62"/>
-      <c r="AQ27" s="63"/>
-      <c r="AR27" s="64">
+      <c r="B27" s="64"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="66"/>
+      <c r="F27" s="67"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="68"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="68"/>
+      <c r="K27" s="68"/>
+      <c r="L27" s="68"/>
+      <c r="M27" s="68"/>
+      <c r="N27" s="68"/>
+      <c r="O27" s="68"/>
+      <c r="P27" s="68"/>
+      <c r="Q27" s="68"/>
+      <c r="R27" s="68"/>
+      <c r="S27" s="68"/>
+      <c r="T27" s="68"/>
+      <c r="U27" s="68"/>
+      <c r="V27" s="68"/>
+      <c r="W27" s="68"/>
+      <c r="X27" s="68"/>
+      <c r="Y27" s="68"/>
+      <c r="Z27" s="68"/>
+      <c r="AA27" s="68"/>
+      <c r="AB27" s="68"/>
+      <c r="AC27" s="68"/>
+      <c r="AD27" s="68"/>
+      <c r="AE27" s="68"/>
+      <c r="AF27" s="68"/>
+      <c r="AG27" s="72"/>
+      <c r="AH27" s="73"/>
+      <c r="AI27" s="73"/>
+      <c r="AJ27" s="73"/>
+      <c r="AK27" s="74"/>
+      <c r="AL27" s="60"/>
+      <c r="AM27" s="60"/>
+      <c r="AN27" s="60"/>
+      <c r="AO27" s="60"/>
+      <c r="AP27" s="60"/>
+      <c r="AQ27" s="61"/>
+      <c r="AR27" s="62">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AS27" s="49"/>
-      <c r="AT27" s="49"/>
-      <c r="AU27" s="49"/>
-      <c r="AV27" s="49"/>
-      <c r="AW27" s="65"/>
+      <c r="AS27" s="47"/>
+      <c r="AT27" s="47"/>
+      <c r="AU27" s="47"/>
+      <c r="AV27" s="47"/>
+      <c r="AW27" s="63"/>
     </row>
     <row r="28" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B28" s="66"/>
-      <c r="C28" s="67"/>
-      <c r="D28" s="67"/>
-      <c r="E28" s="68"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="70"/>
-      <c r="H28" s="70"/>
-      <c r="I28" s="70"/>
-      <c r="J28" s="70"/>
-      <c r="K28" s="70"/>
-      <c r="L28" s="70"/>
-      <c r="M28" s="70"/>
-      <c r="N28" s="70"/>
-      <c r="O28" s="70"/>
-      <c r="P28" s="70"/>
-      <c r="Q28" s="70"/>
-      <c r="R28" s="70"/>
-      <c r="S28" s="70"/>
-      <c r="T28" s="70"/>
-      <c r="U28" s="70"/>
-      <c r="V28" s="70"/>
-      <c r="W28" s="70"/>
-      <c r="X28" s="70"/>
-      <c r="Y28" s="70"/>
-      <c r="Z28" s="70"/>
-      <c r="AA28" s="70"/>
-      <c r="AB28" s="70"/>
-      <c r="AC28" s="70"/>
-      <c r="AD28" s="70"/>
-      <c r="AE28" s="70"/>
-      <c r="AF28" s="70"/>
-      <c r="AG28" s="74"/>
-      <c r="AH28" s="75"/>
-      <c r="AI28" s="75"/>
-      <c r="AJ28" s="75"/>
-      <c r="AK28" s="76"/>
-      <c r="AL28" s="62"/>
-      <c r="AM28" s="62"/>
-      <c r="AN28" s="62"/>
-      <c r="AO28" s="62"/>
-      <c r="AP28" s="62"/>
-      <c r="AQ28" s="63"/>
-      <c r="AR28" s="64">
+      <c r="B28" s="64"/>
+      <c r="C28" s="65"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="66"/>
+      <c r="F28" s="67"/>
+      <c r="G28" s="68"/>
+      <c r="H28" s="68"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="68"/>
+      <c r="L28" s="68"/>
+      <c r="M28" s="68"/>
+      <c r="N28" s="68"/>
+      <c r="O28" s="68"/>
+      <c r="P28" s="68"/>
+      <c r="Q28" s="68"/>
+      <c r="R28" s="68"/>
+      <c r="S28" s="68"/>
+      <c r="T28" s="68"/>
+      <c r="U28" s="68"/>
+      <c r="V28" s="68"/>
+      <c r="W28" s="68"/>
+      <c r="X28" s="68"/>
+      <c r="Y28" s="68"/>
+      <c r="Z28" s="68"/>
+      <c r="AA28" s="68"/>
+      <c r="AB28" s="68"/>
+      <c r="AC28" s="68"/>
+      <c r="AD28" s="68"/>
+      <c r="AE28" s="68"/>
+      <c r="AF28" s="68"/>
+      <c r="AG28" s="72"/>
+      <c r="AH28" s="73"/>
+      <c r="AI28" s="73"/>
+      <c r="AJ28" s="73"/>
+      <c r="AK28" s="74"/>
+      <c r="AL28" s="60"/>
+      <c r="AM28" s="60"/>
+      <c r="AN28" s="60"/>
+      <c r="AO28" s="60"/>
+      <c r="AP28" s="60"/>
+      <c r="AQ28" s="61"/>
+      <c r="AR28" s="62">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AS28" s="49"/>
-      <c r="AT28" s="49"/>
-      <c r="AU28" s="49"/>
-      <c r="AV28" s="49"/>
-      <c r="AW28" s="65"/>
+      <c r="AS28" s="47"/>
+      <c r="AT28" s="47"/>
+      <c r="AU28" s="47"/>
+      <c r="AV28" s="47"/>
+      <c r="AW28" s="63"/>
     </row>
     <row r="29" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B29" s="66"/>
-      <c r="C29" s="67"/>
-      <c r="D29" s="67"/>
-      <c r="E29" s="68"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="70"/>
-      <c r="H29" s="70"/>
-      <c r="I29" s="70"/>
-      <c r="J29" s="70"/>
-      <c r="K29" s="70"/>
-      <c r="L29" s="70"/>
-      <c r="M29" s="70"/>
-      <c r="N29" s="70"/>
-      <c r="O29" s="70"/>
-      <c r="P29" s="70"/>
-      <c r="Q29" s="70"/>
-      <c r="R29" s="70"/>
-      <c r="S29" s="70"/>
-      <c r="T29" s="70"/>
-      <c r="U29" s="70"/>
-      <c r="V29" s="70"/>
-      <c r="W29" s="70"/>
-      <c r="X29" s="70"/>
-      <c r="Y29" s="70"/>
-      <c r="Z29" s="70"/>
-      <c r="AA29" s="70"/>
-      <c r="AB29" s="70"/>
-      <c r="AC29" s="70"/>
-      <c r="AD29" s="70"/>
-      <c r="AE29" s="70"/>
-      <c r="AF29" s="70"/>
-      <c r="AG29" s="74"/>
-      <c r="AH29" s="75"/>
-      <c r="AI29" s="75"/>
-      <c r="AJ29" s="75"/>
-      <c r="AK29" s="76"/>
-      <c r="AL29" s="62"/>
-      <c r="AM29" s="62"/>
-      <c r="AN29" s="62"/>
-      <c r="AO29" s="62"/>
-      <c r="AP29" s="62"/>
-      <c r="AQ29" s="63"/>
-      <c r="AR29" s="64">
+      <c r="B29" s="64"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="66"/>
+      <c r="F29" s="67"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="68"/>
+      <c r="K29" s="68"/>
+      <c r="L29" s="68"/>
+      <c r="M29" s="68"/>
+      <c r="N29" s="68"/>
+      <c r="O29" s="68"/>
+      <c r="P29" s="68"/>
+      <c r="Q29" s="68"/>
+      <c r="R29" s="68"/>
+      <c r="S29" s="68"/>
+      <c r="T29" s="68"/>
+      <c r="U29" s="68"/>
+      <c r="V29" s="68"/>
+      <c r="W29" s="68"/>
+      <c r="X29" s="68"/>
+      <c r="Y29" s="68"/>
+      <c r="Z29" s="68"/>
+      <c r="AA29" s="68"/>
+      <c r="AB29" s="68"/>
+      <c r="AC29" s="68"/>
+      <c r="AD29" s="68"/>
+      <c r="AE29" s="68"/>
+      <c r="AF29" s="68"/>
+      <c r="AG29" s="72"/>
+      <c r="AH29" s="73"/>
+      <c r="AI29" s="73"/>
+      <c r="AJ29" s="73"/>
+      <c r="AK29" s="74"/>
+      <c r="AL29" s="60"/>
+      <c r="AM29" s="60"/>
+      <c r="AN29" s="60"/>
+      <c r="AO29" s="60"/>
+      <c r="AP29" s="60"/>
+      <c r="AQ29" s="61"/>
+      <c r="AR29" s="62">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AS29" s="49"/>
-      <c r="AT29" s="49"/>
-      <c r="AU29" s="49"/>
-      <c r="AV29" s="49"/>
-      <c r="AW29" s="65"/>
+      <c r="AS29" s="47"/>
+      <c r="AT29" s="47"/>
+      <c r="AU29" s="47"/>
+      <c r="AV29" s="47"/>
+      <c r="AW29" s="63"/>
     </row>
     <row r="30" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B30" s="66"/>
-      <c r="C30" s="67"/>
-      <c r="D30" s="67"/>
-      <c r="E30" s="68"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="70"/>
-      <c r="H30" s="70"/>
-      <c r="I30" s="70"/>
-      <c r="J30" s="70"/>
-      <c r="K30" s="70"/>
-      <c r="L30" s="70"/>
-      <c r="M30" s="70"/>
-      <c r="N30" s="70"/>
-      <c r="O30" s="70"/>
-      <c r="P30" s="70"/>
-      <c r="Q30" s="70"/>
-      <c r="R30" s="70"/>
-      <c r="S30" s="70"/>
-      <c r="T30" s="70"/>
-      <c r="U30" s="70"/>
-      <c r="V30" s="70"/>
-      <c r="W30" s="70"/>
-      <c r="X30" s="70"/>
-      <c r="Y30" s="70"/>
-      <c r="Z30" s="70"/>
-      <c r="AA30" s="70"/>
-      <c r="AB30" s="70"/>
-      <c r="AC30" s="70"/>
-      <c r="AD30" s="70"/>
-      <c r="AE30" s="70"/>
-      <c r="AF30" s="70"/>
-      <c r="AG30" s="74"/>
-      <c r="AH30" s="75"/>
-      <c r="AI30" s="75"/>
-      <c r="AJ30" s="75"/>
-      <c r="AK30" s="76"/>
-      <c r="AL30" s="62"/>
-      <c r="AM30" s="62"/>
-      <c r="AN30" s="62"/>
-      <c r="AO30" s="62"/>
-      <c r="AP30" s="62"/>
-      <c r="AQ30" s="63"/>
-      <c r="AR30" s="64">
+      <c r="B30" s="64"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="66"/>
+      <c r="F30" s="67"/>
+      <c r="G30" s="68"/>
+      <c r="H30" s="68"/>
+      <c r="I30" s="68"/>
+      <c r="J30" s="68"/>
+      <c r="K30" s="68"/>
+      <c r="L30" s="68"/>
+      <c r="M30" s="68"/>
+      <c r="N30" s="68"/>
+      <c r="O30" s="68"/>
+      <c r="P30" s="68"/>
+      <c r="Q30" s="68"/>
+      <c r="R30" s="68"/>
+      <c r="S30" s="68"/>
+      <c r="T30" s="68"/>
+      <c r="U30" s="68"/>
+      <c r="V30" s="68"/>
+      <c r="W30" s="68"/>
+      <c r="X30" s="68"/>
+      <c r="Y30" s="68"/>
+      <c r="Z30" s="68"/>
+      <c r="AA30" s="68"/>
+      <c r="AB30" s="68"/>
+      <c r="AC30" s="68"/>
+      <c r="AD30" s="68"/>
+      <c r="AE30" s="68"/>
+      <c r="AF30" s="68"/>
+      <c r="AG30" s="72"/>
+      <c r="AH30" s="73"/>
+      <c r="AI30" s="73"/>
+      <c r="AJ30" s="73"/>
+      <c r="AK30" s="74"/>
+      <c r="AL30" s="60"/>
+      <c r="AM30" s="60"/>
+      <c r="AN30" s="60"/>
+      <c r="AO30" s="60"/>
+      <c r="AP30" s="60"/>
+      <c r="AQ30" s="61"/>
+      <c r="AR30" s="62">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AS30" s="49"/>
-      <c r="AT30" s="49"/>
-      <c r="AU30" s="49"/>
-      <c r="AV30" s="49"/>
-      <c r="AW30" s="65"/>
+      <c r="AS30" s="47"/>
+      <c r="AT30" s="47"/>
+      <c r="AU30" s="47"/>
+      <c r="AV30" s="47"/>
+      <c r="AW30" s="63"/>
     </row>
     <row r="31" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B31" s="66"/>
-      <c r="C31" s="67"/>
-      <c r="D31" s="67"/>
-      <c r="E31" s="68"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="70"/>
-      <c r="H31" s="70"/>
-      <c r="I31" s="70"/>
-      <c r="J31" s="70"/>
-      <c r="K31" s="70"/>
-      <c r="L31" s="70"/>
-      <c r="M31" s="70"/>
-      <c r="N31" s="70"/>
-      <c r="O31" s="70"/>
-      <c r="P31" s="70"/>
-      <c r="Q31" s="70"/>
-      <c r="R31" s="70"/>
-      <c r="S31" s="70"/>
-      <c r="T31" s="70"/>
-      <c r="U31" s="70"/>
-      <c r="V31" s="70"/>
-      <c r="W31" s="70"/>
-      <c r="X31" s="70"/>
-      <c r="Y31" s="70"/>
-      <c r="Z31" s="70"/>
-      <c r="AA31" s="70"/>
-      <c r="AB31" s="70"/>
-      <c r="AC31" s="70"/>
-      <c r="AD31" s="70"/>
-      <c r="AE31" s="70"/>
-      <c r="AF31" s="70"/>
-      <c r="AG31" s="74"/>
-      <c r="AH31" s="75"/>
-      <c r="AI31" s="75"/>
-      <c r="AJ31" s="75"/>
-      <c r="AK31" s="76"/>
-      <c r="AL31" s="62"/>
-      <c r="AM31" s="62"/>
-      <c r="AN31" s="62"/>
-      <c r="AO31" s="62"/>
-      <c r="AP31" s="62"/>
-      <c r="AQ31" s="63"/>
-      <c r="AR31" s="64">
+      <c r="B31" s="64"/>
+      <c r="C31" s="65"/>
+      <c r="D31" s="65"/>
+      <c r="E31" s="66"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="68"/>
+      <c r="H31" s="68"/>
+      <c r="I31" s="68"/>
+      <c r="J31" s="68"/>
+      <c r="K31" s="68"/>
+      <c r="L31" s="68"/>
+      <c r="M31" s="68"/>
+      <c r="N31" s="68"/>
+      <c r="O31" s="68"/>
+      <c r="P31" s="68"/>
+      <c r="Q31" s="68"/>
+      <c r="R31" s="68"/>
+      <c r="S31" s="68"/>
+      <c r="T31" s="68"/>
+      <c r="U31" s="68"/>
+      <c r="V31" s="68"/>
+      <c r="W31" s="68"/>
+      <c r="X31" s="68"/>
+      <c r="Y31" s="68"/>
+      <c r="Z31" s="68"/>
+      <c r="AA31" s="68"/>
+      <c r="AB31" s="68"/>
+      <c r="AC31" s="68"/>
+      <c r="AD31" s="68"/>
+      <c r="AE31" s="68"/>
+      <c r="AF31" s="68"/>
+      <c r="AG31" s="72"/>
+      <c r="AH31" s="73"/>
+      <c r="AI31" s="73"/>
+      <c r="AJ31" s="73"/>
+      <c r="AK31" s="74"/>
+      <c r="AL31" s="60"/>
+      <c r="AM31" s="60"/>
+      <c r="AN31" s="60"/>
+      <c r="AO31" s="60"/>
+      <c r="AP31" s="60"/>
+      <c r="AQ31" s="61"/>
+      <c r="AR31" s="62">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AS31" s="49"/>
-      <c r="AT31" s="49"/>
-      <c r="AU31" s="49"/>
-      <c r="AV31" s="49"/>
-      <c r="AW31" s="65"/>
+      <c r="AS31" s="47"/>
+      <c r="AT31" s="47"/>
+      <c r="AU31" s="47"/>
+      <c r="AV31" s="47"/>
+      <c r="AW31" s="63"/>
     </row>
     <row r="32" spans="2:49" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B32" s="66"/>
-      <c r="C32" s="67"/>
-      <c r="D32" s="67"/>
-      <c r="E32" s="68"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="36"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="36"/>
-      <c r="K32" s="36"/>
-      <c r="L32" s="36"/>
-      <c r="M32" s="36"/>
-      <c r="N32" s="36"/>
-      <c r="O32" s="36"/>
-      <c r="P32" s="36"/>
-      <c r="Q32" s="36"/>
-      <c r="R32" s="36"/>
-      <c r="S32" s="36"/>
-      <c r="T32" s="36"/>
-      <c r="U32" s="36"/>
-      <c r="V32" s="36"/>
-      <c r="W32" s="36"/>
-      <c r="X32" s="36"/>
-      <c r="Y32" s="36"/>
-      <c r="Z32" s="36"/>
-      <c r="AA32" s="36"/>
-      <c r="AB32" s="36"/>
-      <c r="AC32" s="36"/>
-      <c r="AD32" s="36"/>
-      <c r="AE32" s="36"/>
-      <c r="AF32" s="36"/>
+      <c r="B32" s="64"/>
+      <c r="C32" s="65"/>
+      <c r="D32" s="65"/>
+      <c r="E32" s="66"/>
+      <c r="F32" s="72"/>
+      <c r="G32" s="73"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73"/>
+      <c r="J32" s="73"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="73"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="73"/>
+      <c r="O32" s="73"/>
+      <c r="P32" s="73"/>
+      <c r="Q32" s="73"/>
+      <c r="R32" s="73"/>
+      <c r="S32" s="73"/>
+      <c r="T32" s="73"/>
+      <c r="U32" s="73"/>
+      <c r="V32" s="73"/>
+      <c r="W32" s="73"/>
+      <c r="X32" s="73"/>
+      <c r="Y32" s="73"/>
+      <c r="Z32" s="73"/>
+      <c r="AA32" s="73"/>
+      <c r="AB32" s="73"/>
+      <c r="AC32" s="73"/>
+      <c r="AD32" s="73"/>
+      <c r="AE32" s="73"/>
+      <c r="AF32" s="74"/>
       <c r="AG32" s="32"/>
       <c r="AH32" s="16"/>
       <c r="AI32" s="16"/>
       <c r="AJ32" s="16"/>
-      <c r="AK32" s="40"/>
-      <c r="AL32" s="38"/>
-      <c r="AM32" s="38"/>
-      <c r="AN32" s="38"/>
-      <c r="AO32" s="38"/>
-      <c r="AP32" s="38"/>
-      <c r="AQ32" s="39"/>
+      <c r="AK32" s="38"/>
+      <c r="AL32" s="36"/>
+      <c r="AM32" s="36"/>
+      <c r="AN32" s="36"/>
+      <c r="AO32" s="36"/>
+      <c r="AP32" s="36"/>
+      <c r="AQ32" s="37"/>
       <c r="AR32" s="33"/>
       <c r="AS32" s="34"/>
       <c r="AT32" s="34"/>
@@ -3675,48 +3672,48 @@
       <c r="AW32" s="35"/>
     </row>
     <row r="33" spans="2:54" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B33" s="66"/>
-      <c r="C33" s="67"/>
-      <c r="D33" s="67"/>
-      <c r="E33" s="68"/>
-      <c r="F33" s="37"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
-      <c r="J33" s="36"/>
-      <c r="K33" s="36"/>
-      <c r="L33" s="36"/>
-      <c r="M33" s="36"/>
-      <c r="N33" s="36"/>
-      <c r="O33" s="36"/>
-      <c r="P33" s="36"/>
-      <c r="Q33" s="36"/>
-      <c r="R33" s="36"/>
-      <c r="S33" s="36"/>
-      <c r="T33" s="36"/>
-      <c r="U33" s="36"/>
-      <c r="V33" s="36"/>
-      <c r="W33" s="36"/>
-      <c r="X33" s="36"/>
-      <c r="Y33" s="36"/>
-      <c r="Z33" s="36"/>
-      <c r="AA33" s="36"/>
-      <c r="AB33" s="36"/>
-      <c r="AC33" s="36"/>
-      <c r="AD33" s="36"/>
-      <c r="AE33" s="36"/>
-      <c r="AF33" s="36"/>
+      <c r="B33" s="64"/>
+      <c r="C33" s="65"/>
+      <c r="D33" s="65"/>
+      <c r="E33" s="66"/>
+      <c r="F33" s="72"/>
+      <c r="G33" s="73"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73"/>
+      <c r="J33" s="73"/>
+      <c r="K33" s="73"/>
+      <c r="L33" s="73"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="73"/>
+      <c r="O33" s="73"/>
+      <c r="P33" s="73"/>
+      <c r="Q33" s="73"/>
+      <c r="R33" s="73"/>
+      <c r="S33" s="73"/>
+      <c r="T33" s="73"/>
+      <c r="U33" s="73"/>
+      <c r="V33" s="73"/>
+      <c r="W33" s="73"/>
+      <c r="X33" s="73"/>
+      <c r="Y33" s="73"/>
+      <c r="Z33" s="73"/>
+      <c r="AA33" s="73"/>
+      <c r="AB33" s="73"/>
+      <c r="AC33" s="73"/>
+      <c r="AD33" s="73"/>
+      <c r="AE33" s="73"/>
+      <c r="AF33" s="74"/>
       <c r="AG33" s="32"/>
       <c r="AH33" s="16"/>
       <c r="AI33" s="16"/>
       <c r="AJ33" s="16"/>
-      <c r="AK33" s="40"/>
-      <c r="AL33" s="38"/>
-      <c r="AM33" s="38"/>
-      <c r="AN33" s="38"/>
-      <c r="AO33" s="38"/>
-      <c r="AP33" s="38"/>
-      <c r="AQ33" s="39"/>
+      <c r="AK33" s="38"/>
+      <c r="AL33" s="36"/>
+      <c r="AM33" s="36"/>
+      <c r="AN33" s="36"/>
+      <c r="AO33" s="36"/>
+      <c r="AP33" s="36"/>
+      <c r="AQ33" s="37"/>
       <c r="AR33" s="33"/>
       <c r="AS33" s="34"/>
       <c r="AT33" s="34"/>
@@ -3725,168 +3722,168 @@
       <c r="AW33" s="35"/>
     </row>
     <row r="34" spans="2:54" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B34" s="66"/>
-      <c r="C34" s="67"/>
-      <c r="D34" s="67"/>
-      <c r="E34" s="68"/>
-      <c r="F34" s="69"/>
-      <c r="G34" s="70"/>
-      <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
-      <c r="J34" s="70"/>
-      <c r="K34" s="70"/>
-      <c r="L34" s="70"/>
-      <c r="M34" s="70"/>
-      <c r="N34" s="70"/>
-      <c r="O34" s="70"/>
-      <c r="P34" s="70"/>
-      <c r="Q34" s="70"/>
-      <c r="R34" s="70"/>
-      <c r="S34" s="70"/>
-      <c r="T34" s="70"/>
-      <c r="U34" s="70"/>
-      <c r="V34" s="70"/>
-      <c r="W34" s="70"/>
-      <c r="X34" s="70"/>
-      <c r="Y34" s="70"/>
-      <c r="Z34" s="70"/>
-      <c r="AA34" s="70"/>
-      <c r="AB34" s="70"/>
-      <c r="AC34" s="70"/>
-      <c r="AD34" s="70"/>
-      <c r="AE34" s="70"/>
-      <c r="AF34" s="70"/>
-      <c r="AG34" s="74"/>
-      <c r="AH34" s="75"/>
-      <c r="AI34" s="75"/>
-      <c r="AJ34" s="75"/>
-      <c r="AK34" s="76"/>
-      <c r="AL34" s="62"/>
-      <c r="AM34" s="62"/>
-      <c r="AN34" s="62"/>
-      <c r="AO34" s="62"/>
-      <c r="AP34" s="62"/>
-      <c r="AQ34" s="63"/>
-      <c r="AR34" s="64">
+      <c r="B34" s="64"/>
+      <c r="C34" s="65"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="66"/>
+      <c r="F34" s="67"/>
+      <c r="G34" s="68"/>
+      <c r="H34" s="68"/>
+      <c r="I34" s="68"/>
+      <c r="J34" s="68"/>
+      <c r="K34" s="68"/>
+      <c r="L34" s="68"/>
+      <c r="M34" s="68"/>
+      <c r="N34" s="68"/>
+      <c r="O34" s="68"/>
+      <c r="P34" s="68"/>
+      <c r="Q34" s="68"/>
+      <c r="R34" s="68"/>
+      <c r="S34" s="68"/>
+      <c r="T34" s="68"/>
+      <c r="U34" s="68"/>
+      <c r="V34" s="68"/>
+      <c r="W34" s="68"/>
+      <c r="X34" s="68"/>
+      <c r="Y34" s="68"/>
+      <c r="Z34" s="68"/>
+      <c r="AA34" s="68"/>
+      <c r="AB34" s="68"/>
+      <c r="AC34" s="68"/>
+      <c r="AD34" s="68"/>
+      <c r="AE34" s="68"/>
+      <c r="AF34" s="68"/>
+      <c r="AG34" s="72"/>
+      <c r="AH34" s="73"/>
+      <c r="AI34" s="73"/>
+      <c r="AJ34" s="73"/>
+      <c r="AK34" s="74"/>
+      <c r="AL34" s="60"/>
+      <c r="AM34" s="60"/>
+      <c r="AN34" s="60"/>
+      <c r="AO34" s="60"/>
+      <c r="AP34" s="60"/>
+      <c r="AQ34" s="61"/>
+      <c r="AR34" s="62">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AS34" s="49"/>
-      <c r="AT34" s="49"/>
-      <c r="AU34" s="49"/>
-      <c r="AV34" s="49"/>
-      <c r="AW34" s="65"/>
+      <c r="AS34" s="47"/>
+      <c r="AT34" s="47"/>
+      <c r="AU34" s="47"/>
+      <c r="AV34" s="47"/>
+      <c r="AW34" s="63"/>
     </row>
     <row r="35" spans="2:54" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="B35" s="66"/>
-      <c r="C35" s="67"/>
-      <c r="D35" s="67"/>
-      <c r="E35" s="68"/>
-      <c r="F35" s="69"/>
-      <c r="G35" s="70"/>
-      <c r="H35" s="70"/>
-      <c r="I35" s="70"/>
-      <c r="J35" s="70"/>
-      <c r="K35" s="70"/>
-      <c r="L35" s="70"/>
-      <c r="M35" s="70"/>
-      <c r="N35" s="70"/>
-      <c r="O35" s="70"/>
-      <c r="P35" s="70"/>
-      <c r="Q35" s="70"/>
-      <c r="R35" s="70"/>
-      <c r="S35" s="70"/>
-      <c r="T35" s="70"/>
-      <c r="U35" s="70"/>
-      <c r="V35" s="70"/>
-      <c r="W35" s="70"/>
-      <c r="X35" s="70"/>
-      <c r="Y35" s="70"/>
-      <c r="Z35" s="70"/>
-      <c r="AA35" s="70"/>
-      <c r="AB35" s="70"/>
-      <c r="AC35" s="70"/>
-      <c r="AD35" s="70"/>
-      <c r="AE35" s="70"/>
-      <c r="AF35" s="70"/>
-      <c r="AG35" s="71"/>
-      <c r="AH35" s="72"/>
-      <c r="AI35" s="72"/>
-      <c r="AJ35" s="72"/>
-      <c r="AK35" s="73"/>
-      <c r="AL35" s="62"/>
-      <c r="AM35" s="62"/>
-      <c r="AN35" s="62"/>
-      <c r="AO35" s="62"/>
-      <c r="AP35" s="62"/>
-      <c r="AQ35" s="63"/>
-      <c r="AR35" s="64">
+      <c r="B35" s="64"/>
+      <c r="C35" s="65"/>
+      <c r="D35" s="65"/>
+      <c r="E35" s="66"/>
+      <c r="F35" s="67"/>
+      <c r="G35" s="68"/>
+      <c r="H35" s="68"/>
+      <c r="I35" s="68"/>
+      <c r="J35" s="68"/>
+      <c r="K35" s="68"/>
+      <c r="L35" s="68"/>
+      <c r="M35" s="68"/>
+      <c r="N35" s="68"/>
+      <c r="O35" s="68"/>
+      <c r="P35" s="68"/>
+      <c r="Q35" s="68"/>
+      <c r="R35" s="68"/>
+      <c r="S35" s="68"/>
+      <c r="T35" s="68"/>
+      <c r="U35" s="68"/>
+      <c r="V35" s="68"/>
+      <c r="W35" s="68"/>
+      <c r="X35" s="68"/>
+      <c r="Y35" s="68"/>
+      <c r="Z35" s="68"/>
+      <c r="AA35" s="68"/>
+      <c r="AB35" s="68"/>
+      <c r="AC35" s="68"/>
+      <c r="AD35" s="68"/>
+      <c r="AE35" s="68"/>
+      <c r="AF35" s="68"/>
+      <c r="AG35" s="69"/>
+      <c r="AH35" s="70"/>
+      <c r="AI35" s="70"/>
+      <c r="AJ35" s="70"/>
+      <c r="AK35" s="71"/>
+      <c r="AL35" s="60"/>
+      <c r="AM35" s="60"/>
+      <c r="AN35" s="60"/>
+      <c r="AO35" s="60"/>
+      <c r="AP35" s="60"/>
+      <c r="AQ35" s="61"/>
+      <c r="AR35" s="62">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AS35" s="49"/>
-      <c r="AT35" s="49"/>
-      <c r="AU35" s="49"/>
-      <c r="AV35" s="49"/>
-      <c r="AW35" s="65"/>
+      <c r="AS35" s="47"/>
+      <c r="AT35" s="47"/>
+      <c r="AU35" s="47"/>
+      <c r="AV35" s="47"/>
+      <c r="AW35" s="63"/>
     </row>
     <row r="36" spans="2:54" s="4" customFormat="1" ht="20.5" customHeight="1">
-      <c r="B36" s="54" t="str">
+      <c r="B36" s="52" t="str">
         <f>"(  -"&amp;BAHTTEXT(AR38)&amp;"-  )"</f>
         <v>(  -ศูนย์บาทถ้วน-  )</v>
       </c>
-      <c r="C36" s="55"/>
-      <c r="D36" s="55"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="55"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="55"/>
-      <c r="J36" s="55"/>
-      <c r="K36" s="55"/>
-      <c r="L36" s="55"/>
-      <c r="M36" s="55"/>
-      <c r="N36" s="55"/>
-      <c r="O36" s="55"/>
-      <c r="P36" s="55"/>
-      <c r="Q36" s="55"/>
-      <c r="R36" s="55"/>
-      <c r="S36" s="55"/>
-      <c r="T36" s="55"/>
-      <c r="U36" s="55"/>
-      <c r="V36" s="55"/>
-      <c r="W36" s="55"/>
-      <c r="X36" s="55"/>
-      <c r="Y36" s="55"/>
-      <c r="Z36" s="55"/>
-      <c r="AA36" s="55"/>
-      <c r="AB36" s="55"/>
-      <c r="AC36" s="55"/>
-      <c r="AD36" s="55"/>
-      <c r="AE36" s="55"/>
-      <c r="AF36" s="56"/>
-      <c r="AG36" s="57" t="s">
+      <c r="C36" s="53"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53"/>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="53"/>
+      <c r="L36" s="53"/>
+      <c r="M36" s="53"/>
+      <c r="N36" s="53"/>
+      <c r="O36" s="53"/>
+      <c r="P36" s="53"/>
+      <c r="Q36" s="53"/>
+      <c r="R36" s="53"/>
+      <c r="S36" s="53"/>
+      <c r="T36" s="53"/>
+      <c r="U36" s="53"/>
+      <c r="V36" s="53"/>
+      <c r="W36" s="53"/>
+      <c r="X36" s="53"/>
+      <c r="Y36" s="53"/>
+      <c r="Z36" s="53"/>
+      <c r="AA36" s="53"/>
+      <c r="AB36" s="53"/>
+      <c r="AC36" s="53"/>
+      <c r="AD36" s="53"/>
+      <c r="AE36" s="53"/>
+      <c r="AF36" s="54"/>
+      <c r="AG36" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="AH36" s="48"/>
-      <c r="AI36" s="48"/>
-      <c r="AJ36" s="48"/>
-      <c r="AK36" s="48"/>
-      <c r="AL36" s="58"/>
-      <c r="AM36" s="58"/>
-      <c r="AN36" s="58"/>
-      <c r="AO36" s="58"/>
-      <c r="AP36" s="58"/>
-      <c r="AQ36" s="58"/>
-      <c r="AR36" s="59">
+      <c r="AH36" s="46"/>
+      <c r="AI36" s="46"/>
+      <c r="AJ36" s="46"/>
+      <c r="AK36" s="46"/>
+      <c r="AL36" s="56"/>
+      <c r="AM36" s="56"/>
+      <c r="AN36" s="56"/>
+      <c r="AO36" s="56"/>
+      <c r="AP36" s="56"/>
+      <c r="AQ36" s="56"/>
+      <c r="AR36" s="57">
         <f>AR38*100/107</f>
         <v>0</v>
       </c>
-      <c r="AS36" s="59"/>
-      <c r="AT36" s="59"/>
-      <c r="AU36" s="59"/>
-      <c r="AV36" s="59"/>
-      <c r="AW36" s="59"/>
+      <c r="AS36" s="57"/>
+      <c r="AT36" s="57"/>
+      <c r="AU36" s="57"/>
+      <c r="AV36" s="57"/>
+      <c r="AW36" s="57"/>
     </row>
     <row r="37" spans="2:54" s="4" customFormat="1" ht="20.5" customHeight="1">
       <c r="B37" s="16"/>
@@ -3920,28 +3917,28 @@
       <c r="AD37" s="16"/>
       <c r="AE37" s="16"/>
       <c r="AF37" s="16"/>
-      <c r="AG37" s="57" t="s">
+      <c r="AG37" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="AH37" s="48"/>
-      <c r="AI37" s="48"/>
-      <c r="AJ37" s="48"/>
-      <c r="AK37" s="48"/>
-      <c r="AL37" s="48"/>
-      <c r="AM37" s="48"/>
-      <c r="AN37" s="48"/>
-      <c r="AO37" s="48"/>
-      <c r="AP37" s="48"/>
-      <c r="AQ37" s="48"/>
-      <c r="AR37" s="59">
+      <c r="AH37" s="46"/>
+      <c r="AI37" s="46"/>
+      <c r="AJ37" s="46"/>
+      <c r="AK37" s="46"/>
+      <c r="AL37" s="46"/>
+      <c r="AM37" s="46"/>
+      <c r="AN37" s="46"/>
+      <c r="AO37" s="46"/>
+      <c r="AP37" s="46"/>
+      <c r="AQ37" s="46"/>
+      <c r="AR37" s="57">
         <f>AR38-AR36</f>
         <v>0</v>
       </c>
-      <c r="AS37" s="59"/>
-      <c r="AT37" s="59"/>
-      <c r="AU37" s="59"/>
-      <c r="AV37" s="59"/>
-      <c r="AW37" s="59"/>
+      <c r="AS37" s="57"/>
+      <c r="AT37" s="57"/>
+      <c r="AU37" s="57"/>
+      <c r="AV37" s="57"/>
+      <c r="AW37" s="57"/>
     </row>
     <row r="38" spans="2:54" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="B38" s="6"/>
@@ -3975,28 +3972,28 @@
       <c r="AD38" s="6"/>
       <c r="AE38" s="6"/>
       <c r="AF38" s="6"/>
-      <c r="AG38" s="60" t="s">
+      <c r="AG38" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="AH38" s="61"/>
-      <c r="AI38" s="61"/>
-      <c r="AJ38" s="61"/>
-      <c r="AK38" s="61"/>
-      <c r="AL38" s="61"/>
-      <c r="AM38" s="61"/>
-      <c r="AN38" s="61"/>
-      <c r="AO38" s="61"/>
-      <c r="AP38" s="61"/>
-      <c r="AQ38" s="61"/>
-      <c r="AR38" s="59">
+      <c r="AH38" s="59"/>
+      <c r="AI38" s="59"/>
+      <c r="AJ38" s="59"/>
+      <c r="AK38" s="59"/>
+      <c r="AL38" s="59"/>
+      <c r="AM38" s="59"/>
+      <c r="AN38" s="59"/>
+      <c r="AO38" s="59"/>
+      <c r="AP38" s="59"/>
+      <c r="AQ38" s="59"/>
+      <c r="AR38" s="57">
         <f>SUM(AR14:AW34)</f>
         <v>0</v>
       </c>
-      <c r="AS38" s="59"/>
-      <c r="AT38" s="59"/>
-      <c r="AU38" s="59"/>
-      <c r="AV38" s="59"/>
-      <c r="AW38" s="59"/>
+      <c r="AS38" s="57"/>
+      <c r="AT38" s="57"/>
+      <c r="AU38" s="57"/>
+      <c r="AV38" s="57"/>
+      <c r="AW38" s="57"/>
     </row>
     <row r="39" spans="2:54" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="B39" s="17"/>
@@ -4036,23 +4033,23 @@
       <c r="AD39" s="17"/>
       <c r="AE39" s="17"/>
       <c r="AF39" s="17"/>
-      <c r="AG39" s="48"/>
-      <c r="AH39" s="48"/>
-      <c r="AI39" s="48"/>
-      <c r="AJ39" s="48"/>
-      <c r="AK39" s="48"/>
-      <c r="AL39" s="48"/>
-      <c r="AM39" s="48"/>
-      <c r="AN39" s="48"/>
-      <c r="AO39" s="48"/>
-      <c r="AP39" s="48"/>
-      <c r="AQ39" s="48"/>
-      <c r="AR39" s="49"/>
-      <c r="AS39" s="49"/>
-      <c r="AT39" s="49"/>
-      <c r="AU39" s="49"/>
-      <c r="AV39" s="49"/>
-      <c r="AW39" s="49"/>
+      <c r="AG39" s="46"/>
+      <c r="AH39" s="46"/>
+      <c r="AI39" s="46"/>
+      <c r="AJ39" s="46"/>
+      <c r="AK39" s="46"/>
+      <c r="AL39" s="46"/>
+      <c r="AM39" s="46"/>
+      <c r="AN39" s="46"/>
+      <c r="AO39" s="46"/>
+      <c r="AP39" s="46"/>
+      <c r="AQ39" s="46"/>
+      <c r="AR39" s="47"/>
+      <c r="AS39" s="47"/>
+      <c r="AT39" s="47"/>
+      <c r="AU39" s="47"/>
+      <c r="AV39" s="47"/>
+      <c r="AW39" s="47"/>
     </row>
     <row r="40" spans="2:54" ht="12.5" customHeight="1">
       <c r="D40" s="29" t="s">
@@ -4115,12 +4112,12 @@
       </c>
       <c r="Q41" s="7"/>
       <c r="R41" s="7"/>
-      <c r="S41" s="50"/>
-      <c r="T41" s="50"/>
-      <c r="U41" s="44" t="s">
+      <c r="S41" s="48"/>
+      <c r="T41" s="48"/>
+      <c r="U41" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="V41" s="44"/>
+      <c r="V41" s="42"/>
       <c r="W41" s="20"/>
       <c r="X41" s="20"/>
       <c r="Y41" s="30"/>
@@ -4247,66 +4244,66 @@
       <c r="AD43" s="13"/>
       <c r="AE43" s="13"/>
       <c r="AF43" s="13"/>
-      <c r="AG43" s="51"/>
-      <c r="AH43" s="51"/>
-      <c r="AI43" s="51"/>
-      <c r="AJ43" s="51"/>
+      <c r="AG43" s="49"/>
+      <c r="AH43" s="49"/>
+      <c r="AI43" s="49"/>
+      <c r="AJ43" s="49"/>
       <c r="AK43" s="13"/>
       <c r="AL43" s="13"/>
       <c r="AM43" s="13"/>
       <c r="AN43" s="13"/>
     </row>
     <row r="44" spans="2:54" ht="12.5" customHeight="1">
-      <c r="B44" s="52" t="s">
+      <c r="B44" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="53"/>
-      <c r="D44" s="53"/>
-      <c r="E44" s="53"/>
-      <c r="F44" s="53"/>
-      <c r="G44" s="53"/>
-      <c r="H44" s="53"/>
-      <c r="I44" s="53"/>
-      <c r="J44" s="53"/>
-      <c r="K44" s="53"/>
-      <c r="L44" s="53"/>
-      <c r="M44" s="53"/>
-      <c r="N44" s="53"/>
-      <c r="O44" s="53"/>
-      <c r="P44" s="53"/>
-      <c r="Q44" s="53"/>
-      <c r="R44" s="53"/>
-      <c r="S44" s="53"/>
-      <c r="T44" s="53"/>
-      <c r="U44" s="53"/>
-      <c r="V44" s="53"/>
-      <c r="W44" s="53"/>
-      <c r="X44" s="53"/>
-      <c r="Y44" s="53"/>
-      <c r="Z44" s="53"/>
-      <c r="AA44" s="53"/>
-      <c r="AB44" s="53"/>
-      <c r="AC44" s="53"/>
-      <c r="AD44" s="53"/>
-      <c r="AE44" s="53"/>
-      <c r="AF44" s="53"/>
-      <c r="AG44" s="53"/>
-      <c r="AH44" s="53"/>
-      <c r="AI44" s="53"/>
-      <c r="AJ44" s="53"/>
-      <c r="AK44" s="53"/>
-      <c r="AL44" s="53"/>
-      <c r="AM44" s="53"/>
-      <c r="AN44" s="53"/>
-      <c r="AO44" s="53"/>
-      <c r="AP44" s="53"/>
-      <c r="AQ44" s="53"/>
-      <c r="AR44" s="53"/>
-      <c r="AS44" s="53"/>
-      <c r="AT44" s="53"/>
-      <c r="AU44" s="53"/>
-      <c r="AV44" s="53"/>
-      <c r="AW44" s="53"/>
+      <c r="C44" s="51"/>
+      <c r="D44" s="51"/>
+      <c r="E44" s="51"/>
+      <c r="F44" s="51"/>
+      <c r="G44" s="51"/>
+      <c r="H44" s="51"/>
+      <c r="I44" s="51"/>
+      <c r="J44" s="51"/>
+      <c r="K44" s="51"/>
+      <c r="L44" s="51"/>
+      <c r="M44" s="51"/>
+      <c r="N44" s="51"/>
+      <c r="O44" s="51"/>
+      <c r="P44" s="51"/>
+      <c r="Q44" s="51"/>
+      <c r="R44" s="51"/>
+      <c r="S44" s="51"/>
+      <c r="T44" s="51"/>
+      <c r="U44" s="51"/>
+      <c r="V44" s="51"/>
+      <c r="W44" s="51"/>
+      <c r="X44" s="51"/>
+      <c r="Y44" s="51"/>
+      <c r="Z44" s="51"/>
+      <c r="AA44" s="51"/>
+      <c r="AB44" s="51"/>
+      <c r="AC44" s="51"/>
+      <c r="AD44" s="51"/>
+      <c r="AE44" s="51"/>
+      <c r="AF44" s="51"/>
+      <c r="AG44" s="51"/>
+      <c r="AH44" s="51"/>
+      <c r="AI44" s="51"/>
+      <c r="AJ44" s="51"/>
+      <c r="AK44" s="51"/>
+      <c r="AL44" s="51"/>
+      <c r="AM44" s="51"/>
+      <c r="AN44" s="51"/>
+      <c r="AO44" s="51"/>
+      <c r="AP44" s="51"/>
+      <c r="AQ44" s="51"/>
+      <c r="AR44" s="51"/>
+      <c r="AS44" s="51"/>
+      <c r="AT44" s="51"/>
+      <c r="AU44" s="51"/>
+      <c r="AV44" s="51"/>
+      <c r="AW44" s="51"/>
     </row>
     <row r="45" spans="2:54" ht="12.5" customHeight="1">
       <c r="B45" s="7"/>
@@ -4323,27 +4320,27 @@
       <c r="M45" s="7"/>
       <c r="N45" s="7"/>
       <c r="O45" s="7"/>
-      <c r="P45" s="43"/>
-      <c r="Q45" s="43"/>
-      <c r="R45" s="44"/>
-      <c r="S45" s="44"/>
+      <c r="P45" s="41"/>
+      <c r="Q45" s="41"/>
+      <c r="R45" s="42"/>
+      <c r="S45" s="42"/>
       <c r="T45" s="7"/>
-      <c r="U45" s="45"/>
-      <c r="V45" s="45"/>
-      <c r="W45" s="45"/>
-      <c r="X45" s="45"/>
-      <c r="Y45" s="45"/>
-      <c r="Z45" s="45"/>
-      <c r="AA45" s="45"/>
-      <c r="AB45" s="45"/>
-      <c r="AC45" s="45"/>
-      <c r="AD45" s="45"/>
-      <c r="AE45" s="45"/>
-      <c r="AF45" s="45"/>
-      <c r="AG45" s="45"/>
-      <c r="AH45" s="45"/>
-      <c r="AI45" s="45"/>
-      <c r="AJ45" s="45"/>
+      <c r="U45" s="43"/>
+      <c r="V45" s="43"/>
+      <c r="W45" s="43"/>
+      <c r="X45" s="43"/>
+      <c r="Y45" s="43"/>
+      <c r="Z45" s="43"/>
+      <c r="AA45" s="43"/>
+      <c r="AB45" s="43"/>
+      <c r="AC45" s="43"/>
+      <c r="AD45" s="43"/>
+      <c r="AE45" s="43"/>
+      <c r="AF45" s="43"/>
+      <c r="AG45" s="43"/>
+      <c r="AH45" s="43"/>
+      <c r="AI45" s="43"/>
+      <c r="AJ45" s="43"/>
       <c r="AK45" s="7"/>
       <c r="AL45" s="7"/>
       <c r="AM45" s="7"/>
@@ -4351,161 +4348,161 @@
     </row>
     <row r="46" spans="2:54" ht="20" customHeight="1" thickBot="1">
       <c r="B46" s="7"/>
-      <c r="C46" s="46"/>
-      <c r="D46" s="46"/>
-      <c r="E46" s="46"/>
-      <c r="F46" s="46"/>
-      <c r="G46" s="46"/>
-      <c r="H46" s="46"/>
-      <c r="I46" s="46"/>
-      <c r="J46" s="46"/>
-      <c r="K46" s="46"/>
-      <c r="L46" s="46"/>
-      <c r="M46" s="46"/>
-      <c r="N46" s="46"/>
-      <c r="O46" s="46"/>
-      <c r="P46" s="46"/>
-      <c r="Q46" s="46"/>
-      <c r="R46" s="46"/>
-      <c r="S46" s="46"/>
-      <c r="T46" s="46"/>
-      <c r="U46" s="46"/>
-      <c r="V46" s="46"/>
-      <c r="W46" s="46"/>
-      <c r="X46" s="46"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="44"/>
+      <c r="F46" s="44"/>
+      <c r="G46" s="44"/>
+      <c r="H46" s="44"/>
+      <c r="I46" s="44"/>
+      <c r="J46" s="44"/>
+      <c r="K46" s="44"/>
+      <c r="L46" s="44"/>
+      <c r="M46" s="44"/>
+      <c r="N46" s="44"/>
+      <c r="O46" s="44"/>
+      <c r="P46" s="44"/>
+      <c r="Q46" s="44"/>
+      <c r="R46" s="44"/>
+      <c r="S46" s="44"/>
+      <c r="T46" s="44"/>
+      <c r="U46" s="44"/>
+      <c r="V46" s="44"/>
+      <c r="W46" s="44"/>
+      <c r="X46" s="44"/>
       <c r="Y46" s="22"/>
-      <c r="Z46" s="46"/>
-      <c r="AA46" s="46"/>
-      <c r="AB46" s="46"/>
-      <c r="AC46" s="46"/>
-      <c r="AD46" s="46"/>
-      <c r="AE46" s="46"/>
-      <c r="AF46" s="46"/>
-      <c r="AG46" s="46"/>
-      <c r="AH46" s="46"/>
-      <c r="AI46" s="46"/>
-      <c r="AJ46" s="46"/>
-      <c r="AK46" s="46"/>
-      <c r="AL46" s="46"/>
-      <c r="AM46" s="46"/>
-      <c r="AN46" s="46"/>
-      <c r="AO46" s="46"/>
-      <c r="AP46" s="46"/>
-      <c r="AQ46" s="46"/>
-      <c r="AR46" s="46"/>
-      <c r="AS46" s="46"/>
-      <c r="AT46" s="46"/>
-      <c r="AU46" s="46"/>
-      <c r="AV46" s="46"/>
-      <c r="AW46" s="46"/>
+      <c r="Z46" s="44"/>
+      <c r="AA46" s="44"/>
+      <c r="AB46" s="44"/>
+      <c r="AC46" s="44"/>
+      <c r="AD46" s="44"/>
+      <c r="AE46" s="44"/>
+      <c r="AF46" s="44"/>
+      <c r="AG46" s="44"/>
+      <c r="AH46" s="44"/>
+      <c r="AI46" s="44"/>
+      <c r="AJ46" s="44"/>
+      <c r="AK46" s="44"/>
+      <c r="AL46" s="44"/>
+      <c r="AM46" s="44"/>
+      <c r="AN46" s="44"/>
+      <c r="AO46" s="44"/>
+      <c r="AP46" s="44"/>
+      <c r="AQ46" s="44"/>
+      <c r="AR46" s="44"/>
+      <c r="AS46" s="44"/>
+      <c r="AT46" s="44"/>
+      <c r="AU46" s="44"/>
+      <c r="AV46" s="44"/>
+      <c r="AW46" s="44"/>
     </row>
     <row r="47" spans="2:54" ht="22.25" customHeight="1" thickTop="1">
       <c r="B47" s="7"/>
-      <c r="C47" s="47" t="s">
+      <c r="C47" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="D47" s="47"/>
-      <c r="E47" s="47"/>
-      <c r="F47" s="47"/>
-      <c r="G47" s="47"/>
-      <c r="H47" s="47"/>
-      <c r="I47" s="47"/>
-      <c r="J47" s="47"/>
-      <c r="K47" s="47"/>
-      <c r="L47" s="47"/>
-      <c r="M47" s="47"/>
-      <c r="N47" s="47"/>
-      <c r="O47" s="47"/>
-      <c r="P47" s="47"/>
-      <c r="Q47" s="47"/>
-      <c r="R47" s="47"/>
-      <c r="S47" s="47"/>
-      <c r="T47" s="47"/>
-      <c r="U47" s="47"/>
-      <c r="V47" s="47"/>
-      <c r="W47" s="47"/>
-      <c r="X47" s="47"/>
+      <c r="D47" s="45"/>
+      <c r="E47" s="45"/>
+      <c r="F47" s="45"/>
+      <c r="G47" s="45"/>
+      <c r="H47" s="45"/>
+      <c r="I47" s="45"/>
+      <c r="J47" s="45"/>
+      <c r="K47" s="45"/>
+      <c r="L47" s="45"/>
+      <c r="M47" s="45"/>
+      <c r="N47" s="45"/>
+      <c r="O47" s="45"/>
+      <c r="P47" s="45"/>
+      <c r="Q47" s="45"/>
+      <c r="R47" s="45"/>
+      <c r="S47" s="45"/>
+      <c r="T47" s="45"/>
+      <c r="U47" s="45"/>
+      <c r="V47" s="45"/>
+      <c r="W47" s="45"/>
+      <c r="X47" s="45"/>
       <c r="Y47" s="7"/>
-      <c r="Z47" s="47" t="s">
+      <c r="Z47" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="AA47" s="47"/>
-      <c r="AB47" s="47"/>
-      <c r="AC47" s="47"/>
-      <c r="AD47" s="47"/>
-      <c r="AE47" s="47"/>
-      <c r="AF47" s="47"/>
-      <c r="AG47" s="47"/>
-      <c r="AH47" s="47"/>
-      <c r="AI47" s="47"/>
-      <c r="AJ47" s="47"/>
-      <c r="AK47" s="47"/>
-      <c r="AL47" s="47"/>
-      <c r="AM47" s="47"/>
-      <c r="AN47" s="47"/>
-      <c r="AO47" s="47"/>
-      <c r="AP47" s="47"/>
-      <c r="AQ47" s="47"/>
-      <c r="AR47" s="47"/>
-      <c r="AS47" s="47"/>
-      <c r="AT47" s="47"/>
-      <c r="AU47" s="47"/>
-      <c r="AV47" s="47"/>
-      <c r="AW47" s="47"/>
+      <c r="AA47" s="45"/>
+      <c r="AB47" s="45"/>
+      <c r="AC47" s="45"/>
+      <c r="AD47" s="45"/>
+      <c r="AE47" s="45"/>
+      <c r="AF47" s="45"/>
+      <c r="AG47" s="45"/>
+      <c r="AH47" s="45"/>
+      <c r="AI47" s="45"/>
+      <c r="AJ47" s="45"/>
+      <c r="AK47" s="45"/>
+      <c r="AL47" s="45"/>
+      <c r="AM47" s="45"/>
+      <c r="AN47" s="45"/>
+      <c r="AO47" s="45"/>
+      <c r="AP47" s="45"/>
+      <c r="AQ47" s="45"/>
+      <c r="AR47" s="45"/>
+      <c r="AS47" s="45"/>
+      <c r="AT47" s="45"/>
+      <c r="AU47" s="45"/>
+      <c r="AV47" s="45"/>
+      <c r="AW47" s="45"/>
     </row>
     <row r="48" spans="2:54">
       <c r="B48" s="7"/>
-      <c r="C48" s="42" t="s">
+      <c r="C48" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="D48" s="42"/>
-      <c r="E48" s="42"/>
-      <c r="F48" s="42"/>
-      <c r="G48" s="42"/>
-      <c r="H48" s="42"/>
-      <c r="I48" s="42"/>
-      <c r="J48" s="42"/>
-      <c r="K48" s="42"/>
-      <c r="L48" s="42"/>
-      <c r="M48" s="42"/>
-      <c r="N48" s="42"/>
-      <c r="O48" s="42"/>
-      <c r="P48" s="42"/>
-      <c r="Q48" s="42"/>
-      <c r="R48" s="42"/>
-      <c r="S48" s="42"/>
-      <c r="T48" s="42"/>
-      <c r="U48" s="42"/>
-      <c r="V48" s="42"/>
-      <c r="W48" s="42"/>
-      <c r="X48" s="42"/>
+      <c r="D48" s="40"/>
+      <c r="E48" s="40"/>
+      <c r="F48" s="40"/>
+      <c r="G48" s="40"/>
+      <c r="H48" s="40"/>
+      <c r="I48" s="40"/>
+      <c r="J48" s="40"/>
+      <c r="K48" s="40"/>
+      <c r="L48" s="40"/>
+      <c r="M48" s="40"/>
+      <c r="N48" s="40"/>
+      <c r="O48" s="40"/>
+      <c r="P48" s="40"/>
+      <c r="Q48" s="40"/>
+      <c r="R48" s="40"/>
+      <c r="S48" s="40"/>
+      <c r="T48" s="40"/>
+      <c r="U48" s="40"/>
+      <c r="V48" s="40"/>
+      <c r="W48" s="40"/>
+      <c r="X48" s="40"/>
       <c r="Y48" s="7"/>
-      <c r="Z48" s="42" t="s">
+      <c r="Z48" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="AA48" s="42"/>
-      <c r="AB48" s="42"/>
-      <c r="AC48" s="42"/>
-      <c r="AD48" s="42"/>
-      <c r="AE48" s="42"/>
-      <c r="AF48" s="42"/>
-      <c r="AG48" s="42"/>
-      <c r="AH48" s="42"/>
-      <c r="AI48" s="42"/>
-      <c r="AJ48" s="42"/>
-      <c r="AK48" s="42"/>
-      <c r="AL48" s="42"/>
-      <c r="AM48" s="42"/>
-      <c r="AN48" s="42"/>
-      <c r="AO48" s="42"/>
-      <c r="AP48" s="42"/>
-      <c r="AQ48" s="42"/>
-      <c r="AR48" s="42"/>
-      <c r="AS48" s="42"/>
-      <c r="AT48" s="42"/>
-      <c r="AU48" s="42"/>
-      <c r="AV48" s="42"/>
-      <c r="AW48" s="42"/>
+      <c r="AA48" s="40"/>
+      <c r="AB48" s="40"/>
+      <c r="AC48" s="40"/>
+      <c r="AD48" s="40"/>
+      <c r="AE48" s="40"/>
+      <c r="AF48" s="40"/>
+      <c r="AG48" s="40"/>
+      <c r="AH48" s="40"/>
+      <c r="AI48" s="40"/>
+      <c r="AJ48" s="40"/>
+      <c r="AK48" s="40"/>
+      <c r="AL48" s="40"/>
+      <c r="AM48" s="40"/>
+      <c r="AN48" s="40"/>
+      <c r="AO48" s="40"/>
+      <c r="AP48" s="40"/>
+      <c r="AQ48" s="40"/>
+      <c r="AR48" s="40"/>
+      <c r="AS48" s="40"/>
+      <c r="AT48" s="40"/>
+      <c r="AU48" s="40"/>
+      <c r="AV48" s="40"/>
+      <c r="AW48" s="40"/>
       <c r="AX48" s="21"/>
       <c r="AY48" s="21"/>
       <c r="AZ48" s="21"/>
@@ -4513,7 +4510,7 @@
       <c r="BB48" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="167">
+  <mergeCells count="170">
     <mergeCell ref="AN2:AV3"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="G6:AF6"/>
@@ -4620,6 +4617,7 @@
     <mergeCell ref="AG26:AI26"/>
     <mergeCell ref="AJ26:AK26"/>
     <mergeCell ref="AL26:AQ26"/>
+    <mergeCell ref="F25:AF25"/>
     <mergeCell ref="B29:E29"/>
     <mergeCell ref="F29:AF29"/>
     <mergeCell ref="AG29:AI29"/>
@@ -4657,6 +4655,8 @@
     <mergeCell ref="F34:AF34"/>
     <mergeCell ref="AG34:AI34"/>
     <mergeCell ref="AJ34:AK34"/>
+    <mergeCell ref="F32:AF32"/>
+    <mergeCell ref="F33:AF33"/>
     <mergeCell ref="N1:AV1"/>
     <mergeCell ref="C48:X48"/>
     <mergeCell ref="Z48:AW48"/>
